--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/aimeehdz/Desktop/SMR Thermal Loop/thermal-loop/resources/v0.1.1/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD2AFDC2-7D5C-8348-94E9-C88B8F040BE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB86741C-B140-4227-AA60-A33DEA4639A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="16980" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="269">
   <si>
     <t>Total Cost</t>
   </si>
@@ -821,10 +821,28 @@
     <t>Flange, 304 Stainless Steel, Metal Pipe Flange - 4WPV1 | Grainger</t>
   </si>
   <si>
-    <t>Zinc Coated</t>
-  </si>
-  <si>
     <t>Need to be a smaller diameter</t>
+  </si>
+  <si>
+    <t>Std Hex, 1/2"-13 Thread, Hex Nut - 2FE69|U08110.050.0001 - Grainger</t>
+  </si>
+  <si>
+    <t>2FE69</t>
+  </si>
+  <si>
+    <t>Nuts (TO ORDER)</t>
+  </si>
+  <si>
+    <t>Bolts (TO ORDER)</t>
+  </si>
+  <si>
+    <t>Hex Nut: Std Hex, 1/2"-13 Thread, 3/4 in Hex Wd, 7/16 in Hex Ht, Steel, Grade 2, Zinc-Plated, 50 PK</t>
+  </si>
+  <si>
+    <t>Steel, A307A, Hex Tap Bolt - 41UD24|U01209.050.0250 - Grainger</t>
+  </si>
+  <si>
+    <t>41UD24</t>
   </si>
 </sst>
 </file>
@@ -1159,8 +1177,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K105" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K105" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K106" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K106" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1498,24 +1516,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M109"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.1640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5" customWidth="1"/>
+    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.5" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.5" customWidth="1"/>
-    <col min="11" max="11" width="62.5" customWidth="1"/>
-    <col min="12" max="12" width="55.83203125" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.77734375" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
@@ -1550,7 +1568,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
@@ -1576,7 +1594,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15" t="s">
         <v>11</v>
       </c>
@@ -1602,7 +1620,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
@@ -1627,7 +1645,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
@@ -1653,7 +1671,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="14" t="s">
         <v>10</v>
       </c>
@@ -1679,7 +1697,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
@@ -1707,7 +1725,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
@@ -1733,7 +1751,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>15</v>
       </c>
@@ -1760,7 +1778,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="14" t="s">
         <v>16</v>
       </c>
@@ -1785,7 +1803,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>17</v>
       </c>
@@ -1811,7 +1829,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
         <v>18</v>
       </c>
@@ -1835,7 +1853,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>19</v>
       </c>
@@ -1861,7 +1879,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="14" t="s">
         <v>20</v>
       </c>
@@ -1887,7 +1905,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="15" t="s">
         <v>21</v>
       </c>
@@ -1913,7 +1931,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="14" t="s">
         <v>22</v>
       </c>
@@ -1939,7 +1957,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="15" t="s">
         <v>23</v>
       </c>
@@ -1965,7 +1983,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="14" t="s">
         <v>24</v>
       </c>
@@ -1989,7 +2007,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="15" t="s">
         <v>25</v>
       </c>
@@ -2015,7 +2033,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
@@ -2041,7 +2059,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
         <v>27</v>
       </c>
@@ -2067,7 +2085,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="14" t="s">
         <v>28</v>
       </c>
@@ -2093,7 +2111,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="15" t="s">
         <v>29</v>
       </c>
@@ -2119,7 +2137,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="14" t="s">
         <v>30</v>
       </c>
@@ -2145,7 +2163,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="15" t="s">
         <v>28</v>
       </c>
@@ -2171,7 +2189,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="14" t="s">
         <v>31</v>
       </c>
@@ -2197,7 +2215,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="15" t="s">
         <v>17</v>
       </c>
@@ -2222,7 +2240,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="14" t="s">
         <v>32</v>
       </c>
@@ -2246,7 +2264,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="15" t="s">
         <v>33</v>
       </c>
@@ -2270,7 +2288,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="14" t="s">
         <v>34</v>
       </c>
@@ -2294,7 +2312,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="15" t="s">
         <v>35</v>
       </c>
@@ -2318,7 +2336,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="14" t="s">
         <v>35</v>
       </c>
@@ -2342,7 +2360,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="15" t="s">
         <v>36</v>
       </c>
@@ -2366,7 +2384,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="14" t="s">
         <v>36</v>
       </c>
@@ -2390,7 +2408,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="15" t="s">
         <v>37</v>
       </c>
@@ -2414,7 +2432,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="14" t="s">
         <v>37</v>
       </c>
@@ -2438,7 +2456,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="15" t="s">
         <v>35</v>
       </c>
@@ -2462,7 +2480,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="14" t="s">
         <v>38</v>
       </c>
@@ -2486,7 +2504,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="15" t="s">
         <v>38</v>
       </c>
@@ -2510,7 +2528,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="14" t="s">
         <v>12</v>
       </c>
@@ -2534,7 +2552,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="15" t="s">
         <v>39</v>
       </c>
@@ -2558,7 +2576,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="14" t="s">
         <v>40</v>
       </c>
@@ -2582,7 +2600,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="15" t="s">
         <v>41</v>
       </c>
@@ -2606,7 +2624,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="14" t="s">
         <v>42</v>
       </c>
@@ -2630,7 +2648,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="15" t="s">
         <v>43</v>
       </c>
@@ -2654,7 +2672,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="14" t="s">
         <v>44</v>
       </c>
@@ -2678,7 +2696,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="15" t="s">
         <v>45</v>
       </c>
@@ -2702,7 +2720,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="14" t="s">
         <v>45</v>
       </c>
@@ -2726,7 +2744,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="15" t="s">
         <v>46</v>
       </c>
@@ -2750,7 +2768,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="14" t="s">
         <v>47</v>
       </c>
@@ -2774,7 +2792,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="15" t="s">
         <v>46</v>
       </c>
@@ -2798,7 +2816,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="14" t="s">
         <v>46</v>
       </c>
@@ -2822,7 +2840,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="15" t="s">
         <v>48</v>
       </c>
@@ -2846,7 +2864,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="14" t="s">
         <v>49</v>
       </c>
@@ -2870,7 +2888,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="15" t="s">
         <v>50</v>
       </c>
@@ -2894,7 +2912,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="14" t="s">
         <v>35</v>
       </c>
@@ -2918,7 +2936,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="15" t="s">
         <v>48</v>
       </c>
@@ -2942,7 +2960,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="14" t="s">
         <v>39</v>
       </c>
@@ -2966,7 +2984,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="15" t="s">
         <v>12</v>
       </c>
@@ -2990,7 +3008,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="14" t="s">
         <v>51</v>
       </c>
@@ -3014,7 +3032,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="15" t="s">
         <v>46</v>
       </c>
@@ -3038,7 +3056,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="14" t="s">
         <v>52</v>
       </c>
@@ -3062,7 +3080,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="15" t="s">
         <v>52</v>
       </c>
@@ -3086,7 +3104,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="14" t="s">
         <v>48</v>
       </c>
@@ -3110,7 +3128,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="15" t="s">
         <v>45</v>
       </c>
@@ -3134,7 +3152,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="14" t="s">
         <v>37</v>
       </c>
@@ -3158,7 +3176,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="15" t="s">
         <v>53</v>
       </c>
@@ -3182,7 +3200,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="14" t="s">
         <v>45</v>
       </c>
@@ -3206,7 +3224,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="15" t="s">
         <v>54</v>
       </c>
@@ -3230,7 +3248,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="14" t="s">
         <v>54</v>
       </c>
@@ -3254,7 +3272,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="15" t="s">
         <v>55</v>
       </c>
@@ -3278,7 +3296,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="14" t="s">
         <v>46</v>
       </c>
@@ -3302,7 +3320,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="15" t="s">
         <v>56</v>
       </c>
@@ -3326,7 +3344,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="14" t="s">
         <v>57</v>
       </c>
@@ -3350,7 +3368,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="15" t="s">
         <v>11</v>
       </c>
@@ -3374,7 +3392,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="14" t="s">
         <v>58</v>
       </c>
@@ -3398,7 +3416,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="15" t="s">
         <v>46</v>
       </c>
@@ -3422,7 +3440,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="14" t="s">
         <v>39</v>
       </c>
@@ -3446,7 +3464,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="15" t="s">
         <v>59</v>
       </c>
@@ -3470,7 +3488,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="14" t="s">
         <v>60</v>
       </c>
@@ -3494,7 +3512,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="15" t="s">
         <v>61</v>
       </c>
@@ -3518,7 +3536,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="14" t="s">
         <v>62</v>
       </c>
@@ -3542,7 +3560,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="15" t="s">
         <v>63</v>
       </c>
@@ -3566,7 +3584,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="14" t="s">
         <v>64</v>
       </c>
@@ -3590,7 +3608,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="15" t="s">
         <v>35</v>
       </c>
@@ -3614,7 +3632,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="14" t="s">
         <v>63</v>
       </c>
@@ -3638,7 +3656,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="15" t="s">
         <v>65</v>
       </c>
@@ -3662,7 +3680,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="14" t="s">
         <v>63</v>
       </c>
@@ -3686,7 +3704,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="15" t="s">
         <v>66</v>
       </c>
@@ -3710,7 +3728,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="14" t="s">
         <v>67</v>
       </c>
@@ -3734,7 +3752,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="15" t="s">
         <v>46</v>
       </c>
@@ -3758,7 +3776,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="14" t="s">
         <v>68</v>
       </c>
@@ -3780,7 +3798,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="15" t="s">
         <v>68</v>
       </c>
@@ -3802,7 +3820,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="14" t="s">
         <v>69</v>
       </c>
@@ -3824,7 +3842,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="15" t="s">
         <v>67</v>
       </c>
@@ -3848,7 +3866,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="14" t="s">
         <v>70</v>
       </c>
@@ -3872,7 +3890,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="15" t="s">
         <v>66</v>
       </c>
@@ -3896,7 +3914,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
         <v>17</v>
       </c>
@@ -3920,7 +3938,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="15" t="s">
         <v>61</v>
       </c>
@@ -3944,7 +3962,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="14" t="s">
         <v>71</v>
       </c>
@@ -3968,7 +3986,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="15" t="s">
         <v>72</v>
       </c>
@@ -3992,7 +4010,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
         <v>73</v>
       </c>
@@ -4016,7 +4034,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="15" t="s">
         <v>74</v>
       </c>
@@ -4040,54 +4058,78 @@
         <v>255</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="28" t="s">
-        <v>74</v>
+        <v>264</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="C104" s="11"/>
-      <c r="D104" s="29"/>
-      <c r="E104" s="29"/>
+        <v>266</v>
+      </c>
+      <c r="C104" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="D104" s="29">
+        <v>1</v>
+      </c>
+      <c r="E104" s="29">
+        <v>5.35</v>
+      </c>
       <c r="F104" s="7">
         <f>D104*E104</f>
-        <v>0</v>
-      </c>
-      <c r="H104" s="11"/>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
+        <v>5.35</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="28" t="s">
         <v>72</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="C105" s="11"/>
-      <c r="D105" s="29"/>
-      <c r="E105" s="29"/>
+        <v>261</v>
+      </c>
+      <c r="C105" s="11" t="s">
+        <v>268</v>
+      </c>
+      <c r="D105" s="29">
+        <v>1</v>
+      </c>
+      <c r="E105" s="29">
+        <v>3.98</v>
+      </c>
       <c r="F105" s="7">
         <f>D105*E105</f>
+        <v>3.98</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="B106" s="27"/>
+      <c r="C106" s="11"/>
+      <c r="D106" s="29"/>
+      <c r="E106" s="29"/>
+      <c r="F106" s="7">
+        <f>D106*E106</f>
         <v>0</v>
       </c>
-      <c r="H105" s="11"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A106" s="11"/>
-      <c r="B106" s="11"/>
-      <c r="C106" s="11"/>
       <c r="H106" s="11"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="11"/>
       <c r="B107" s="11"/>
       <c r="C107" s="11"/>
       <c r="H107" s="11"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F109" s="6">
-        <f>SUM(F2:F105)</f>
-        <v>9533.0300000000043</v>
+        <f>SUM(F2:F106)</f>
+        <v>9542.3600000000042</v>
       </c>
     </row>
   </sheetData>
@@ -4190,11 +4232,13 @@
     <hyperlink ref="H101" r:id="rId95" display="https://www.grainger.com/product/Flat-Washer-Case-Hardened-22UH10" xr:uid="{F6D6A8E5-AD79-44C6-A73D-2B94FCDD6282}"/>
     <hyperlink ref="H102" r:id="rId96" display="https://www.grainger.com/product/Hex-Head-Cap-Screw-Steel-22RY64" xr:uid="{2D74872F-EB16-4A0C-9164-FAB0F7694052}"/>
     <hyperlink ref="H103" r:id="rId97" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-4FAY9" xr:uid="{DC92A91C-6CBD-4254-8AF0-587D141AC162}"/>
+    <hyperlink ref="H104" r:id="rId98" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
+    <hyperlink ref="H105" r:id="rId99" display="https://www.grainger.com/product/Hex-Tap-Bolt-Steel-41UD24" xr:uid="{2A74E83D-5B73-48D8-B120-DAD4E0091D0B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId98"/>
+  <pageSetup orientation="portrait" r:id="rId100"/>
   <tableParts count="1">
-    <tablePart r:id="rId99"/>
+    <tablePart r:id="rId101"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB86741C-B140-4227-AA60-A33DEA4639A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{ACAB9E25-ACA8-4B4C-939D-A53510876EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="273">
   <si>
     <t>Total Cost</t>
   </si>
@@ -821,9 +821,6 @@
     <t>Flange, 304 Stainless Steel, Metal Pipe Flange - 4WPV1 | Grainger</t>
   </si>
   <si>
-    <t>Need to be a smaller diameter</t>
-  </si>
-  <si>
     <t>Std Hex, 1/2"-13 Thread, Hex Nut - 2FE69|U08110.050.0001 - Grainger</t>
   </si>
   <si>
@@ -839,10 +836,25 @@
     <t>Hex Nut: Std Hex, 1/2"-13 Thread, 3/4 in Hex Wd, 7/16 in Hex Ht, Steel, Grade 2, Zinc-Plated, 50 PK</t>
   </si>
   <si>
-    <t>Steel, A307A, Hex Tap Bolt - 41UD24|U01209.050.0250 - Grainger</t>
-  </si>
-  <si>
-    <t>41UD24</t>
+    <t>Steel, Grade 5, Hex Tap Bolt - 41UE27|U01210.050.0300 - Grainger</t>
+  </si>
+  <si>
+    <t>41UE27</t>
+  </si>
+  <si>
+    <t>Hex Tap Bolt: Steel, Grade 5, Zinc Plated, 1/2"-13, Coarse, 3 in lg, Globally Sourced, Inch, 10 PK</t>
+  </si>
+  <si>
+    <t>Washers (TO ORDER)</t>
+  </si>
+  <si>
+    <t>18-8, Stainless Steel, Mil. Spec. Flat Washer - 2DNV3|NAS1149-C0863R - Grainger</t>
+  </si>
+  <si>
+    <t>Mil. Spec. Flat Washer: 18-8, Stainless Steel, 1/2 in Screw Sz, 0.515 in In Dia, 18-8, 25 PK</t>
+  </si>
+  <si>
+    <t>2DNV3</t>
   </si>
 </sst>
 </file>
@@ -4060,13 +4072,13 @@
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="28" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B104" s="27" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C104" s="11" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D104" s="29">
         <v>1</v>
@@ -4079,46 +4091,56 @@
         <v>5.35</v>
       </c>
       <c r="H104" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="28" t="s">
-        <v>72</v>
+        <v>269</v>
       </c>
       <c r="B105" s="27" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="C105" s="11" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="D105" s="29">
         <v>1</v>
       </c>
       <c r="E105" s="29">
-        <v>3.98</v>
+        <v>10.75</v>
       </c>
       <c r="F105" s="7">
         <f>D105*E105</f>
-        <v>3.98</v>
+        <v>10.75</v>
       </c>
       <c r="H105" s="1" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="28" t="s">
-        <v>265</v>
-      </c>
-      <c r="B106" s="27"/>
-      <c r="C106" s="11"/>
-      <c r="D106" s="29"/>
-      <c r="E106" s="29"/>
+        <v>264</v>
+      </c>
+      <c r="B106" s="27" t="s">
+        <v>268</v>
+      </c>
+      <c r="C106" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="D106" s="29">
+        <v>1</v>
+      </c>
+      <c r="E106" s="29">
+        <v>6.68</v>
+      </c>
       <c r="F106" s="7">
         <f>D106*E106</f>
-        <v>0</v>
-      </c>
-      <c r="H106" s="11"/>
+        <v>6.68</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>266</v>
+      </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="11"/>
@@ -4129,7 +4151,7 @@
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="F109" s="6">
         <f>SUM(F2:F106)</f>
-        <v>9542.3600000000042</v>
+        <v>9555.8100000000049</v>
       </c>
     </row>
   </sheetData>
@@ -4233,12 +4255,13 @@
     <hyperlink ref="H102" r:id="rId96" display="https://www.grainger.com/product/Hex-Head-Cap-Screw-Steel-22RY64" xr:uid="{2D74872F-EB16-4A0C-9164-FAB0F7694052}"/>
     <hyperlink ref="H103" r:id="rId97" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-4FAY9" xr:uid="{DC92A91C-6CBD-4254-8AF0-587D141AC162}"/>
     <hyperlink ref="H104" r:id="rId98" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
-    <hyperlink ref="H105" r:id="rId99" display="https://www.grainger.com/product/Hex-Tap-Bolt-Steel-41UD24" xr:uid="{2A74E83D-5B73-48D8-B120-DAD4E0091D0B}"/>
+    <hyperlink ref="H106" r:id="rId99" display="https://www.grainger.com/product/Hex-Tap-Bolt-Steel-41UE27" xr:uid="{ED784337-5380-4525-A81D-6E27265845C5}"/>
+    <hyperlink ref="H105" r:id="rId100" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId100"/>
+  <pageSetup orientation="portrait" r:id="rId101"/>
   <tableParts count="1">
-    <tablePart r:id="rId101"/>
+    <tablePart r:id="rId102"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{ACAB9E25-ACA8-4B4C-939D-A53510876EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006D401C-62C7-4EE0-92AA-4648FA7ED0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="264">
   <si>
     <t>Total Cost</t>
   </si>
@@ -254,15 +254,6 @@
     <t>Flanged Sleeve Bearings</t>
   </si>
   <si>
-    <t>Washers</t>
-  </si>
-  <si>
-    <t>Botls</t>
-  </si>
-  <si>
-    <t>Nuts</t>
-  </si>
-  <si>
     <t>53UJ14</t>
   </si>
   <si>
@@ -509,15 +500,6 @@
     <t>2NCK6</t>
   </si>
   <si>
-    <t>22UH10</t>
-  </si>
-  <si>
-    <t>22RY64</t>
-  </si>
-  <si>
-    <t>4FAY9</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -797,15 +779,6 @@
     <t>IGUS, Polymer, 1/2 in Bore, Flanged Sleeve Bearing - 2NCK6|RFI-0810-10 - Grainger</t>
   </si>
   <si>
-    <t>Case Hardened, Zinc Plated, Flat Washer - 22UH10|U38400.050.0002 - Grainger</t>
-  </si>
-  <si>
-    <t>Steel, Grade 2, Hex Head Cap Screw - 22RY64|U08210.050.0250 - Grainger</t>
-  </si>
-  <si>
-    <t>Std Hex, 1/2"-13 Thread, Hex Nut - 4FAY9|U04120.050.0001 - Grainger</t>
-  </si>
-  <si>
     <t>Thomas &amp; Betts - 2 X 2 X 72 IN GRAY WIDE SLOT WIRING DUCT | MSC Direct</t>
   </si>
   <si>
@@ -827,27 +800,9 @@
     <t>2FE69</t>
   </si>
   <si>
-    <t>Nuts (TO ORDER)</t>
-  </si>
-  <si>
-    <t>Bolts (TO ORDER)</t>
-  </si>
-  <si>
     <t>Hex Nut: Std Hex, 1/2"-13 Thread, 3/4 in Hex Wd, 7/16 in Hex Ht, Steel, Grade 2, Zinc-Plated, 50 PK</t>
   </si>
   <si>
-    <t>Steel, Grade 5, Hex Tap Bolt - 41UE27|U01210.050.0300 - Grainger</t>
-  </si>
-  <si>
-    <t>41UE27</t>
-  </si>
-  <si>
-    <t>Hex Tap Bolt: Steel, Grade 5, Zinc Plated, 1/2"-13, Coarse, 3 in lg, Globally Sourced, Inch, 10 PK</t>
-  </si>
-  <si>
-    <t>Washers (TO ORDER)</t>
-  </si>
-  <si>
     <t>18-8, Stainless Steel, Mil. Spec. Flat Washer - 2DNV3|NAS1149-C0863R - Grainger</t>
   </si>
   <si>
@@ -855,6 +810,24 @@
   </si>
   <si>
     <t>2DNV3</t>
+  </si>
+  <si>
+    <t>Nuts for heater rod insulated connection</t>
+  </si>
+  <si>
+    <t>Washers for heater rod insulated connection</t>
+  </si>
+  <si>
+    <t>Bolts for heater rod insulated connection</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/Hex-Head-Cap-Screw-Steel-23KZ77</t>
+  </si>
+  <si>
+    <t>23KZ77</t>
+  </si>
+  <si>
+    <t>Hex Head Cap Screw: Steel, Grade 5, Zinc Plated, 1/2"-13, Coarse, 3 in lg, Globally Sourced, 10 PK</t>
   </si>
 </sst>
 </file>
@@ -1189,8 +1162,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K106" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K106" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K103" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K103" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1527,25 +1500,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M109"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M106"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.44140625" customWidth="1"/>
-    <col min="11" max="11" width="62.44140625" customWidth="1"/>
-    <col min="12" max="12" width="55.77734375" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.42578125" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" customWidth="1"/>
+    <col min="12" max="12" width="55.7109375" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>8</v>
       </c>
@@ -1556,7 +1529,7 @@
         <v>7</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>1</v>
@@ -1580,12 +1553,12 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="C2" s="14">
         <v>92012988</v>
@@ -1602,16 +1575,16 @@
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="23" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="27" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C3" s="15">
         <v>67436964</v>
@@ -1628,16 +1601,16 @@
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="24" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="27" t="s">
-        <v>163</v>
+        <v>157</v>
       </c>
       <c r="C4" s="16">
         <v>67473967</v>
@@ -1654,15 +1627,15 @@
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="23" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="27" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="C5" s="17">
         <v>99176795</v>
@@ -1679,19 +1652,19 @@
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="24" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D6" s="8">
         <v>3</v>
@@ -1705,19 +1678,19 @@
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="23" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D7" s="9">
         <v>3</v>
@@ -1731,21 +1704,21 @@
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="24" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
         <v>14</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D8" s="8">
         <v>1</v>
@@ -1759,19 +1732,19 @@
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="23" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D9" s="9">
         <v>1</v>
@@ -1785,20 +1758,20 @@
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="24" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
         <v>16</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D10" s="8">
         <v>1</v>
@@ -1812,18 +1785,18 @@
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="23" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="27" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -1837,17 +1810,17 @@
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="24" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="14" t="s">
         <v>18</v>
       </c>
       <c r="B12" s="27"/>
       <c r="C12" s="14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D12" s="8">
         <v>1</v>
@@ -1861,16 +1834,16 @@
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="27" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="C13" s="20">
         <v>316533</v>
@@ -1887,16 +1860,16 @@
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="24" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
         <v>20</v>
       </c>
       <c r="B14" s="27" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="C14" s="18">
         <v>316530</v>
@@ -1913,16 +1886,16 @@
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="23" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>21</v>
       </c>
       <c r="B15" s="27" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="C15" s="20">
         <v>314802</v>
@@ -1939,16 +1912,16 @@
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="24" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
         <v>22</v>
       </c>
       <c r="B16" s="27" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="C16" s="21">
         <v>164598</v>
@@ -1965,19 +1938,19 @@
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="23" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>23</v>
       </c>
       <c r="B17" s="27" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="D17" s="9">
         <v>25</v>
@@ -1991,17 +1964,17 @@
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="24" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="14" t="s">
         <v>24</v>
       </c>
       <c r="B18" s="27"/>
       <c r="C18" s="14" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="D18" s="8">
         <v>1</v>
@@ -2015,19 +1988,19 @@
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="25" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>25</v>
       </c>
       <c r="B19" s="27" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D19" s="9">
         <v>2</v>
@@ -2041,19 +2014,19 @@
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="24" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="14" t="s">
         <v>26</v>
       </c>
       <c r="B20" s="27" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="D20" s="8">
         <v>1</v>
@@ -2067,19 +2040,19 @@
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="23" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>27</v>
       </c>
       <c r="B21" s="27" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D21" s="9">
         <v>250</v>
@@ -2093,19 +2066,19 @@
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="24" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="14" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="27" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D22" s="8">
         <v>1</v>
@@ -2119,16 +2092,16 @@
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="23" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="27" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="C23" s="15">
         <v>7568365</v>
@@ -2145,16 +2118,16 @@
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="24" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="14" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="27" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C24" s="14">
         <v>8323512</v>
@@ -2171,19 +2144,19 @@
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="23" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="27" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D25" s="9">
         <v>5</v>
@@ -2197,19 +2170,19 @@
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="24" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
         <v>31</v>
       </c>
       <c r="B26" s="27" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D26" s="8">
         <v>4</v>
@@ -2223,19 +2196,19 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="23" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>17</v>
       </c>
       <c r="B27" s="27" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D27" s="9">
         <v>4</v>
@@ -2249,18 +2222,18 @@
       </c>
       <c r="G27" s="2"/>
       <c r="H27" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="14" t="s">
         <v>32</v>
       </c>
       <c r="B28" s="27" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D28" s="8">
         <v>4</v>
@@ -2273,18 +2246,18 @@
         <v>52.92</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>33</v>
       </c>
       <c r="B29" s="27" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D29" s="9">
         <v>4</v>
@@ -2297,18 +2270,18 @@
         <v>51.12</v>
       </c>
       <c r="H29" s="24" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="14" t="s">
         <v>34</v>
       </c>
       <c r="B30" s="27" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="D30" s="8">
         <v>4</v>
@@ -2321,18 +2294,18 @@
         <v>39.96</v>
       </c>
       <c r="H30" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B31" s="27" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="C31" s="19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D31" s="9">
         <v>4</v>
@@ -2345,18 +2318,18 @@
         <v>89.36</v>
       </c>
       <c r="H31" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="14" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="27" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D32" s="8">
         <v>4</v>
@@ -2369,18 +2342,18 @@
         <v>67.56</v>
       </c>
       <c r="H32" s="23" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="27" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="C33" s="19" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D33" s="9">
         <v>2</v>
@@ -2393,18 +2366,18 @@
         <v>43.58</v>
       </c>
       <c r="H33" s="24" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="14" t="s">
         <v>36</v>
       </c>
       <c r="B34" s="27" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D34" s="8">
         <v>2</v>
@@ -2417,18 +2390,18 @@
         <v>39.72</v>
       </c>
       <c r="H34" s="23" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>37</v>
       </c>
       <c r="B35" s="27" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D35" s="9">
         <v>1</v>
@@ -2441,18 +2414,18 @@
         <v>36.979999999999997</v>
       </c>
       <c r="H35" s="24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B36" s="27" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D36" s="8">
         <v>1</v>
@@ -2465,18 +2438,18 @@
         <v>26.2</v>
       </c>
       <c r="H36" s="23" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B37" s="27" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="C37" s="19" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D37" s="9">
         <v>4</v>
@@ -2489,18 +2462,18 @@
         <v>76.88</v>
       </c>
       <c r="H37" s="24" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
         <v>38</v>
       </c>
       <c r="B38" s="27" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D38" s="8">
         <v>6</v>
@@ -2513,18 +2486,18 @@
         <v>14.879999999999999</v>
       </c>
       <c r="H38" s="23" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>38</v>
       </c>
       <c r="B39" s="27" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C39" s="19" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="D39" s="9">
         <v>6</v>
@@ -2537,18 +2510,18 @@
         <v>19.259999999999998</v>
       </c>
       <c r="H39" s="24" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="14" t="s">
         <v>12</v>
       </c>
       <c r="B40" s="27" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D40" s="8">
         <v>1</v>
@@ -2561,18 +2534,18 @@
         <v>16.010000000000002</v>
       </c>
       <c r="H40" s="23" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>39</v>
       </c>
       <c r="B41" s="27" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="C41" s="19" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D41" s="9">
         <v>3</v>
@@ -2585,18 +2558,18 @@
         <v>22.65</v>
       </c>
       <c r="H41" s="24" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="14" t="s">
         <v>40</v>
       </c>
       <c r="B42" s="27" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D42" s="8">
         <v>12</v>
@@ -2609,18 +2582,18 @@
         <v>42.599999999999994</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>41</v>
       </c>
       <c r="B43" s="27" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D43" s="9">
         <v>1</v>
@@ -2633,18 +2606,18 @@
         <v>50.51</v>
       </c>
       <c r="H43" s="24" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="14" t="s">
         <v>42</v>
       </c>
       <c r="B44" s="27" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D44" s="8">
         <v>1</v>
@@ -2657,18 +2630,18 @@
         <v>24.17</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>43</v>
       </c>
       <c r="B45" s="27" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C45" s="19" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D45" s="9">
         <v>1</v>
@@ -2681,18 +2654,18 @@
         <v>26.01</v>
       </c>
       <c r="H45" s="24" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B46" s="27" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D46" s="8">
         <v>1</v>
@@ -2705,18 +2678,18 @@
         <v>16.82</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B47" s="27" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="C47" s="19" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D47" s="9">
         <v>2</v>
@@ -2729,18 +2702,18 @@
         <v>50.34</v>
       </c>
       <c r="H47" s="24" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
         <v>45</v>
       </c>
       <c r="B48" s="27" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D48" s="8">
         <v>2</v>
@@ -2753,18 +2726,18 @@
         <v>25</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B49" s="27" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D49" s="9">
         <v>1</v>
@@ -2777,18 +2750,18 @@
         <v>28.56</v>
       </c>
       <c r="H49" s="24" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
         <v>47</v>
       </c>
       <c r="B50" s="27" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D50" s="8">
         <v>5</v>
@@ -2801,18 +2774,18 @@
         <v>16.75</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B51" s="27" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="C51" s="19" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D51" s="9">
         <v>1</v>
@@ -2825,18 +2798,18 @@
         <v>14.81</v>
       </c>
       <c r="H51" s="24" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B52" s="27" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D52" s="8">
         <v>1</v>
@@ -2849,18 +2822,18 @@
         <v>19.989999999999998</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B53" s="27" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="C53" s="19" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D53" s="9">
         <v>5</v>
@@ -2873,18 +2846,18 @@
         <v>26.8</v>
       </c>
       <c r="H53" s="24" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="14" t="s">
         <v>49</v>
       </c>
       <c r="B54" s="27" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D54" s="8">
         <v>1</v>
@@ -2897,18 +2870,18 @@
         <v>40.14</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B55" s="27" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D55" s="9">
         <v>1</v>
@@ -2921,18 +2894,18 @@
         <v>300</v>
       </c>
       <c r="H55" s="24" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="14" t="s">
         <v>35</v>
       </c>
       <c r="B56" s="27" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D56" s="8">
         <v>6</v>
@@ -2945,18 +2918,18 @@
         <v>69.179999999999993</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B57" s="27" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D57" s="9">
         <v>2</v>
@@ -2969,18 +2942,18 @@
         <v>9.5</v>
       </c>
       <c r="H57" s="24" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D58" s="8">
         <v>1</v>
@@ -2993,18 +2966,18 @@
         <v>5.41</v>
       </c>
       <c r="H58" s="23" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
         <v>12</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D59" s="9">
         <v>1</v>
@@ -3017,18 +2990,18 @@
         <v>9.0299999999999994</v>
       </c>
       <c r="H59" s="24" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
         <v>51</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D60" s="8">
         <v>1</v>
@@ -3041,18 +3014,18 @@
         <v>16.87</v>
       </c>
       <c r="H60" s="23" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="C61" s="19" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D61" s="9">
         <v>1</v>
@@ -3065,18 +3038,18 @@
         <v>14.02</v>
       </c>
       <c r="H61" s="24" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="14" t="s">
         <v>52</v>
       </c>
       <c r="B62" s="27" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D62" s="8">
         <v>1</v>
@@ -3089,18 +3062,18 @@
         <v>8.83</v>
       </c>
       <c r="H62" s="23" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B63" s="27" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="C63" s="19" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D63" s="9">
         <v>1</v>
@@ -3113,18 +3086,18 @@
         <v>7.19</v>
       </c>
       <c r="H63" s="24" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="14" t="s">
         <v>48</v>
       </c>
       <c r="B64" s="27" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D64" s="8">
         <v>4</v>
@@ -3137,18 +3110,18 @@
         <v>11.04</v>
       </c>
       <c r="H64" s="23" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
         <v>45</v>
       </c>
       <c r="B65" s="27" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="C65" s="19" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D65" s="9">
         <v>2</v>
@@ -3161,18 +3134,18 @@
         <v>6.98</v>
       </c>
       <c r="H65" s="24" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="14" t="s">
         <v>37</v>
       </c>
       <c r="B66" s="27" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D66" s="8">
         <v>1</v>
@@ -3185,18 +3158,18 @@
         <v>42.76</v>
       </c>
       <c r="H66" s="23" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B67" s="27" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="C67" s="19" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D67" s="9">
         <v>1</v>
@@ -3205,22 +3178,22 @@
         <v>45.81</v>
       </c>
       <c r="F67" s="7">
-        <f t="shared" ref="F67:F103" si="1">D67*E67</f>
+        <f t="shared" ref="F67:F100" si="1">D67*E67</f>
         <v>45.81</v>
       </c>
       <c r="H67" s="24" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="14" t="s">
         <v>45</v>
       </c>
       <c r="B68" s="27" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="C68" s="18" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="D68" s="8">
         <v>1</v>
@@ -3233,18 +3206,18 @@
         <v>18.73</v>
       </c>
       <c r="H68" s="23" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="15" t="s">
         <v>54</v>
       </c>
       <c r="B69" s="27" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="C69" s="19" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D69" s="9">
         <v>1</v>
@@ -3257,18 +3230,18 @@
         <v>4.99</v>
       </c>
       <c r="H69" s="24" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="14" t="s">
         <v>54</v>
       </c>
       <c r="B70" s="27" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C70" s="18" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="D70" s="8">
         <v>1</v>
@@ -3281,18 +3254,18 @@
         <v>4.68</v>
       </c>
       <c r="H70" s="23" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B71" s="27" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="C71" s="19" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D71" s="9">
         <v>1</v>
@@ -3305,18 +3278,18 @@
         <v>39.72</v>
       </c>
       <c r="H71" s="24" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B72" s="27" t="s">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C72" s="18" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D72" s="8">
         <v>1</v>
@@ -3329,18 +3302,18 @@
         <v>15.07</v>
       </c>
       <c r="H72" s="23" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B73" s="27" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C73" s="19" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D73" s="9">
         <v>1</v>
@@ -3353,18 +3326,18 @@
         <v>45.58</v>
       </c>
       <c r="H73" s="24" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="14" t="s">
         <v>57</v>
       </c>
       <c r="B74" s="27" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="C74" s="18" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D74" s="8">
         <v>1</v>
@@ -3377,18 +3350,18 @@
         <v>6.43</v>
       </c>
       <c r="H74" s="23" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="15" t="s">
         <v>11</v>
       </c>
       <c r="B75" s="27" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C75" s="19" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D75" s="9">
         <v>1</v>
@@ -3401,18 +3374,18 @@
         <v>26.5</v>
       </c>
       <c r="H75" s="24" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="14" t="s">
         <v>58</v>
       </c>
       <c r="B76" s="27" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="C76" s="14" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D76" s="8">
         <v>2</v>
@@ -3425,18 +3398,18 @@
         <v>25.6</v>
       </c>
       <c r="H76" s="23" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B77" s="27" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C77" s="19" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D77" s="9">
         <v>1</v>
@@ -3449,18 +3422,18 @@
         <v>14.16</v>
       </c>
       <c r="H77" s="24" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="14" t="s">
         <v>39</v>
       </c>
       <c r="B78" s="27" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="C78" s="18" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D78" s="8">
         <v>5</v>
@@ -3473,18 +3446,18 @@
         <v>34.900000000000006</v>
       </c>
       <c r="H78" s="23" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="15" t="s">
         <v>59</v>
       </c>
       <c r="B79" s="27" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C79" s="19" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D79" s="9">
         <v>1</v>
@@ -3497,18 +3470,18 @@
         <v>3.76</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B80" s="27" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="C80" s="18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D80" s="8">
         <v>1</v>
@@ -3521,18 +3494,18 @@
         <v>4.72</v>
       </c>
       <c r="H80" s="23" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B81" s="27" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="C81" s="19" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D81" s="9">
         <v>2</v>
@@ -3545,18 +3518,18 @@
         <v>122.08</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B82" s="27" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="C82" s="18" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D82" s="8">
         <v>1</v>
@@ -3569,18 +3542,18 @@
         <v>382.26</v>
       </c>
       <c r="H82" s="23" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="15" t="s">
         <v>63</v>
       </c>
       <c r="B83" s="27" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="C83" s="19" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D83" s="9">
         <v>2</v>
@@ -3593,18 +3566,18 @@
         <v>95.56</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B84" s="27" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C84" s="18" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D84" s="8">
         <v>5</v>
@@ -3617,18 +3590,18 @@
         <v>49.95</v>
       </c>
       <c r="H84" s="23" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="15" t="s">
         <v>35</v>
       </c>
       <c r="B85" s="27" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C85" s="19" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D85" s="9">
         <v>1</v>
@@ -3641,18 +3614,18 @@
         <v>6.02</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="14" t="s">
         <v>63</v>
       </c>
       <c r="B86" s="27" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="C86" s="18" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D86" s="8">
         <v>1</v>
@@ -3665,18 +3638,18 @@
         <v>2.3199999999999998</v>
       </c>
       <c r="H86" s="23" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="15" t="s">
         <v>65</v>
       </c>
       <c r="B87" s="27" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C87" s="15" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="D87" s="9">
         <v>4</v>
@@ -3689,18 +3662,18 @@
         <v>47.96</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="14" t="s">
         <v>63</v>
       </c>
       <c r="B88" s="27" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C88" s="14" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D88" s="8">
         <v>1</v>
@@ -3713,18 +3686,18 @@
         <v>9.99</v>
       </c>
       <c r="H88" s="23" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B89" s="27" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="C89" s="19" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D89" s="9">
         <v>2</v>
@@ -3737,18 +3710,18 @@
         <v>29.26</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="14" t="s">
         <v>67</v>
       </c>
       <c r="B90" s="27" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C90" s="22" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D90" s="8">
         <v>4</v>
@@ -3761,18 +3734,18 @@
         <v>669.68</v>
       </c>
       <c r="H90" s="23" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B91" s="27" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="C91" s="19" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D91" s="9">
         <v>1</v>
@@ -3785,16 +3758,16 @@
         <v>12.61</v>
       </c>
       <c r="H91" s="24" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="14" t="s">
         <v>68</v>
       </c>
       <c r="B92" s="27"/>
       <c r="C92" s="14" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D92" s="8">
         <v>2</v>
@@ -3807,16 +3780,16 @@
         <v>20.9</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="15" t="s">
         <v>68</v>
       </c>
       <c r="B93" s="27"/>
       <c r="C93" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D93" s="9">
         <v>3</v>
@@ -3829,10 +3802,10 @@
         <v>6.5400000000000009</v>
       </c>
       <c r="H93" s="26" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="14" t="s">
         <v>69</v>
       </c>
@@ -3851,18 +3824,18 @@
         <v>107.91</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="15" t="s">
         <v>67</v>
       </c>
       <c r="B95" s="27" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C95" s="15" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D95" s="9">
         <v>3</v>
@@ -3875,15 +3848,15 @@
         <v>502.26</v>
       </c>
       <c r="H95" s="24" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="14" t="s">
         <v>70</v>
       </c>
       <c r="B96" s="27" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="C96" s="14">
         <v>316529</v>
@@ -3899,18 +3872,18 @@
         <v>405</v>
       </c>
       <c r="H96" s="23" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="15" t="s">
         <v>66</v>
       </c>
       <c r="B97" s="27" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D97" s="9">
         <v>1</v>
@@ -3923,18 +3896,18 @@
         <v>37.4</v>
       </c>
       <c r="H97" s="24" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="14" t="s">
         <v>17</v>
       </c>
       <c r="B98" s="27" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="C98" s="13" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D98" s="8">
         <v>1</v>
@@ -3947,18 +3920,18 @@
         <v>20.91</v>
       </c>
       <c r="H98" s="23" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B99" s="27" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D99" s="9">
         <v>1</v>
@@ -3971,18 +3944,18 @@
         <v>79.099999999999994</v>
       </c>
       <c r="H99" s="24" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="14" t="s">
         <v>71</v>
       </c>
       <c r="B100" s="27" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="C100" s="18" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D100" s="8">
         <v>1</v>
@@ -3995,163 +3968,90 @@
         <v>16.260000000000002</v>
       </c>
       <c r="H100" s="23" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="28" t="s">
+        <v>258</v>
+      </c>
+      <c r="B101" s="27" t="s">
+        <v>254</v>
+      </c>
+      <c r="C101" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="D101" s="29">
+        <v>1</v>
+      </c>
+      <c r="E101" s="29">
+        <v>5.35</v>
+      </c>
+      <c r="F101" s="7">
+        <f>D101*E101</f>
+        <v>5.35</v>
+      </c>
+      <c r="H101" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="B101" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="C101" s="19" t="s">
-        <v>157</v>
-      </c>
-      <c r="D101" s="9">
-        <v>1</v>
-      </c>
-      <c r="E101" s="9">
-        <v>6.94</v>
-      </c>
-      <c r="F101" s="7">
-        <f t="shared" si="1"/>
-        <v>6.94</v>
-      </c>
-      <c r="H101" s="24" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
-        <v>73</v>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="28" t="s">
+        <v>259</v>
       </c>
       <c r="B102" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="C102" s="18" t="s">
-        <v>158</v>
-      </c>
-      <c r="D102" s="8">
-        <v>1</v>
-      </c>
-      <c r="E102" s="8">
-        <v>7.91</v>
+        <v>256</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="D102" s="29">
+        <v>1</v>
+      </c>
+      <c r="E102" s="29">
+        <v>10.75</v>
       </c>
       <c r="F102" s="7">
-        <f t="shared" si="1"/>
-        <v>7.91</v>
-      </c>
-      <c r="H102" s="23" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="15" t="s">
-        <v>74</v>
+        <f>D102*E102</f>
+        <v>10.75</v>
+      </c>
+      <c r="H102" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="28" t="s">
+        <v>260</v>
       </c>
       <c r="B103" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="C103" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="D103" s="9">
-        <v>1</v>
-      </c>
-      <c r="E103" s="9">
-        <v>7.68</v>
+        <v>263</v>
+      </c>
+      <c r="C103" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="D103" s="29">
+        <v>1</v>
+      </c>
+      <c r="E103" s="29">
+        <v>6.68</v>
       </c>
       <c r="F103" s="7">
-        <f t="shared" si="1"/>
-        <v>7.68</v>
-      </c>
-      <c r="H103" s="24" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="28" t="s">
-        <v>263</v>
-      </c>
-      <c r="B104" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="C104" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="D104" s="29">
-        <v>1</v>
-      </c>
-      <c r="E104" s="29">
-        <v>5.35</v>
-      </c>
-      <c r="F104" s="7">
-        <f>D104*E104</f>
-        <v>5.35</v>
-      </c>
-      <c r="H104" s="1" t="s">
+        <v>7.96</v>
+      </c>
+      <c r="H103" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="28" t="s">
-        <v>269</v>
-      </c>
-      <c r="B105" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="C105" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="D105" s="29">
-        <v>1</v>
-      </c>
-      <c r="E105" s="29">
-        <v>10.75</v>
-      </c>
-      <c r="F105" s="7">
-        <f>D105*E105</f>
-        <v>10.75</v>
-      </c>
-      <c r="H105" s="1" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="28" t="s">
-        <v>264</v>
-      </c>
-      <c r="B106" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="D106" s="29">
-        <v>1</v>
-      </c>
-      <c r="E106" s="29">
-        <v>6.68</v>
-      </c>
-      <c r="F106" s="7">
-        <f>D106*E106</f>
-        <v>6.68</v>
-      </c>
-      <c r="H106" s="1" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="11"/>
-      <c r="B107" s="11"/>
-      <c r="C107" s="11"/>
-      <c r="H107" s="11"/>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="F109" s="6">
-        <f>SUM(F2:F106)</f>
-        <v>9555.8100000000049</v>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="H104" s="11"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F106" s="6">
+        <f>SUM(F2:F103)</f>
+        <v>9534.5600000000031</v>
       </c>
     </row>
   </sheetData>
@@ -4251,17 +4151,14 @@
     <hyperlink ref="H98" r:id="rId92" display="https://www.grainger.com/product/20XM58?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=5fbed57f928e0d20c3753de78a2b9a38ffd20234e126526a2f6d6b4fe4e772db&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C07356E-8DE4-40F2-A1AD-4E8492786388}"/>
     <hyperlink ref="H99" r:id="rId93" xr:uid="{94CC04D7-EB9A-450B-BB5C-C756BC4DE898}"/>
     <hyperlink ref="H100" r:id="rId94" display="https://www.grainger.com/product/IGUS-Flanged-Sleeve-Bearing-Polymer-2NCK6" xr:uid="{83384CCF-7FBA-4E7B-9A1D-1C877A885273}"/>
-    <hyperlink ref="H101" r:id="rId95" display="https://www.grainger.com/product/Flat-Washer-Case-Hardened-22UH10" xr:uid="{F6D6A8E5-AD79-44C6-A73D-2B94FCDD6282}"/>
-    <hyperlink ref="H102" r:id="rId96" display="https://www.grainger.com/product/Hex-Head-Cap-Screw-Steel-22RY64" xr:uid="{2D74872F-EB16-4A0C-9164-FAB0F7694052}"/>
-    <hyperlink ref="H103" r:id="rId97" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-4FAY9" xr:uid="{DC92A91C-6CBD-4254-8AF0-587D141AC162}"/>
-    <hyperlink ref="H104" r:id="rId98" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
-    <hyperlink ref="H106" r:id="rId99" display="https://www.grainger.com/product/Hex-Tap-Bolt-Steel-41UE27" xr:uid="{ED784337-5380-4525-A81D-6E27265845C5}"/>
-    <hyperlink ref="H105" r:id="rId100" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
+    <hyperlink ref="H101" r:id="rId95" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
+    <hyperlink ref="H102" r:id="rId96" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
+    <hyperlink ref="H103" r:id="rId97" xr:uid="{FDEFAFD3-3687-4641-964A-8BC9B3E42512}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId101"/>
+  <pageSetup orientation="portrait" r:id="rId98"/>
   <tableParts count="1">
-    <tablePart r:id="rId102"/>
+    <tablePart r:id="rId99"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{006D401C-62C7-4EE0-92AA-4648FA7ED0CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9767054-3909-4284-9249-BF43A556FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="276">
   <si>
     <t>Total Cost</t>
   </si>
@@ -828,6 +828,42 @@
   </si>
   <si>
     <t>Hex Head Cap Screw: Steel, Grade 5, Zinc Plated, 1/2"-13, Coarse, 3 in lg, Globally Sourced, 10 PK</t>
+  </si>
+  <si>
+    <t>USB hub</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series 4-Port Industrial-Grade USB 3.x (5Gbps) Hub - 20 kV ESD Immunity, Metal Housing, Mountable</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> U360-004-IND</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/tripp-lite-4-port-industrial-usb-3.0-superspeed-hub-15kv-esd-immunity-metal/3682489?pfm=srh</t>
+  </si>
+  <si>
+    <t>15ft usb cable hub to PC</t>
+  </si>
+  <si>
+    <t>15ft usb cable dcaq to hub</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/belkin-16ft-4.8m-usb-2.0-a-b-device-cable-printer-cable/1109346</t>
+  </si>
+  <si>
+    <t>https://www.cdwg.com/product/eaton-tripp-lite-series-usb-3.2-gen-1-superspeed-device-cable-a-to-b-m-m/3386201</t>
+  </si>
+  <si>
+    <t>Belkin USB-A to USB Type B Cable - M/M - 480 Mbps - 16ft - Device Extension Cable</t>
+  </si>
+  <si>
+    <t>Eaton Tripp Lite Series USB 3.2 Gen 1 SuperSpeed Device Cable (A to B M/M) Black, 15 ft. (4.57 m) - USB cable - USB Type</t>
+  </si>
+  <si>
+    <t>U322-015-BK</t>
+  </si>
+  <si>
+    <t>F3U133B16</t>
   </si>
 </sst>
 </file>
@@ -838,7 +874,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -898,6 +934,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3A414B"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF444444"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -963,7 +1006,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1048,6 +1091,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1162,8 +1212,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K103" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K103" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K112" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K112" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1500,7 +1550,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M106"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
@@ -3178,7 +3228,7 @@
         <v>45.81</v>
       </c>
       <c r="F67" s="7">
-        <f t="shared" ref="F67:F100" si="1">D67*E67</f>
+        <f t="shared" ref="F67:F109" si="1">D67*E67</f>
         <v>45.81</v>
       </c>
       <c r="H67" s="24" t="s">
@@ -3784,274 +3834,418 @@
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="15" t="s">
+      <c r="A93" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C93" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="D93" s="2">
+        <v>1</v>
+      </c>
+      <c r="E93" s="7">
+        <v>110</v>
+      </c>
+      <c r="F93" s="7">
+        <f>D93*E93</f>
+        <v>110</v>
+      </c>
+      <c r="H93" s="25" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" s="30" t="s">
+        <v>268</v>
+      </c>
+      <c r="B94" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C94" s="30" t="s">
+        <v>274</v>
+      </c>
+      <c r="D94" s="8">
+        <v>1</v>
+      </c>
+      <c r="E94" s="8">
+        <v>13.55</v>
+      </c>
+      <c r="F94" s="7">
+        <f>D94*E94</f>
+        <v>13.55</v>
+      </c>
+      <c r="H94" s="23" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A95" s="30" t="s">
+        <v>269</v>
+      </c>
+      <c r="B95" s="31" t="s">
+        <v>272</v>
+      </c>
+      <c r="C95" s="30" t="s">
+        <v>275</v>
+      </c>
+      <c r="D95" s="8">
+        <v>1</v>
+      </c>
+      <c r="E95" s="8">
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="F95" s="7">
+        <f>D95*E95</f>
+        <v>8.4700000000000006</v>
+      </c>
+      <c r="H95" s="23" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="30"/>
+      <c r="B96" s="31"/>
+      <c r="C96" s="30"/>
+      <c r="D96" s="8"/>
+      <c r="E96" s="8"/>
+      <c r="F96" s="7">
+        <f>D96*E96</f>
+        <v>0</v>
+      </c>
+      <c r="H96" s="25"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="30"/>
+      <c r="B97" s="31"/>
+      <c r="C97" s="30"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="7">
+        <f>D97*E97</f>
+        <v>0</v>
+      </c>
+      <c r="H97" s="25"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A98" s="30"/>
+      <c r="B98" s="31"/>
+      <c r="C98" s="30"/>
+      <c r="D98" s="8"/>
+      <c r="E98" s="8"/>
+      <c r="F98" s="7">
+        <f>D98*E98</f>
+        <v>0</v>
+      </c>
+      <c r="H98" s="25"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A99" s="30"/>
+      <c r="B99" s="31"/>
+      <c r="C99" s="30"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="7">
+        <f>D99*E99</f>
+        <v>0</v>
+      </c>
+      <c r="H99" s="25"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A100" s="30"/>
+      <c r="B100" s="31"/>
+      <c r="C100" s="30"/>
+      <c r="D100" s="8"/>
+      <c r="E100" s="8"/>
+      <c r="F100" s="7">
+        <f>D100*E100</f>
+        <v>0</v>
+      </c>
+      <c r="H100" s="25"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A101" s="30"/>
+      <c r="B101" s="31"/>
+      <c r="C101" s="30"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="7">
+        <f>D101*E101</f>
+        <v>0</v>
+      </c>
+      <c r="H101" s="25"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A102" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="B93" s="27"/>
-      <c r="C93" s="15" t="s">
+      <c r="B102" s="27"/>
+      <c r="C102" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="D93" s="9">
+      <c r="D102" s="9">
         <v>3</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E102" s="9">
         <v>2.1800000000000002</v>
       </c>
-      <c r="F93" s="7">
+      <c r="F102" s="7">
         <f t="shared" si="1"/>
         <v>6.5400000000000009</v>
       </c>
-      <c r="H93" s="26" t="s">
+      <c r="H102" s="26" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="14" t="s">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A103" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B94" s="27"/>
-      <c r="C94" s="14">
+      <c r="B103" s="27"/>
+      <c r="C103" s="14">
         <v>156665159304</v>
       </c>
-      <c r="D94" s="8">
+      <c r="D103" s="8">
         <v>3</v>
       </c>
-      <c r="E94" s="8">
+      <c r="E103" s="8">
         <v>35.97</v>
       </c>
-      <c r="F94" s="7">
+      <c r="F103" s="7">
         <f t="shared" si="1"/>
         <v>107.91</v>
       </c>
-      <c r="H94" s="25" t="s">
+      <c r="H103" s="25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="15" t="s">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A104" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B95" s="27" t="s">
+      <c r="B104" s="27" t="s">
         <v>240</v>
       </c>
-      <c r="C95" s="15" t="s">
+      <c r="C104" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="D95" s="9">
+      <c r="D104" s="9">
         <v>3</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E104" s="9">
         <v>167.42</v>
       </c>
-      <c r="F95" s="7">
+      <c r="F104" s="7">
         <f t="shared" si="1"/>
         <v>502.26</v>
       </c>
-      <c r="H95" s="24" t="s">
+      <c r="H104" s="24" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="14" t="s">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A105" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="B96" s="27" t="s">
+      <c r="B105" s="27" t="s">
         <v>249</v>
       </c>
-      <c r="C96" s="14">
+      <c r="C105" s="14">
         <v>316529</v>
       </c>
-      <c r="D96" s="8">
-        <v>1</v>
-      </c>
-      <c r="E96" s="8">
+      <c r="D105" s="8">
+        <v>1</v>
+      </c>
+      <c r="E105" s="8">
         <v>405</v>
       </c>
-      <c r="F96" s="7">
+      <c r="F105" s="7">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="H96" s="23" t="s">
+      <c r="H105" s="23" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="15" t="s">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A106" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B97" s="27" t="s">
+      <c r="B106" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="C97" s="12" t="s">
+      <c r="C106" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="D97" s="9">
-        <v>1</v>
-      </c>
-      <c r="E97" s="9">
+      <c r="D106" s="9">
+        <v>1</v>
+      </c>
+      <c r="E106" s="9">
         <v>37.4</v>
       </c>
-      <c r="F97" s="7">
+      <c r="F106" s="7">
         <f t="shared" si="1"/>
         <v>37.4</v>
       </c>
-      <c r="H97" s="24" t="s">
+      <c r="H106" s="24" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="14" t="s">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A107" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B98" s="27" t="s">
+      <c r="B107" s="27" t="s">
         <v>244</v>
       </c>
-      <c r="C98" s="13" t="s">
+      <c r="C107" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="D98" s="8">
-        <v>1</v>
-      </c>
-      <c r="E98" s="8">
+      <c r="D107" s="8">
+        <v>1</v>
+      </c>
+      <c r="E107" s="8">
         <v>20.91</v>
       </c>
-      <c r="F98" s="7">
+      <c r="F107" s="7">
         <f t="shared" si="1"/>
         <v>20.91</v>
       </c>
-      <c r="H98" s="23" t="s">
+      <c r="H107" s="23" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="15" t="s">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B99" s="27" t="s">
+      <c r="B108" s="27" t="s">
         <v>251</v>
       </c>
-      <c r="C99" s="12" t="s">
+      <c r="C108" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="D99" s="9">
-        <v>1</v>
-      </c>
-      <c r="E99" s="9">
+      <c r="D108" s="9">
+        <v>1</v>
+      </c>
+      <c r="E108" s="9">
         <v>79.099999999999994</v>
       </c>
-      <c r="F99" s="7">
+      <c r="F108" s="7">
         <f t="shared" si="1"/>
         <v>79.099999999999994</v>
       </c>
-      <c r="H99" s="24" t="s">
+      <c r="H108" s="24" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="14" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A109" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="B100" s="27" t="s">
+      <c r="B109" s="27" t="s">
         <v>246</v>
       </c>
-      <c r="C100" s="18" t="s">
+      <c r="C109" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D100" s="8">
-        <v>1</v>
-      </c>
-      <c r="E100" s="8">
+      <c r="D109" s="8">
+        <v>1</v>
+      </c>
+      <c r="E109" s="8">
         <v>16.260000000000002</v>
       </c>
-      <c r="F100" s="7">
+      <c r="F109" s="7">
         <f t="shared" si="1"/>
         <v>16.260000000000002</v>
       </c>
-      <c r="H100" s="23" t="s">
+      <c r="H109" s="23" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="28" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A110" s="28" t="s">
         <v>258</v>
       </c>
-      <c r="B101" s="27" t="s">
+      <c r="B110" s="27" t="s">
         <v>254</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C110" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="D101" s="29">
-        <v>1</v>
-      </c>
-      <c r="E101" s="29">
+      <c r="D110" s="29">
+        <v>1</v>
+      </c>
+      <c r="E110" s="29">
         <v>5.35</v>
       </c>
-      <c r="F101" s="7">
-        <f>D101*E101</f>
+      <c r="F110" s="7">
+        <f>D110*E110</f>
         <v>5.35</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H110" s="1" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="28" t="s">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A111" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="B102" s="27" t="s">
+      <c r="B111" s="27" t="s">
         <v>256</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C111" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="D102" s="29">
-        <v>1</v>
-      </c>
-      <c r="E102" s="29">
+      <c r="D111" s="29">
+        <v>1</v>
+      </c>
+      <c r="E111" s="29">
         <v>10.75</v>
       </c>
-      <c r="F102" s="7">
-        <f>D102*E102</f>
+      <c r="F111" s="7">
+        <f>D111*E111</f>
         <v>10.75</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H111" s="1" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="28" t="s">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="28" t="s">
         <v>260</v>
       </c>
-      <c r="B103" s="27" t="s">
+      <c r="B112" s="27" t="s">
         <v>263</v>
       </c>
-      <c r="C103" s="11" t="s">
+      <c r="C112" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="D103" s="29">
-        <v>1</v>
-      </c>
-      <c r="E103" s="29">
+      <c r="D112" s="29">
+        <v>1</v>
+      </c>
+      <c r="E112" s="29">
         <v>6.68</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F112" s="7">
         <v>7.96</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H112" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="11"/>
-      <c r="B104" s="11"/>
-      <c r="C104" s="11"/>
-      <c r="H104" s="11"/>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F106" s="6">
-        <f>SUM(F2:F103)</f>
-        <v>9534.5600000000031</v>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="11"/>
+      <c r="B113" s="11"/>
+      <c r="C113" s="11"/>
+      <c r="H113" s="11"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="F115" s="6">
+        <f>SUM(F2:F112)</f>
+        <v>9666.5800000000017</v>
       </c>
     </row>
   </sheetData>
@@ -4145,20 +4339,22 @@
     <hyperlink ref="H89" r:id="rId86" display="https://www.grainger.com/product/1VFX8?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=6d4e1d7881c4014dc580a65ce33a0287e6d4e842f558a81fadd5dcde7a752909&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{460DB0C6-014B-408D-A50E-7C7CB6F31C51}"/>
     <hyperlink ref="H90" r:id="rId87" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{B046FF95-BF93-46C9-B8CE-FB723F36F53A}"/>
     <hyperlink ref="H91" r:id="rId88" display="https://www.grainger.com/product/Hex-Tap-Bolt-Stainless-Steel-41UH04?gucid=n:n:em:owned:wwg:deliveryConfirmation:apz_1&amp;emcid=body:pdpurl" xr:uid="{5ACA225F-14EA-4C12-8992-27C2A205D0A2}"/>
-    <hyperlink ref="H96" r:id="rId89" xr:uid="{66B68E33-6FB6-4B9E-8DEE-AD4543BA3948}"/>
-    <hyperlink ref="H95" r:id="rId90" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{E0383BBC-B224-42C5-8E0D-F57DE49C5FA3}"/>
-    <hyperlink ref="H97" r:id="rId91" xr:uid="{A3D63FAB-C850-40A1-A637-DF41091272C8}"/>
-    <hyperlink ref="H98" r:id="rId92" display="https://www.grainger.com/product/20XM58?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=5fbed57f928e0d20c3753de78a2b9a38ffd20234e126526a2f6d6b4fe4e772db&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C07356E-8DE4-40F2-A1AD-4E8492786388}"/>
-    <hyperlink ref="H99" r:id="rId93" xr:uid="{94CC04D7-EB9A-450B-BB5C-C756BC4DE898}"/>
-    <hyperlink ref="H100" r:id="rId94" display="https://www.grainger.com/product/IGUS-Flanged-Sleeve-Bearing-Polymer-2NCK6" xr:uid="{83384CCF-7FBA-4E7B-9A1D-1C877A885273}"/>
-    <hyperlink ref="H101" r:id="rId95" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
-    <hyperlink ref="H102" r:id="rId96" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
-    <hyperlink ref="H103" r:id="rId97" xr:uid="{FDEFAFD3-3687-4641-964A-8BC9B3E42512}"/>
+    <hyperlink ref="H105" r:id="rId89" xr:uid="{66B68E33-6FB6-4B9E-8DEE-AD4543BA3948}"/>
+    <hyperlink ref="H104" r:id="rId90" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{E0383BBC-B224-42C5-8E0D-F57DE49C5FA3}"/>
+    <hyperlink ref="H106" r:id="rId91" xr:uid="{A3D63FAB-C850-40A1-A637-DF41091272C8}"/>
+    <hyperlink ref="H107" r:id="rId92" display="https://www.grainger.com/product/20XM58?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=5fbed57f928e0d20c3753de78a2b9a38ffd20234e126526a2f6d6b4fe4e772db&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C07356E-8DE4-40F2-A1AD-4E8492786388}"/>
+    <hyperlink ref="H108" r:id="rId93" xr:uid="{94CC04D7-EB9A-450B-BB5C-C756BC4DE898}"/>
+    <hyperlink ref="H109" r:id="rId94" display="https://www.grainger.com/product/IGUS-Flanged-Sleeve-Bearing-Polymer-2NCK6" xr:uid="{83384CCF-7FBA-4E7B-9A1D-1C877A885273}"/>
+    <hyperlink ref="H110" r:id="rId95" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
+    <hyperlink ref="H111" r:id="rId96" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
+    <hyperlink ref="H112" r:id="rId97" xr:uid="{FDEFAFD3-3687-4641-964A-8BC9B3E42512}"/>
+    <hyperlink ref="H95" r:id="rId98" xr:uid="{29622D1D-FB83-4317-A033-D7DD9D94A271}"/>
+    <hyperlink ref="H94" r:id="rId99" xr:uid="{5FC8DB1C-6249-4551-B238-6394EA039EB9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId98"/>
+  <pageSetup orientation="portrait" r:id="rId100"/>
   <tableParts count="1">
-    <tablePart r:id="rId99"/>
+    <tablePart r:id="rId101"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9767054-3909-4284-9249-BF43A556FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{F9767054-3909-4284-9249-BF43A556FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB46BDF3-3269-411F-B3BC-B7712C5D24DE}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="288">
   <si>
     <t>Total Cost</t>
   </si>
@@ -864,6 +864,42 @@
   </si>
   <si>
     <t>F3U133B16</t>
+  </si>
+  <si>
+    <t>Water Filter (TO ORDER)</t>
+  </si>
+  <si>
+    <t>BANJO Inline Strainer: Polypropylene, 3/4 in, NPT, Mesh, 0.007 in Screen Size, 4 1/4 in Ht, 3 in Lg</t>
+  </si>
+  <si>
+    <t>3ELX2</t>
+  </si>
+  <si>
+    <t>BANJO, Polypropylene, 3/4 in, Inline Strainer - 3ELX2|LSTM075-80C - Grainger</t>
+  </si>
+  <si>
+    <t>Pressure Reducer Valve (TO ORDER)</t>
+  </si>
+  <si>
+    <t>BELL &amp; GOSSETT, NPT x NPT, 3/4 in Pipe Size, Water Pressure Reducing Valve - 6LFA3|110196LF - Grainger</t>
+  </si>
+  <si>
+    <t>6LFA3</t>
+  </si>
+  <si>
+    <t>BELL &amp; GOSSETT Water Pressure Reducing Valve: NPT x NPT, 3/4 in Pipe Size, Brass, 10 psi to 25 psi</t>
+  </si>
+  <si>
+    <t>APOLLO Relief Valve: FNPT x FNPT, 3/4 in x 3/4 in, Bronze, 94 psi Max. Op Pressure</t>
+  </si>
+  <si>
+    <t>Pressure Relief Valve (TO ORDER)</t>
+  </si>
+  <si>
+    <t>804Z55</t>
+  </si>
+  <si>
+    <t>https://www.grainger.com/product/APOLLO-Relief-Valve-FNPT-x-FNPT-804Z55</t>
   </si>
 </sst>
 </file>
@@ -1006,7 +1042,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1021,7 +1057,6 @@
     <xf numFmtId="7" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1091,13 +1126,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1212,8 +1263,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K112" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K112" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K122" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K122" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1550,2638 +1601,2638 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M115"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M122"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="1" max="1" width="39" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.42578125" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" customWidth="1"/>
-    <col min="12" max="12" width="55.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.6640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="J1" s="10" t="s">
+      <c r="J1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="10" t="s">
+      <c r="K1" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="26" t="s">
         <v>247</v>
       </c>
-      <c r="C2" s="14">
+      <c r="C2" s="13">
         <v>92012988</v>
       </c>
-      <c r="D2" s="8">
-        <v>1</v>
-      </c>
-      <c r="E2" s="8">
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
+      <c r="E2" s="7">
         <v>25.58</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="6">
         <f>D2*E2</f>
         <v>25.58</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="23" t="s">
+      <c r="H2" s="22" t="s">
         <v>155</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="15">
+      <c r="C3" s="14">
         <v>67436964</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="8">
         <v>10</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="8">
         <v>1.71</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="6">
         <f t="shared" ref="F3:F66" si="0">D3*E3</f>
         <v>17.100000000000001</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="24" t="s">
+      <c r="H3" s="23" t="s">
         <v>156</v>
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="16">
+      <c r="C4" s="15">
         <v>67473967</v>
       </c>
-      <c r="D4" s="8">
+      <c r="D4" s="7">
         <v>10</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>0.47</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="6">
         <f t="shared" si="0"/>
         <v>4.6999999999999993</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="23" t="s">
+      <c r="H4" s="22" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="16">
         <v>99176795</v>
       </c>
-      <c r="D5" s="9">
+      <c r="D5" s="8">
         <v>6</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="8">
         <v>5.45</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="6">
         <f t="shared" si="0"/>
         <v>32.700000000000003</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="24" t="s">
+      <c r="H5" s="23" t="s">
         <v>158</v>
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="D6" s="8">
+      <c r="D6" s="7">
         <v>3</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>25.94</v>
       </c>
-      <c r="F6" s="7">
+      <c r="F6" s="6">
         <f t="shared" si="0"/>
         <v>77.820000000000007</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="23" t="s">
+      <c r="H6" s="22" t="s">
         <v>159</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="D7" s="9">
+      <c r="D7" s="8">
         <v>3</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="8">
         <v>10.41</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="6">
         <f t="shared" si="0"/>
         <v>31.23</v>
       </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="24" t="s">
+      <c r="H7" s="23" t="s">
         <v>160</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>74</v>
       </c>
-      <c r="D8" s="8">
-        <v>1</v>
-      </c>
-      <c r="E8" s="8">
+      <c r="D8" s="7">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7">
         <v>93.93</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="6">
         <f t="shared" si="0"/>
         <v>93.93</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="23" t="s">
+      <c r="H8" s="22" t="s">
         <v>161</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="26" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="9">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="D9" s="8">
+        <v>1</v>
+      </c>
+      <c r="E9" s="8">
         <v>5.99</v>
       </c>
-      <c r="F9" s="7">
+      <c r="F9" s="6">
         <f t="shared" si="0"/>
         <v>5.99</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="24" t="s">
+      <c r="H9" s="23" t="s">
         <v>162</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="26" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="D10" s="8">
-        <v>1</v>
-      </c>
-      <c r="E10" s="8">
+      <c r="D10" s="7">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7">
         <v>41.22</v>
       </c>
-      <c r="F10" s="7">
+      <c r="F10" s="6">
         <f t="shared" si="0"/>
         <v>41.22</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="23" t="s">
+      <c r="H10" s="22" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="D11" s="9">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="D11" s="8">
+        <v>1</v>
+      </c>
+      <c r="E11" s="8">
         <v>60.89</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="6">
         <f t="shared" si="0"/>
         <v>60.89</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="23" t="s">
         <v>164</v>
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="14" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="8">
-        <v>1</v>
-      </c>
-      <c r="E12" s="8">
+      <c r="D12" s="7">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7">
         <v>27.83</v>
       </c>
-      <c r="F12" s="7">
+      <c r="F12" s="6">
         <f t="shared" si="0"/>
         <v>27.83</v>
       </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="25" t="s">
+      <c r="H12" s="24" t="s">
         <v>78</v>
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="20">
+      <c r="C13" s="19">
         <v>316533</v>
       </c>
-      <c r="D13" s="9">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9">
+      <c r="D13" s="8">
+        <v>1</v>
+      </c>
+      <c r="E13" s="8">
         <v>370</v>
       </c>
-      <c r="F13" s="7">
+      <c r="F13" s="6">
         <f t="shared" si="0"/>
         <v>370</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="24" t="s">
+      <c r="H13" s="23" t="s">
         <v>165</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="18">
+      <c r="C14" s="17">
         <v>316530</v>
       </c>
-      <c r="D14" s="8">
-        <v>1</v>
-      </c>
-      <c r="E14" s="8">
+      <c r="D14" s="7">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7">
         <v>312</v>
       </c>
-      <c r="F14" s="7">
+      <c r="F14" s="6">
         <f t="shared" si="0"/>
         <v>312</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="23" t="s">
+      <c r="H14" s="22" t="s">
         <v>166</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="20">
+      <c r="C15" s="19">
         <v>314802</v>
       </c>
-      <c r="D15" s="9">
-        <v>1</v>
-      </c>
-      <c r="E15" s="9">
+      <c r="D15" s="8">
+        <v>1</v>
+      </c>
+      <c r="E15" s="8">
         <v>5.9</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="6">
         <f t="shared" si="0"/>
         <v>5.9</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="24" t="s">
+      <c r="H15" s="23" t="s">
         <v>167</v>
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="27" t="s">
+      <c r="B16" s="26" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>164598</v>
       </c>
-      <c r="D16" s="8">
-        <v>1</v>
-      </c>
-      <c r="E16" s="8">
+      <c r="D16" s="7">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7">
         <v>1610</v>
       </c>
-      <c r="F16" s="7">
+      <c r="F16" s="6">
         <f t="shared" si="0"/>
         <v>1610</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="23" t="s">
+      <c r="H16" s="22" t="s">
         <v>168</v>
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="26" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D17" s="8">
         <v>25</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="8">
         <v>3.97</v>
       </c>
-      <c r="F17" s="7">
+      <c r="F17" s="6">
         <f t="shared" si="0"/>
         <v>99.25</v>
       </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="24" t="s">
+      <c r="H17" s="23" t="s">
         <v>169</v>
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="27"/>
-      <c r="C18" s="14" t="s">
+      <c r="B18" s="26"/>
+      <c r="C18" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="D18" s="8">
-        <v>1</v>
-      </c>
-      <c r="E18" s="8">
+      <c r="D18" s="7">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7">
         <v>839.97</v>
       </c>
-      <c r="F18" s="7">
+      <c r="F18" s="6">
         <f t="shared" si="0"/>
         <v>839.97</v>
       </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="25" t="s">
+      <c r="H18" s="24" t="s">
         <v>78</v>
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D19" s="8">
         <v>2</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="8">
         <v>14.02</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="6">
         <f t="shared" si="0"/>
         <v>28.04</v>
       </c>
       <c r="G19" s="5"/>
-      <c r="H19" s="24" t="s">
+      <c r="H19" s="23" t="s">
         <v>170</v>
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="8">
-        <v>1</v>
-      </c>
-      <c r="E20" s="8">
+      <c r="D20" s="7">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7">
         <v>33.58</v>
       </c>
-      <c r="F20" s="7">
+      <c r="F20" s="6">
         <f t="shared" si="0"/>
         <v>33.58</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="23" t="s">
+      <c r="H20" s="22" t="s">
         <v>171</v>
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D21" s="9">
+      <c r="D21" s="8">
         <v>250</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="8">
         <v>0.12664</v>
       </c>
-      <c r="F21" s="7">
+      <c r="F21" s="6">
         <f t="shared" si="0"/>
         <v>31.66</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="24" t="s">
+      <c r="H21" s="23" t="s">
         <v>172</v>
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="8">
-        <v>1</v>
-      </c>
-      <c r="E22" s="8">
+      <c r="D22" s="7">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7">
         <v>59</v>
       </c>
-      <c r="F22" s="7">
+      <c r="F22" s="6">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="23" t="s">
+      <c r="H22" s="22" t="s">
         <v>173</v>
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="26" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="15">
+      <c r="C23" s="14">
         <v>7568365</v>
       </c>
-      <c r="D23" s="9">
+      <c r="D23" s="8">
         <v>2</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="8">
         <v>341.13</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="6">
         <f t="shared" si="0"/>
         <v>682.26</v>
       </c>
       <c r="G23" s="5"/>
-      <c r="H23" s="24" t="s">
+      <c r="H23" s="23" t="s">
         <v>174</v>
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="26" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="14">
+      <c r="C24" s="13">
         <v>8323512</v>
       </c>
-      <c r="D24" s="8">
+      <c r="D24" s="7">
         <v>2</v>
       </c>
-      <c r="E24" s="8">
+      <c r="E24" s="7">
         <v>108.02</v>
       </c>
-      <c r="F24" s="7">
+      <c r="F24" s="6">
         <f t="shared" si="0"/>
         <v>216.04</v>
       </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="23" t="s">
+      <c r="H24" s="22" t="s">
         <v>175</v>
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="9">
+      <c r="D25" s="8">
         <v>5</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="8">
         <v>59</v>
       </c>
-      <c r="F25" s="7">
+      <c r="F25" s="6">
         <f t="shared" si="0"/>
         <v>295</v>
       </c>
       <c r="G25" s="2"/>
-      <c r="H25" s="24" t="s">
+      <c r="H25" s="23" t="s">
         <v>173</v>
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="8">
+      <c r="D26" s="7">
         <v>4</v>
       </c>
-      <c r="E26" s="8">
+      <c r="E26" s="7">
         <v>20.99</v>
       </c>
-      <c r="F26" s="7">
+      <c r="F26" s="6">
         <f t="shared" si="0"/>
         <v>83.96</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="22" t="s">
         <v>176</v>
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="27" t="s">
+      <c r="B27" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D27" s="9">
+      <c r="D27" s="8">
         <v>4</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="8">
         <v>7.46</v>
       </c>
-      <c r="F27" s="7">
+      <c r="F27" s="6">
         <f t="shared" si="0"/>
         <v>29.84</v>
       </c>
       <c r="G27" s="2"/>
-      <c r="H27" s="24" t="s">
+      <c r="H27" s="23" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="D28" s="8">
+      <c r="D28" s="7">
         <v>4</v>
       </c>
-      <c r="E28" s="8">
+      <c r="E28" s="7">
         <v>13.23</v>
       </c>
-      <c r="F28" s="7">
+      <c r="F28" s="6">
         <f t="shared" si="0"/>
         <v>52.92</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="22" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="9">
+      <c r="D29" s="8">
         <v>4</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="8">
         <v>12.78</v>
       </c>
-      <c r="F29" s="7">
+      <c r="F29" s="6">
         <f t="shared" si="0"/>
         <v>51.12</v>
       </c>
-      <c r="H29" s="24" t="s">
+      <c r="H29" s="23" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="27" t="s">
+      <c r="B30" s="26" t="s">
         <v>180</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="D30" s="8">
+      <c r="D30" s="7">
         <v>4</v>
       </c>
-      <c r="E30" s="8">
+      <c r="E30" s="7">
         <v>9.99</v>
       </c>
-      <c r="F30" s="7">
+      <c r="F30" s="6">
         <f t="shared" si="0"/>
         <v>39.96</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="22" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="27" t="s">
+      <c r="B31" s="26" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="9">
+      <c r="D31" s="8">
         <v>4</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="8">
         <v>22.34</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="6">
         <f t="shared" si="0"/>
         <v>89.36</v>
       </c>
-      <c r="H31" s="24" t="s">
+      <c r="H31" s="23" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="27" t="s">
+      <c r="B32" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="8">
+      <c r="D32" s="7">
         <v>4</v>
       </c>
-      <c r="E32" s="8">
+      <c r="E32" s="7">
         <v>16.89</v>
       </c>
-      <c r="F32" s="7">
+      <c r="F32" s="6">
         <f t="shared" si="0"/>
         <v>67.56</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="22" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="27" t="s">
+      <c r="B33" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="D33" s="9">
+      <c r="D33" s="8">
         <v>2</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="8">
         <v>21.79</v>
       </c>
-      <c r="F33" s="7">
+      <c r="F33" s="6">
         <f t="shared" si="0"/>
         <v>43.58</v>
       </c>
-      <c r="H33" s="24" t="s">
+      <c r="H33" s="23" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="27" t="s">
+      <c r="B34" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="17" t="s">
         <v>93</v>
       </c>
-      <c r="D34" s="8">
+      <c r="D34" s="7">
         <v>2</v>
       </c>
-      <c r="E34" s="8">
+      <c r="E34" s="7">
         <v>19.86</v>
       </c>
-      <c r="F34" s="7">
+      <c r="F34" s="6">
         <f t="shared" si="0"/>
         <v>39.72</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="22" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="27" t="s">
+      <c r="B35" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="D35" s="9">
-        <v>1</v>
-      </c>
-      <c r="E35" s="9">
+      <c r="D35" s="8">
+        <v>1</v>
+      </c>
+      <c r="E35" s="8">
         <v>36.979999999999997</v>
       </c>
-      <c r="F35" s="7">
+      <c r="F35" s="6">
         <f t="shared" si="0"/>
         <v>36.979999999999997</v>
       </c>
-      <c r="H35" s="24" t="s">
+      <c r="H35" s="23" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="27" t="s">
+      <c r="B36" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="8">
-        <v>1</v>
-      </c>
-      <c r="E36" s="8">
+      <c r="D36" s="7">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7">
         <v>26.2</v>
       </c>
-      <c r="F36" s="7">
+      <c r="F36" s="6">
         <f t="shared" si="0"/>
         <v>26.2</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="H36" s="22" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A37" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="B37" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="18" t="s">
         <v>96</v>
       </c>
-      <c r="D37" s="9">
+      <c r="D37" s="8">
         <v>4</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="8">
         <v>19.22</v>
       </c>
-      <c r="F37" s="7">
+      <c r="F37" s="6">
         <f t="shared" si="0"/>
         <v>76.88</v>
       </c>
-      <c r="H37" s="24" t="s">
+      <c r="H37" s="23" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="B38" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>97</v>
       </c>
-      <c r="D38" s="8">
+      <c r="D38" s="7">
         <v>6</v>
       </c>
-      <c r="E38" s="8">
+      <c r="E38" s="7">
         <v>2.48</v>
       </c>
-      <c r="F38" s="7">
+      <c r="F38" s="6">
         <f t="shared" si="0"/>
         <v>14.879999999999999</v>
       </c>
-      <c r="H38" s="23" t="s">
+      <c r="H38" s="22" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A39" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="27" t="s">
+      <c r="B39" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="18" t="s">
         <v>98</v>
       </c>
-      <c r="D39" s="9">
+      <c r="D39" s="8">
         <v>6</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="8">
         <v>3.21</v>
       </c>
-      <c r="F39" s="7">
+      <c r="F39" s="6">
         <f t="shared" si="0"/>
         <v>19.259999999999998</v>
       </c>
-      <c r="H39" s="24" t="s">
+      <c r="H39" s="23" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="27" t="s">
+      <c r="B40" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="D40" s="8">
-        <v>1</v>
-      </c>
-      <c r="E40" s="8">
+      <c r="D40" s="7">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7">
         <v>16.010000000000002</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="6">
         <f t="shared" si="0"/>
         <v>16.010000000000002</v>
       </c>
-      <c r="H40" s="23" t="s">
+      <c r="H40" s="22" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A41" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="27" t="s">
+      <c r="B41" s="26" t="s">
         <v>248</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="D41" s="9">
+      <c r="D41" s="8">
         <v>3</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="8">
         <v>7.55</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="6">
         <f t="shared" si="0"/>
         <v>22.65</v>
       </c>
-      <c r="H41" s="24" t="s">
+      <c r="H41" s="23" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="27" t="s">
+      <c r="B42" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="D42" s="8">
+      <c r="D42" s="7">
         <v>12</v>
       </c>
-      <c r="E42" s="8">
+      <c r="E42" s="7">
         <v>3.55</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="6">
         <f t="shared" si="0"/>
         <v>42.599999999999994</v>
       </c>
-      <c r="H42" s="23" t="s">
+      <c r="H42" s="22" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A43" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="27" t="s">
+      <c r="B43" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="D43" s="9">
-        <v>1</v>
-      </c>
-      <c r="E43" s="9">
+      <c r="D43" s="8">
+        <v>1</v>
+      </c>
+      <c r="E43" s="8">
         <v>50.51</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="6">
         <f t="shared" si="0"/>
         <v>50.51</v>
       </c>
-      <c r="H43" s="24" t="s">
+      <c r="H43" s="23" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="27" t="s">
+      <c r="B44" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="D44" s="8">
-        <v>1</v>
-      </c>
-      <c r="E44" s="8">
+      <c r="D44" s="7">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7">
         <v>24.17</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="6">
         <f t="shared" si="0"/>
         <v>24.17</v>
       </c>
-      <c r="H44" s="23" t="s">
+      <c r="H44" s="22" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A45" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="27" t="s">
+      <c r="B45" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="18" t="s">
         <v>104</v>
       </c>
-      <c r="D45" s="9">
-        <v>1</v>
-      </c>
-      <c r="E45" s="9">
+      <c r="D45" s="8">
+        <v>1</v>
+      </c>
+      <c r="E45" s="8">
         <v>26.01</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="6">
         <f t="shared" si="0"/>
         <v>26.01</v>
       </c>
-      <c r="H45" s="24" t="s">
+      <c r="H45" s="23" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="27" t="s">
+      <c r="B46" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="8">
-        <v>1</v>
-      </c>
-      <c r="E46" s="8">
+      <c r="D46" s="7">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7">
         <v>16.82</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="6">
         <f t="shared" si="0"/>
         <v>16.82</v>
       </c>
-      <c r="H46" s="23" t="s">
+      <c r="H46" s="22" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A47" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="27" t="s">
+      <c r="B47" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="18" t="s">
         <v>106</v>
       </c>
-      <c r="D47" s="9">
+      <c r="D47" s="8">
         <v>2</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="8">
         <v>25.17</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="6">
         <f t="shared" si="0"/>
         <v>50.34</v>
       </c>
-      <c r="H47" s="24" t="s">
+      <c r="H47" s="23" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="27" t="s">
+      <c r="B48" s="26" t="s">
         <v>198</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="17" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="8">
+      <c r="D48" s="7">
         <v>2</v>
       </c>
-      <c r="E48" s="8">
+      <c r="E48" s="7">
         <v>12.5</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="6">
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="H48" s="23" t="s">
+      <c r="H48" s="22" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A49" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="27" t="s">
+      <c r="B49" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="18" t="s">
         <v>108</v>
       </c>
-      <c r="D49" s="9">
-        <v>1</v>
-      </c>
-      <c r="E49" s="9">
+      <c r="D49" s="8">
+        <v>1</v>
+      </c>
+      <c r="E49" s="8">
         <v>28.56</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="6">
         <f t="shared" si="0"/>
         <v>28.56</v>
       </c>
-      <c r="H49" s="24" t="s">
+      <c r="H49" s="23" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A50" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="27" t="s">
+      <c r="B50" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="17" t="s">
         <v>109</v>
       </c>
-      <c r="D50" s="8">
+      <c r="D50" s="7">
         <v>5</v>
       </c>
-      <c r="E50" s="8">
+      <c r="E50" s="7">
         <v>3.35</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="6">
         <f t="shared" si="0"/>
         <v>16.75</v>
       </c>
-      <c r="H50" s="23" t="s">
+      <c r="H50" s="22" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="15" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A51" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="27" t="s">
+      <c r="B51" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="18" t="s">
         <v>110</v>
       </c>
-      <c r="D51" s="9">
-        <v>1</v>
-      </c>
-      <c r="E51" s="9">
+      <c r="D51" s="8">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8">
         <v>14.81</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="6">
         <f t="shared" si="0"/>
         <v>14.81</v>
       </c>
-      <c r="H51" s="24" t="s">
+      <c r="H51" s="23" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A52" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="27" t="s">
+      <c r="B52" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="17" t="s">
         <v>111</v>
       </c>
-      <c r="D52" s="8">
-        <v>1</v>
-      </c>
-      <c r="E52" s="8">
+      <c r="D52" s="7">
+        <v>1</v>
+      </c>
+      <c r="E52" s="7">
         <v>19.989999999999998</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="6">
         <f t="shared" si="0"/>
         <v>19.989999999999998</v>
       </c>
-      <c r="H52" s="23" t="s">
+      <c r="H52" s="22" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="15" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A53" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="27" t="s">
+      <c r="B53" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="18" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="9">
+      <c r="D53" s="8">
         <v>5</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="8">
         <v>5.36</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="6">
         <f t="shared" si="0"/>
         <v>26.8</v>
       </c>
-      <c r="H53" s="24" t="s">
+      <c r="H53" s="23" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="27" t="s">
+      <c r="B54" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="17" t="s">
         <v>113</v>
       </c>
-      <c r="D54" s="8">
-        <v>1</v>
-      </c>
-      <c r="E54" s="8">
+      <c r="D54" s="7">
+        <v>1</v>
+      </c>
+      <c r="E54" s="7">
         <v>40.14</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="6">
         <f t="shared" si="0"/>
         <v>40.14</v>
       </c>
-      <c r="H54" s="23" t="s">
+      <c r="H54" s="22" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="15" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A55" s="14" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="27" t="s">
+      <c r="B55" s="26" t="s">
         <v>205</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="C55" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D55" s="9">
-        <v>1</v>
-      </c>
-      <c r="E55" s="9">
+      <c r="D55" s="8">
+        <v>1</v>
+      </c>
+      <c r="E55" s="8">
         <v>300</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55" s="6">
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="H55" s="24" t="s">
+      <c r="H55" s="23" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A56" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="27" t="s">
+      <c r="B56" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="17" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="8">
+      <c r="D56" s="7">
         <v>6</v>
       </c>
-      <c r="E56" s="8">
+      <c r="E56" s="7">
         <v>11.53</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="6">
         <f t="shared" si="0"/>
         <v>69.179999999999993</v>
       </c>
-      <c r="H56" s="23" t="s">
+      <c r="H56" s="22" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A57" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="27" t="s">
+      <c r="B57" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="18" t="s">
         <v>115</v>
       </c>
-      <c r="D57" s="9">
+      <c r="D57" s="8">
         <v>2</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="8">
         <v>4.75</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="6">
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="H57" s="24" t="s">
+      <c r="H57" s="23" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="27" t="s">
+      <c r="B58" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="17" t="s">
         <v>116</v>
       </c>
-      <c r="D58" s="8">
-        <v>1</v>
-      </c>
-      <c r="E58" s="8">
+      <c r="D58" s="7">
+        <v>1</v>
+      </c>
+      <c r="E58" s="7">
         <v>5.41</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="6">
         <f t="shared" si="0"/>
         <v>5.41</v>
       </c>
-      <c r="H58" s="23" t="s">
+      <c r="H58" s="22" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A59" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="18" t="s">
         <v>117</v>
       </c>
-      <c r="D59" s="9">
-        <v>1</v>
-      </c>
-      <c r="E59" s="9">
+      <c r="D59" s="8">
+        <v>1</v>
+      </c>
+      <c r="E59" s="8">
         <v>9.0299999999999994</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="6">
         <f t="shared" si="0"/>
         <v>9.0299999999999994</v>
       </c>
-      <c r="H59" s="24" t="s">
+      <c r="H59" s="23" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A60" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="27" t="s">
+      <c r="B60" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="D60" s="8">
-        <v>1</v>
-      </c>
-      <c r="E60" s="8">
+      <c r="D60" s="7">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7">
         <v>16.87</v>
       </c>
-      <c r="F60" s="7">
+      <c r="F60" s="6">
         <f t="shared" si="0"/>
         <v>16.87</v>
       </c>
-      <c r="H60" s="23" t="s">
+      <c r="H60" s="22" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="15" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A61" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B61" s="27" t="s">
+      <c r="B61" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="D61" s="9">
-        <v>1</v>
-      </c>
-      <c r="E61" s="9">
+      <c r="D61" s="8">
+        <v>1</v>
+      </c>
+      <c r="E61" s="8">
         <v>14.02</v>
       </c>
-      <c r="F61" s="7">
+      <c r="F61" s="6">
         <f t="shared" si="0"/>
         <v>14.02</v>
       </c>
-      <c r="H61" s="24" t="s">
+      <c r="H61" s="23" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A62" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B62" s="27" t="s">
+      <c r="B62" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="17" t="s">
         <v>120</v>
       </c>
-      <c r="D62" s="8">
-        <v>1</v>
-      </c>
-      <c r="E62" s="8">
+      <c r="D62" s="7">
+        <v>1</v>
+      </c>
+      <c r="E62" s="7">
         <v>8.83</v>
       </c>
-      <c r="F62" s="7">
+      <c r="F62" s="6">
         <f t="shared" si="0"/>
         <v>8.83</v>
       </c>
-      <c r="H62" s="23" t="s">
+      <c r="H62" s="22" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A63" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="B63" s="27" t="s">
+      <c r="B63" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D63" s="9">
-        <v>1</v>
-      </c>
-      <c r="E63" s="9">
+      <c r="D63" s="8">
+        <v>1</v>
+      </c>
+      <c r="E63" s="8">
         <v>7.19</v>
       </c>
-      <c r="F63" s="7">
+      <c r="F63" s="6">
         <f t="shared" si="0"/>
         <v>7.19</v>
       </c>
-      <c r="H63" s="24" t="s">
+      <c r="H63" s="23" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A64" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="27" t="s">
+      <c r="B64" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="D64" s="8">
+      <c r="D64" s="7">
         <v>4</v>
       </c>
-      <c r="E64" s="8">
+      <c r="E64" s="7">
         <v>2.76</v>
       </c>
-      <c r="F64" s="7">
+      <c r="F64" s="6">
         <f t="shared" si="0"/>
         <v>11.04</v>
       </c>
-      <c r="H64" s="23" t="s">
+      <c r="H64" s="22" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="15" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A65" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="27" t="s">
+      <c r="B65" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="D65" s="9">
+      <c r="D65" s="8">
         <v>2</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="8">
         <v>3.49</v>
       </c>
-      <c r="F65" s="7">
+      <c r="F65" s="6">
         <f t="shared" si="0"/>
         <v>6.98</v>
       </c>
-      <c r="H65" s="24" t="s">
+      <c r="H65" s="23" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A66" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B66" s="27" t="s">
+      <c r="B66" s="26" t="s">
         <v>216</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="17" t="s">
         <v>124</v>
       </c>
-      <c r="D66" s="8">
-        <v>1</v>
-      </c>
-      <c r="E66" s="8">
+      <c r="D66" s="7">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7">
         <v>42.76</v>
       </c>
-      <c r="F66" s="7">
+      <c r="F66" s="6">
         <f t="shared" si="0"/>
         <v>42.76</v>
       </c>
-      <c r="H66" s="23" t="s">
+      <c r="H66" s="22" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A67" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="B67" s="27" t="s">
+      <c r="B67" s="26" t="s">
         <v>217</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="D67" s="9">
-        <v>1</v>
-      </c>
-      <c r="E67" s="9">
+      <c r="D67" s="8">
+        <v>1</v>
+      </c>
+      <c r="E67" s="8">
         <v>45.81</v>
       </c>
-      <c r="F67" s="7">
+      <c r="F67" s="6">
         <f t="shared" ref="F67:F109" si="1">D67*E67</f>
         <v>45.81</v>
       </c>
-      <c r="H67" s="24" t="s">
+      <c r="H67" s="23" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A68" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="27" t="s">
+      <c r="B68" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="C68" s="18" t="s">
+      <c r="C68" s="17" t="s">
         <v>126</v>
       </c>
-      <c r="D68" s="8">
-        <v>1</v>
-      </c>
-      <c r="E68" s="8">
+      <c r="D68" s="7">
+        <v>1</v>
+      </c>
+      <c r="E68" s="7">
         <v>18.73</v>
       </c>
-      <c r="F68" s="7">
+      <c r="F68" s="6">
         <f t="shared" si="1"/>
         <v>18.73</v>
       </c>
-      <c r="H68" s="23" t="s">
+      <c r="H68" s="22" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="15" t="s">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A69" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="B69" s="27" t="s">
+      <c r="B69" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="D69" s="9">
-        <v>1</v>
-      </c>
-      <c r="E69" s="9">
+      <c r="D69" s="8">
+        <v>1</v>
+      </c>
+      <c r="E69" s="8">
         <v>4.99</v>
       </c>
-      <c r="F69" s="7">
+      <c r="F69" s="6">
         <f t="shared" si="1"/>
         <v>4.99</v>
       </c>
-      <c r="H69" s="24" t="s">
+      <c r="H69" s="23" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A70" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B70" s="27" t="s">
+      <c r="B70" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="C70" s="18" t="s">
+      <c r="C70" s="17" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="8">
-        <v>1</v>
-      </c>
-      <c r="E70" s="8">
+      <c r="D70" s="7">
+        <v>1</v>
+      </c>
+      <c r="E70" s="7">
         <v>4.68</v>
       </c>
-      <c r="F70" s="7">
+      <c r="F70" s="6">
         <f t="shared" si="1"/>
         <v>4.68</v>
       </c>
-      <c r="H70" s="23" t="s">
+      <c r="H70" s="22" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="15" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A71" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="B71" s="27" t="s">
+      <c r="B71" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="C71" s="18" t="s">
         <v>129</v>
       </c>
-      <c r="D71" s="9">
-        <v>1</v>
-      </c>
-      <c r="E71" s="9">
+      <c r="D71" s="8">
+        <v>1</v>
+      </c>
+      <c r="E71" s="8">
         <v>39.72</v>
       </c>
-      <c r="F71" s="7">
+      <c r="F71" s="6">
         <f t="shared" si="1"/>
         <v>39.72</v>
       </c>
-      <c r="H71" s="24" t="s">
+      <c r="H71" s="23" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="14" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A72" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B72" s="27" t="s">
+      <c r="B72" s="26" t="s">
         <v>222</v>
       </c>
-      <c r="C72" s="18" t="s">
+      <c r="C72" s="17" t="s">
         <v>130</v>
       </c>
-      <c r="D72" s="8">
-        <v>1</v>
-      </c>
-      <c r="E72" s="8">
+      <c r="D72" s="7">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7">
         <v>15.07</v>
       </c>
-      <c r="F72" s="7">
+      <c r="F72" s="6">
         <f t="shared" si="1"/>
         <v>15.07</v>
       </c>
-      <c r="H72" s="23" t="s">
+      <c r="H72" s="22" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A73" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="26" t="s">
         <v>223</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="D73" s="9">
-        <v>1</v>
-      </c>
-      <c r="E73" s="9">
+      <c r="D73" s="8">
+        <v>1</v>
+      </c>
+      <c r="E73" s="8">
         <v>45.58</v>
       </c>
-      <c r="F73" s="7">
+      <c r="F73" s="6">
         <f t="shared" si="1"/>
         <v>45.58</v>
       </c>
-      <c r="H73" s="24" t="s">
+      <c r="H73" s="23" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="14" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A74" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="B74" s="27" t="s">
+      <c r="B74" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="C74" s="18" t="s">
+      <c r="C74" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D74" s="8">
-        <v>1</v>
-      </c>
-      <c r="E74" s="8">
+      <c r="D74" s="7">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7">
         <v>6.43</v>
       </c>
-      <c r="F74" s="7">
+      <c r="F74" s="6">
         <f t="shared" si="1"/>
         <v>6.43</v>
       </c>
-      <c r="H74" s="23" t="s">
+      <c r="H74" s="22" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="15" t="s">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A75" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="27" t="s">
+      <c r="B75" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="D75" s="9">
-        <v>1</v>
-      </c>
-      <c r="E75" s="9">
+      <c r="D75" s="8">
+        <v>1</v>
+      </c>
+      <c r="E75" s="8">
         <v>26.5</v>
       </c>
-      <c r="F75" s="7">
+      <c r="F75" s="6">
         <f t="shared" si="1"/>
         <v>26.5</v>
       </c>
-      <c r="H75" s="24" t="s">
+      <c r="H75" s="23" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="14" t="s">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A76" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="B76" s="27" t="s">
+      <c r="B76" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="C76" s="14" t="s">
+      <c r="C76" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="D76" s="8">
+      <c r="D76" s="7">
         <v>2</v>
       </c>
-      <c r="E76" s="8">
+      <c r="E76" s="7">
         <v>12.8</v>
       </c>
-      <c r="F76" s="7">
+      <c r="F76" s="6">
         <f t="shared" si="1"/>
         <v>25.6</v>
       </c>
-      <c r="H76" s="23" t="s">
+      <c r="H76" s="22" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="15" t="s">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A77" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B77" s="27" t="s">
+      <c r="B77" s="26" t="s">
         <v>227</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="D77" s="9">
-        <v>1</v>
-      </c>
-      <c r="E77" s="9">
+      <c r="D77" s="8">
+        <v>1</v>
+      </c>
+      <c r="E77" s="8">
         <v>14.16</v>
       </c>
-      <c r="F77" s="7">
+      <c r="F77" s="6">
         <f t="shared" si="1"/>
         <v>14.16</v>
       </c>
-      <c r="H77" s="24" t="s">
+      <c r="H77" s="23" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="14" t="s">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A78" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B78" s="27" t="s">
+      <c r="B78" s="26" t="s">
         <v>228</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="C78" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D78" s="8">
+      <c r="D78" s="7">
         <v>5</v>
       </c>
-      <c r="E78" s="8">
+      <c r="E78" s="7">
         <v>6.98</v>
       </c>
-      <c r="F78" s="7">
+      <c r="F78" s="6">
         <f t="shared" si="1"/>
         <v>34.900000000000006</v>
       </c>
-      <c r="H78" s="23" t="s">
+      <c r="H78" s="22" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="15" t="s">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A79" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B79" s="27" t="s">
+      <c r="B79" s="26" t="s">
         <v>229</v>
       </c>
-      <c r="C79" s="19" t="s">
+      <c r="C79" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="D79" s="9">
-        <v>1</v>
-      </c>
-      <c r="E79" s="9">
+      <c r="D79" s="8">
+        <v>1</v>
+      </c>
+      <c r="E79" s="8">
         <v>3.76</v>
       </c>
-      <c r="F79" s="7">
+      <c r="F79" s="6">
         <f t="shared" si="1"/>
         <v>3.76</v>
       </c>
-      <c r="H79" s="24" t="s">
+      <c r="H79" s="23" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="14" t="s">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A80" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="B80" s="27" t="s">
+      <c r="B80" s="26" t="s">
         <v>230</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="C80" s="17" t="s">
         <v>138</v>
       </c>
-      <c r="D80" s="8">
-        <v>1</v>
-      </c>
-      <c r="E80" s="8">
+      <c r="D80" s="7">
+        <v>1</v>
+      </c>
+      <c r="E80" s="7">
         <v>4.72</v>
       </c>
-      <c r="F80" s="7">
+      <c r="F80" s="6">
         <f t="shared" si="1"/>
         <v>4.72</v>
       </c>
-      <c r="H80" s="23" t="s">
+      <c r="H80" s="22" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="15" t="s">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A81" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B81" s="27" t="s">
+      <c r="B81" s="26" t="s">
         <v>231</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="D81" s="9">
+      <c r="D81" s="8">
         <v>2</v>
       </c>
-      <c r="E81" s="9">
+      <c r="E81" s="8">
         <v>61.04</v>
       </c>
-      <c r="F81" s="7">
+      <c r="F81" s="6">
         <f t="shared" si="1"/>
         <v>122.08</v>
       </c>
-      <c r="H81" s="24" t="s">
+      <c r="H81" s="23" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="14" t="s">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A82" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="B82" s="27" t="s">
+      <c r="B82" s="26" t="s">
         <v>232</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="C82" s="17" t="s">
         <v>140</v>
       </c>
-      <c r="D82" s="8">
-        <v>1</v>
-      </c>
-      <c r="E82" s="8">
+      <c r="D82" s="7">
+        <v>1</v>
+      </c>
+      <c r="E82" s="7">
         <v>382.26</v>
       </c>
-      <c r="F82" s="7">
+      <c r="F82" s="6">
         <f t="shared" si="1"/>
         <v>382.26</v>
       </c>
-      <c r="H82" s="23" t="s">
+      <c r="H82" s="22" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="15" t="s">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A83" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="B83" s="27" t="s">
+      <c r="B83" s="26" t="s">
         <v>233</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="D83" s="9">
+      <c r="D83" s="8">
         <v>2</v>
       </c>
-      <c r="E83" s="9">
+      <c r="E83" s="8">
         <v>47.78</v>
       </c>
-      <c r="F83" s="7">
+      <c r="F83" s="6">
         <f t="shared" si="1"/>
         <v>95.56</v>
       </c>
-      <c r="H83" s="24" t="s">
+      <c r="H83" s="23" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="14" t="s">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A84" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="B84" s="27" t="s">
+      <c r="B84" s="26" t="s">
         <v>234</v>
       </c>
-      <c r="C84" s="18" t="s">
+      <c r="C84" s="17" t="s">
         <v>142</v>
       </c>
-      <c r="D84" s="8">
+      <c r="D84" s="7">
         <v>5</v>
       </c>
-      <c r="E84" s="8">
+      <c r="E84" s="7">
         <v>9.99</v>
       </c>
-      <c r="F84" s="7">
+      <c r="F84" s="6">
         <f t="shared" si="1"/>
         <v>49.95</v>
       </c>
-      <c r="H84" s="23" t="s">
+      <c r="H84" s="22" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="15" t="s">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A85" s="14" t="s">
         <v>35</v>
       </c>
-      <c r="B85" s="27" t="s">
+      <c r="B85" s="26" t="s">
         <v>235</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="D85" s="9">
-        <v>1</v>
-      </c>
-      <c r="E85" s="9">
+      <c r="D85" s="8">
+        <v>1</v>
+      </c>
+      <c r="E85" s="8">
         <v>6.02</v>
       </c>
-      <c r="F85" s="7">
+      <c r="F85" s="6">
         <f t="shared" si="1"/>
         <v>6.02</v>
       </c>
-      <c r="H85" s="24" t="s">
+      <c r="H85" s="23" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="14" t="s">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A86" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B86" s="27" t="s">
+      <c r="B86" s="26" t="s">
         <v>236</v>
       </c>
-      <c r="C86" s="18" t="s">
+      <c r="C86" s="17" t="s">
         <v>144</v>
       </c>
-      <c r="D86" s="8">
-        <v>1</v>
-      </c>
-      <c r="E86" s="8">
+      <c r="D86" s="7">
+        <v>1</v>
+      </c>
+      <c r="E86" s="7">
         <v>2.3199999999999998</v>
       </c>
-      <c r="F86" s="7">
+      <c r="F86" s="6">
         <f t="shared" si="1"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="H86" s="23" t="s">
+      <c r="H86" s="22" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="15" t="s">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A87" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B87" s="27" t="s">
+      <c r="B87" s="26" t="s">
         <v>237</v>
       </c>
-      <c r="C87" s="15" t="s">
+      <c r="C87" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D87" s="9">
+      <c r="D87" s="8">
         <v>4</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="8">
         <v>11.99</v>
       </c>
-      <c r="F87" s="7">
+      <c r="F87" s="6">
         <f t="shared" si="1"/>
         <v>47.96</v>
       </c>
-      <c r="H87" s="24" t="s">
+      <c r="H87" s="23" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="14" t="s">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A88" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B88" s="27" t="s">
+      <c r="B88" s="26" t="s">
         <v>238</v>
       </c>
-      <c r="C88" s="14" t="s">
+      <c r="C88" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="D88" s="8">
-        <v>1</v>
-      </c>
-      <c r="E88" s="8">
+      <c r="D88" s="7">
+        <v>1</v>
+      </c>
+      <c r="E88" s="7">
         <v>9.99</v>
       </c>
-      <c r="F88" s="7">
+      <c r="F88" s="6">
         <f t="shared" si="1"/>
         <v>9.99</v>
       </c>
-      <c r="H88" s="23" t="s">
+      <c r="H88" s="22" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="15" t="s">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B89" s="27" t="s">
+      <c r="B89" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="D89" s="9">
+      <c r="D89" s="8">
         <v>2</v>
       </c>
-      <c r="E89" s="9">
+      <c r="E89" s="8">
         <v>14.63</v>
       </c>
-      <c r="F89" s="7">
+      <c r="F89" s="6">
         <f t="shared" si="1"/>
         <v>29.26</v>
       </c>
-      <c r="H89" s="24" t="s">
+      <c r="H89" s="23" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="14" t="s">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B90" s="27" t="s">
+      <c r="B90" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="22" t="s">
+      <c r="C90" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="D90" s="8">
+      <c r="D90" s="7">
         <v>4</v>
       </c>
-      <c r="E90" s="8">
+      <c r="E90" s="7">
         <v>167.42</v>
       </c>
-      <c r="F90" s="7">
+      <c r="F90" s="6">
         <f t="shared" si="1"/>
         <v>669.68</v>
       </c>
-      <c r="H90" s="23" t="s">
+      <c r="H90" s="22" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="15" t="s">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B91" s="27" t="s">
+      <c r="B91" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="19" t="s">
+      <c r="C91" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D91" s="9">
-        <v>1</v>
-      </c>
-      <c r="E91" s="9">
+      <c r="D91" s="8">
+        <v>1</v>
+      </c>
+      <c r="E91" s="8">
         <v>12.61</v>
       </c>
-      <c r="F91" s="7">
+      <c r="F91" s="6">
         <f t="shared" si="1"/>
         <v>12.61</v>
       </c>
-      <c r="H91" s="24" t="s">
+      <c r="H91" s="23" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="14" t="s">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B92" s="27"/>
-      <c r="C92" s="14" t="s">
+      <c r="B92" s="26"/>
+      <c r="C92" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D92" s="8">
+      <c r="D92" s="7">
         <v>2</v>
       </c>
-      <c r="E92" s="8">
+      <c r="E92" s="7">
         <v>10.45</v>
       </c>
-      <c r="F92" s="7">
+      <c r="F92" s="6">
         <f t="shared" si="1"/>
         <v>20.9</v>
       </c>
-      <c r="H92" s="25" t="s">
+      <c r="H92" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="32" t="s">
+      <c r="C93" s="29" t="s">
         <v>266</v>
       </c>
       <c r="D93" s="2">
         <v>1</v>
       </c>
-      <c r="E93" s="7">
+      <c r="E93" s="6">
         <v>110</v>
       </c>
-      <c r="F93" s="7">
-        <f>D93*E93</f>
+      <c r="F93" s="6">
+        <f t="shared" ref="F93:F101" si="2">D93*E93</f>
         <v>110</v>
       </c>
-      <c r="H93" s="25" t="s">
+      <c r="H93" s="24" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="30" t="s">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B94" s="31" t="s">
+      <c r="B94" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="C94" s="30" t="s">
+      <c r="C94" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="D94" s="8">
-        <v>1</v>
-      </c>
-      <c r="E94" s="8">
+      <c r="D94" s="7">
+        <v>1</v>
+      </c>
+      <c r="E94" s="7">
         <v>13.55</v>
       </c>
-      <c r="F94" s="7">
-        <f>D94*E94</f>
+      <c r="F94" s="6">
+        <f t="shared" si="2"/>
         <v>13.55</v>
       </c>
-      <c r="H94" s="23" t="s">
+      <c r="H94" s="22" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="30" t="s">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="B95" s="31" t="s">
+      <c r="B95" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="C95" s="30" t="s">
+      <c r="C95" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="D95" s="8">
-        <v>1</v>
-      </c>
-      <c r="E95" s="8">
+      <c r="D95" s="7">
+        <v>1</v>
+      </c>
+      <c r="E95" s="7">
         <v>8.4700000000000006</v>
       </c>
-      <c r="F95" s="7">
-        <f>D95*E95</f>
+      <c r="F95" s="6">
+        <f t="shared" si="2"/>
         <v>8.4700000000000006</v>
       </c>
-      <c r="H95" s="23" t="s">
+      <c r="H95" s="22" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="30"/>
-      <c r="B96" s="31"/>
-      <c r="C96" s="30"/>
-      <c r="D96" s="8"/>
-      <c r="E96" s="8"/>
-      <c r="F96" s="7">
-        <f>D96*E96</f>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="13"/>
+      <c r="B96" s="26"/>
+      <c r="C96" s="13"/>
+      <c r="D96" s="7"/>
+      <c r="E96" s="7"/>
+      <c r="F96" s="6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H96" s="25"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="30"/>
-      <c r="B97" s="31"/>
-      <c r="C97" s="30"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="7">
-        <f>D97*E97</f>
+      <c r="H96" s="24"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A97" s="13"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="13"/>
+      <c r="D97" s="7"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H97" s="25"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="30"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="30"/>
-      <c r="D98" s="8"/>
-      <c r="E98" s="8"/>
-      <c r="F98" s="7">
-        <f>D98*E98</f>
+      <c r="H97" s="24"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A98" s="13"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="13"/>
+      <c r="D98" s="7"/>
+      <c r="E98" s="7"/>
+      <c r="F98" s="6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H98" s="25"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="30"/>
-      <c r="B99" s="31"/>
-      <c r="C99" s="30"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="7">
-        <f>D99*E99</f>
+      <c r="H98" s="24"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A99" s="13"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H99" s="25"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="30"/>
-      <c r="B100" s="31"/>
-      <c r="C100" s="30"/>
-      <c r="D100" s="8"/>
-      <c r="E100" s="8"/>
-      <c r="F100" s="7">
-        <f>D100*E100</f>
+      <c r="H99" s="24"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A100" s="13"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="13"/>
+      <c r="D100" s="7"/>
+      <c r="E100" s="7"/>
+      <c r="F100" s="6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H100" s="25"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="30"/>
-      <c r="B101" s="31"/>
-      <c r="C101" s="30"/>
-      <c r="D101" s="8"/>
-      <c r="E101" s="8"/>
-      <c r="F101" s="7">
-        <f>D101*E101</f>
+      <c r="H100" s="24"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A101" s="13"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="6">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H101" s="25"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="15" t="s">
+      <c r="H101" s="24"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A102" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="B102" s="27"/>
-      <c r="C102" s="15" t="s">
+      <c r="B102" s="26"/>
+      <c r="C102" s="14" t="s">
         <v>150</v>
       </c>
-      <c r="D102" s="9">
+      <c r="D102" s="8">
         <v>3</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="8">
         <v>2.1800000000000002</v>
       </c>
-      <c r="F102" s="7">
+      <c r="F102" s="6">
         <f t="shared" si="1"/>
         <v>6.5400000000000009</v>
       </c>
-      <c r="H102" s="26" t="s">
+      <c r="H102" s="25" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="14" t="s">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A103" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B103" s="27"/>
-      <c r="C103" s="14">
+      <c r="B103" s="26"/>
+      <c r="C103" s="13">
         <v>156665159304</v>
       </c>
-      <c r="D103" s="8">
+      <c r="D103" s="7">
         <v>3</v>
       </c>
-      <c r="E103" s="8">
+      <c r="E103" s="7">
         <v>35.97</v>
       </c>
-      <c r="F103" s="7">
+      <c r="F103" s="6">
         <f t="shared" si="1"/>
         <v>107.91</v>
       </c>
-      <c r="H103" s="25" t="s">
+      <c r="H103" s="24" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="15" t="s">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A104" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B104" s="27" t="s">
+      <c r="B104" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C104" s="15" t="s">
+      <c r="C104" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="D104" s="9">
+      <c r="D104" s="8">
         <v>3</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="8">
         <v>167.42</v>
       </c>
-      <c r="F104" s="7">
+      <c r="F104" s="6">
         <f t="shared" si="1"/>
         <v>502.26</v>
       </c>
-      <c r="H104" s="24" t="s">
+      <c r="H104" s="23" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="14" t="s">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A105" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B105" s="27" t="s">
+      <c r="B105" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C105" s="14">
+      <c r="C105" s="13">
         <v>316529</v>
       </c>
-      <c r="D105" s="8">
-        <v>1</v>
-      </c>
-      <c r="E105" s="8">
+      <c r="D105" s="7">
+        <v>1</v>
+      </c>
+      <c r="E105" s="7">
         <v>405</v>
       </c>
-      <c r="F105" s="7">
+      <c r="F105" s="6">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="H105" s="23" t="s">
+      <c r="H105" s="22" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="15" t="s">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A106" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="B106" s="27" t="s">
+      <c r="B106" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="C106" s="12" t="s">
+      <c r="C106" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D106" s="9">
-        <v>1</v>
-      </c>
-      <c r="E106" s="9">
+      <c r="D106" s="8">
+        <v>1</v>
+      </c>
+      <c r="E106" s="8">
         <v>37.4</v>
       </c>
-      <c r="F106" s="7">
+      <c r="F106" s="6">
         <f t="shared" si="1"/>
         <v>37.4</v>
       </c>
-      <c r="H106" s="24" t="s">
+      <c r="H106" s="23" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="14" t="s">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A107" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B107" s="27" t="s">
+      <c r="B107" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="C107" s="13" t="s">
+      <c r="C107" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="D107" s="8">
-        <v>1</v>
-      </c>
-      <c r="E107" s="8">
+      <c r="D107" s="7">
+        <v>1</v>
+      </c>
+      <c r="E107" s="7">
         <v>20.91</v>
       </c>
-      <c r="F107" s="7">
+      <c r="F107" s="6">
         <f t="shared" si="1"/>
         <v>20.91</v>
       </c>
-      <c r="H107" s="23" t="s">
+      <c r="H107" s="22" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="15" t="s">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A108" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="B108" s="27" t="s">
+      <c r="B108" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C108" s="12" t="s">
+      <c r="C108" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D108" s="9">
-        <v>1</v>
-      </c>
-      <c r="E108" s="9">
+      <c r="D108" s="8">
+        <v>1</v>
+      </c>
+      <c r="E108" s="8">
         <v>79.099999999999994</v>
       </c>
-      <c r="F108" s="7">
+      <c r="F108" s="6">
         <f t="shared" si="1"/>
         <v>79.099999999999994</v>
       </c>
-      <c r="H108" s="24" t="s">
+      <c r="H108" s="23" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="14" t="s">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A109" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B109" s="27" t="s">
+      <c r="B109" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="C109" s="18" t="s">
+      <c r="C109" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D109" s="8">
-        <v>1</v>
-      </c>
-      <c r="E109" s="8">
+      <c r="D109" s="7">
+        <v>1</v>
+      </c>
+      <c r="E109" s="7">
         <v>16.260000000000002</v>
       </c>
-      <c r="F109" s="7">
+      <c r="F109" s="6">
         <f t="shared" si="1"/>
         <v>16.260000000000002</v>
       </c>
-      <c r="H109" s="23" t="s">
+      <c r="H109" s="22" t="s">
         <v>246</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="28" t="s">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A110" s="27" t="s">
         <v>258</v>
       </c>
-      <c r="B110" s="27" t="s">
+      <c r="B110" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C110" s="11" t="s">
+      <c r="C110" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D110" s="29">
-        <v>1</v>
-      </c>
-      <c r="E110" s="29">
+      <c r="D110" s="28">
+        <v>1</v>
+      </c>
+      <c r="E110" s="28">
         <v>5.35</v>
       </c>
-      <c r="F110" s="7">
+      <c r="F110" s="6">
         <f>D110*E110</f>
         <v>5.35</v>
       </c>
@@ -4189,23 +4240,23 @@
         <v>252</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="28" t="s">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A111" s="27" t="s">
         <v>259</v>
       </c>
-      <c r="B111" s="27" t="s">
+      <c r="B111" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C111" s="11" t="s">
+      <c r="C111" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="D111" s="29">
-        <v>1</v>
-      </c>
-      <c r="E111" s="29">
+      <c r="D111" s="28">
+        <v>1</v>
+      </c>
+      <c r="E111" s="28">
         <v>10.75</v>
       </c>
-      <c r="F111" s="7">
+      <c r="F111" s="6">
         <f>D111*E111</f>
         <v>10.75</v>
       </c>
@@ -4213,40 +4264,224 @@
         <v>255</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="28" t="s">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A112" s="27" t="s">
         <v>260</v>
       </c>
-      <c r="B112" s="27" t="s">
+      <c r="B112" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D112" s="29">
-        <v>1</v>
-      </c>
-      <c r="E112" s="29">
+      <c r="D112" s="28">
+        <v>1</v>
+      </c>
+      <c r="E112" s="28">
         <v>6.68</v>
       </c>
-      <c r="F112" s="7">
+      <c r="F112" s="6">
         <v>7.96</v>
       </c>
       <c r="H112" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="11"/>
-      <c r="B113" s="11"/>
-      <c r="C113" s="11"/>
-      <c r="H113" s="11"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F115" s="6">
-        <f>SUM(F2:F112)</f>
-        <v>9666.5800000000017</v>
-      </c>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A113" s="30" t="s">
+        <v>276</v>
+      </c>
+      <c r="B113" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C113" s="33" t="s">
+        <v>278</v>
+      </c>
+      <c r="D113" s="8">
+        <v>1</v>
+      </c>
+      <c r="E113" s="8">
+        <v>28.78</v>
+      </c>
+      <c r="F113" s="34">
+        <f t="shared" ref="F113:F115" si="3">D113*E113</f>
+        <v>28.78</v>
+      </c>
+      <c r="G113" s="35"/>
+      <c r="H113" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="I113" s="35"/>
+      <c r="J113" s="35"/>
+      <c r="K113" s="35"/>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A114" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="B114" s="32" t="s">
+        <v>283</v>
+      </c>
+      <c r="C114" s="33" t="s">
+        <v>282</v>
+      </c>
+      <c r="D114" s="8">
+        <v>1</v>
+      </c>
+      <c r="E114" s="8">
+        <v>146.18</v>
+      </c>
+      <c r="F114" s="34">
+        <f t="shared" si="3"/>
+        <v>146.18</v>
+      </c>
+      <c r="G114" s="35"/>
+      <c r="H114" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I114" s="35"/>
+      <c r="J114" s="35"/>
+      <c r="K114" s="35"/>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B115" s="32" t="s">
+        <v>284</v>
+      </c>
+      <c r="C115" s="33" t="s">
+        <v>286</v>
+      </c>
+      <c r="D115" s="8">
+        <v>1</v>
+      </c>
+      <c r="E115" s="8">
+        <v>36.06</v>
+      </c>
+      <c r="F115" s="34">
+        <f t="shared" si="3"/>
+        <v>36.06</v>
+      </c>
+      <c r="G115" s="35"/>
+      <c r="H115" s="37" t="s">
+        <v>287</v>
+      </c>
+      <c r="I115" s="35"/>
+      <c r="J115" s="35"/>
+      <c r="K115" s="35"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="30"/>
+      <c r="B116" s="32"/>
+      <c r="C116" s="33"/>
+      <c r="D116" s="8"/>
+      <c r="E116" s="8"/>
+      <c r="F116" s="34">
+        <f t="shared" ref="F116:F122" si="4">D116*E116</f>
+        <v>0</v>
+      </c>
+      <c r="G116" s="35"/>
+      <c r="H116" s="36"/>
+      <c r="I116" s="35"/>
+      <c r="J116" s="35"/>
+      <c r="K116" s="35"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="30"/>
+      <c r="B117" s="32"/>
+      <c r="C117" s="33"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G117" s="35"/>
+      <c r="H117" s="36"/>
+      <c r="I117" s="35"/>
+      <c r="J117" s="35"/>
+      <c r="K117" s="35"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="30"/>
+      <c r="B118" s="32"/>
+      <c r="C118" s="33"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="35"/>
+      <c r="H118" s="36"/>
+      <c r="I118" s="35"/>
+      <c r="J118" s="35"/>
+      <c r="K118" s="35"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="30"/>
+      <c r="B119" s="32"/>
+      <c r="C119" s="33"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G119" s="35"/>
+      <c r="H119" s="36"/>
+      <c r="I119" s="35"/>
+      <c r="J119" s="35"/>
+      <c r="K119" s="35"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="30"/>
+      <c r="B120" s="32"/>
+      <c r="C120" s="33"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G120" s="35"/>
+      <c r="H120" s="36"/>
+      <c r="I120" s="35"/>
+      <c r="J120" s="35"/>
+      <c r="K120" s="35"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="30"/>
+      <c r="B121" s="32"/>
+      <c r="C121" s="33"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G121" s="35"/>
+      <c r="H121" s="36"/>
+      <c r="I121" s="35"/>
+      <c r="J121" s="35"/>
+      <c r="K121" s="35"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="31"/>
+      <c r="B122" s="32"/>
+      <c r="C122" s="33"/>
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="34">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="G122" s="35"/>
+      <c r="H122" s="36"/>
+      <c r="I122" s="35"/>
+      <c r="J122" s="35"/>
+      <c r="K122" s="35"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4350,11 +4585,14 @@
     <hyperlink ref="H112" r:id="rId97" xr:uid="{FDEFAFD3-3687-4641-964A-8BC9B3E42512}"/>
     <hyperlink ref="H95" r:id="rId98" xr:uid="{29622D1D-FB83-4317-A033-D7DD9D94A271}"/>
     <hyperlink ref="H94" r:id="rId99" xr:uid="{5FC8DB1C-6249-4551-B238-6394EA039EB9}"/>
+    <hyperlink ref="H113" r:id="rId100" display="https://www.grainger.com/product/BANJO-Inline-Strainer-Polypropylene-3ELX2" xr:uid="{5DDCF04D-0B2B-4400-9BF3-CBBD33627CF9}"/>
+    <hyperlink ref="H114" r:id="rId101" display="https://www.grainger.com/product/BELL-GOSSETT-Water-Pressure-Reducing-Valve-6LFA3" xr:uid="{704D45CE-3BF8-44FB-A2F9-FBD42F90D381}"/>
+    <hyperlink ref="H115" r:id="rId102" xr:uid="{DA2A078E-95DA-4F11-A662-702B09E6F14A}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId100"/>
+  <pageSetup orientation="portrait" r:id="rId103"/>
   <tableParts count="1">
-    <tablePart r:id="rId101"/>
+    <tablePart r:id="rId104"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ig2\Desktop\SMR Thermal\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{F9767054-3909-4284-9249-BF43A556FFA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EB46BDF3-3269-411F-B3BC-B7712C5D24DE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0CC7EB-E376-4619-9A43-94EBDD984420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="288">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="295">
   <si>
     <t>Total Cost</t>
   </si>
@@ -900,6 +900,27 @@
   </si>
   <si>
     <t>https://www.grainger.com/product/APOLLO-Relief-Valve-FNPT-x-FNPT-804Z55</t>
+  </si>
+  <si>
+    <t>Nichrome Rod (TO ORDER)</t>
+  </si>
+  <si>
+    <t>360 Brass Rod: 3/8 in Outside Dia, 12 in Overall Lg, H02, Mill, 45,000 psi Yield Strength, Inch</t>
+  </si>
+  <si>
+    <t>BR360/375-12</t>
+  </si>
+  <si>
+    <t>3/8 in Outside Dia, 12 in Overall Lg, 360 Brass Rod - 803H45|BR360/375-12 - Grainger</t>
+  </si>
+  <si>
+    <t>WEATHERHEAD Compression Fitting Union: 3/8 in OD x 3/8 in OD Fitting Size, Compression x Compression</t>
+  </si>
+  <si>
+    <t>62X6</t>
+  </si>
+  <si>
+    <t>WEATHERHEAD, 3/8 in OD x 3/8 in OD Fitting Size, Compression x Compression, Compression Fitting Union - 20KF99|62X6 - Grainger</t>
   </si>
 </sst>
 </file>
@@ -910,7 +931,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -981,6 +1002,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1042,7 +1089,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1127,27 +1174,50 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1602,24 +1672,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M122"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.08984375" customWidth="1"/>
+    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.453125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.44140625" customWidth="1"/>
-    <col min="11" max="11" width="62.44140625" customWidth="1"/>
-    <col min="12" max="12" width="55.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.453125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.453125" customWidth="1"/>
+    <col min="11" max="11" width="62.453125" customWidth="1"/>
+    <col min="12" max="12" width="55.6328125" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1654,7 +1724,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
@@ -1680,7 +1750,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>11</v>
       </c>
@@ -1706,7 +1776,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
@@ -1731,7 +1801,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
@@ -1757,7 +1827,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
@@ -1783,7 +1853,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
@@ -1811,7 +1881,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
@@ -1837,7 +1907,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
@@ -1864,7 +1934,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="13" t="s">
         <v>16</v>
       </c>
@@ -1889,7 +1959,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="14" t="s">
         <v>17</v>
       </c>
@@ -1915,7 +1985,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
@@ -1939,7 +2009,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
@@ -1965,7 +2035,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
         <v>20</v>
       </c>
@@ -1991,7 +2061,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
         <v>21</v>
       </c>
@@ -2017,7 +2087,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="13" t="s">
         <v>22</v>
       </c>
@@ -2043,7 +2113,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="14" t="s">
         <v>23</v>
       </c>
@@ -2069,7 +2139,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="13" t="s">
         <v>24</v>
       </c>
@@ -2093,7 +2163,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="14" t="s">
         <v>25</v>
       </c>
@@ -2119,7 +2189,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="13" t="s">
         <v>26</v>
       </c>
@@ -2145,7 +2215,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="14" t="s">
         <v>27</v>
       </c>
@@ -2171,7 +2241,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="13" t="s">
         <v>28</v>
       </c>
@@ -2197,7 +2267,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="14" t="s">
         <v>29</v>
       </c>
@@ -2223,7 +2293,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="13" t="s">
         <v>30</v>
       </c>
@@ -2249,7 +2319,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="14" t="s">
         <v>28</v>
       </c>
@@ -2275,7 +2345,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="13" t="s">
         <v>31</v>
       </c>
@@ -2301,7 +2371,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="14" t="s">
         <v>17</v>
       </c>
@@ -2326,7 +2396,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="13" t="s">
         <v>32</v>
       </c>
@@ -2350,7 +2420,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="14" t="s">
         <v>33</v>
       </c>
@@ -2374,7 +2444,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="13" t="s">
         <v>34</v>
       </c>
@@ -2398,7 +2468,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A31" s="14" t="s">
         <v>35</v>
       </c>
@@ -2422,7 +2492,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A32" s="13" t="s">
         <v>35</v>
       </c>
@@ -2446,7 +2516,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="14" t="s">
         <v>36</v>
       </c>
@@ -2470,7 +2540,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="13" t="s">
         <v>36</v>
       </c>
@@ -2494,7 +2564,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="14" t="s">
         <v>37</v>
       </c>
@@ -2518,7 +2588,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A36" s="13" t="s">
         <v>37</v>
       </c>
@@ -2542,7 +2612,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A37" s="14" t="s">
         <v>35</v>
       </c>
@@ -2566,7 +2636,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A38" s="13" t="s">
         <v>38</v>
       </c>
@@ -2590,7 +2660,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A39" s="14" t="s">
         <v>38</v>
       </c>
@@ -2614,7 +2684,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A40" s="13" t="s">
         <v>12</v>
       </c>
@@ -2638,7 +2708,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A41" s="14" t="s">
         <v>39</v>
       </c>
@@ -2662,7 +2732,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A42" s="13" t="s">
         <v>40</v>
       </c>
@@ -2686,7 +2756,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A43" s="14" t="s">
         <v>41</v>
       </c>
@@ -2710,7 +2780,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A44" s="13" t="s">
         <v>42</v>
       </c>
@@ -2734,7 +2804,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A45" s="14" t="s">
         <v>43</v>
       </c>
@@ -2758,7 +2828,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A46" s="13" t="s">
         <v>44</v>
       </c>
@@ -2782,7 +2852,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A47" s="14" t="s">
         <v>45</v>
       </c>
@@ -2806,7 +2876,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A48" s="13" t="s">
         <v>45</v>
       </c>
@@ -2830,7 +2900,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
         <v>46</v>
       </c>
@@ -2854,7 +2924,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A50" s="13" t="s">
         <v>47</v>
       </c>
@@ -2878,7 +2948,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A51" s="14" t="s">
         <v>46</v>
       </c>
@@ -2902,7 +2972,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A52" s="13" t="s">
         <v>46</v>
       </c>
@@ -2926,7 +2996,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A53" s="14" t="s">
         <v>48</v>
       </c>
@@ -2950,7 +3020,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A54" s="13" t="s">
         <v>49</v>
       </c>
@@ -2974,7 +3044,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A55" s="14" t="s">
         <v>50</v>
       </c>
@@ -2998,7 +3068,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A56" s="13" t="s">
         <v>35</v>
       </c>
@@ -3022,7 +3092,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A57" s="14" t="s">
         <v>48</v>
       </c>
@@ -3046,7 +3116,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A58" s="13" t="s">
         <v>39</v>
       </c>
@@ -3070,7 +3140,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A59" s="14" t="s">
         <v>12</v>
       </c>
@@ -3094,7 +3164,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A60" s="13" t="s">
         <v>51</v>
       </c>
@@ -3118,7 +3188,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A61" s="14" t="s">
         <v>46</v>
       </c>
@@ -3142,7 +3212,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A62" s="13" t="s">
         <v>52</v>
       </c>
@@ -3166,7 +3236,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A63" s="14" t="s">
         <v>52</v>
       </c>
@@ -3190,7 +3260,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A64" s="13" t="s">
         <v>48</v>
       </c>
@@ -3214,7 +3284,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A65" s="14" t="s">
         <v>45</v>
       </c>
@@ -3238,7 +3308,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A66" s="13" t="s">
         <v>37</v>
       </c>
@@ -3262,7 +3332,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A67" s="14" t="s">
         <v>53</v>
       </c>
@@ -3286,7 +3356,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A68" s="13" t="s">
         <v>45</v>
       </c>
@@ -3310,7 +3380,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A69" s="14" t="s">
         <v>54</v>
       </c>
@@ -3334,7 +3404,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A70" s="13" t="s">
         <v>54</v>
       </c>
@@ -3358,7 +3428,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A71" s="14" t="s">
         <v>55</v>
       </c>
@@ -3382,7 +3452,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A72" s="13" t="s">
         <v>46</v>
       </c>
@@ -3406,7 +3476,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A73" s="14" t="s">
         <v>56</v>
       </c>
@@ -3430,7 +3500,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A74" s="13" t="s">
         <v>57</v>
       </c>
@@ -3454,7 +3524,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A75" s="14" t="s">
         <v>11</v>
       </c>
@@ -3478,7 +3548,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A76" s="13" t="s">
         <v>58</v>
       </c>
@@ -3502,7 +3572,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A77" s="14" t="s">
         <v>46</v>
       </c>
@@ -3526,7 +3596,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A78" s="13" t="s">
         <v>39</v>
       </c>
@@ -3550,7 +3620,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A79" s="14" t="s">
         <v>59</v>
       </c>
@@ -3574,7 +3644,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A80" s="13" t="s">
         <v>60</v>
       </c>
@@ -3598,7 +3668,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A81" s="14" t="s">
         <v>61</v>
       </c>
@@ -3622,7 +3692,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
         <v>62</v>
       </c>
@@ -3646,7 +3716,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A83" s="14" t="s">
         <v>63</v>
       </c>
@@ -3670,7 +3740,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A84" s="13" t="s">
         <v>64</v>
       </c>
@@ -3694,7 +3764,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A85" s="14" t="s">
         <v>35</v>
       </c>
@@ -3718,7 +3788,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A86" s="13" t="s">
         <v>63</v>
       </c>
@@ -3742,7 +3812,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A87" s="14" t="s">
         <v>65</v>
       </c>
@@ -3766,7 +3836,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A88" s="13" t="s">
         <v>63</v>
       </c>
@@ -3790,7 +3860,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A89" s="14" t="s">
         <v>66</v>
       </c>
@@ -3814,7 +3884,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3838,7 +3908,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A91" s="14" t="s">
         <v>46</v>
       </c>
@@ -3862,7 +3932,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -3884,7 +3954,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -3908,7 +3978,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -3932,7 +4002,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -3956,7 +4026,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A96" s="13"/>
       <c r="B96" s="26"/>
       <c r="C96" s="13"/>
@@ -3968,7 +4038,7 @@
       </c>
       <c r="H96" s="24"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A97" s="13"/>
       <c r="B97" s="26"/>
       <c r="C97" s="13"/>
@@ -3980,7 +4050,7 @@
       </c>
       <c r="H97" s="24"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A98" s="13"/>
       <c r="B98" s="26"/>
       <c r="C98" s="13"/>
@@ -3992,7 +4062,7 @@
       </c>
       <c r="H98" s="24"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A99" s="13"/>
       <c r="B99" s="26"/>
       <c r="C99" s="13"/>
@@ -4004,7 +4074,7 @@
       </c>
       <c r="H99" s="24"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A100" s="13"/>
       <c r="B100" s="26"/>
       <c r="C100" s="13"/>
@@ -4016,7 +4086,7 @@
       </c>
       <c r="H100" s="24"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A101" s="13"/>
       <c r="B101" s="26"/>
       <c r="C101" s="13"/>
@@ -4028,7 +4098,7 @@
       </c>
       <c r="H101" s="24"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A102" s="14" t="s">
         <v>68</v>
       </c>
@@ -4050,7 +4120,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A103" s="13" t="s">
         <v>69</v>
       </c>
@@ -4072,7 +4142,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A104" s="14" t="s">
         <v>67</v>
       </c>
@@ -4096,7 +4166,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A105" s="13" t="s">
         <v>70</v>
       </c>
@@ -4120,7 +4190,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A106" s="14" t="s">
         <v>66</v>
       </c>
@@ -4144,7 +4214,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A107" s="13" t="s">
         <v>17</v>
       </c>
@@ -4168,7 +4238,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A108" s="14" t="s">
         <v>61</v>
       </c>
@@ -4192,7 +4262,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A109" s="13" t="s">
         <v>71</v>
       </c>
@@ -4216,7 +4286,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A110" s="27" t="s">
         <v>258</v>
       </c>
@@ -4240,7 +4310,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A111" s="27" t="s">
         <v>259</v>
       </c>
@@ -4264,7 +4334,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A112" s="27" t="s">
         <v>260</v>
       </c>
@@ -4287,14 +4357,14 @@
         <v>261</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A113" s="30" t="s">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A113" s="14" t="s">
         <v>276</v>
       </c>
-      <c r="B113" s="32" t="s">
+      <c r="B113" s="26" t="s">
         <v>277</v>
       </c>
-      <c r="C113" s="33" t="s">
+      <c r="C113" s="10" t="s">
         <v>278</v>
       </c>
       <c r="D113" s="8">
@@ -4303,26 +4373,22 @@
       <c r="E113" s="8">
         <v>28.78</v>
       </c>
-      <c r="F113" s="34">
+      <c r="F113" s="6">
         <f t="shared" ref="F113:F115" si="3">D113*E113</f>
         <v>28.78</v>
       </c>
-      <c r="G113" s="35"/>
       <c r="H113" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="I113" s="35"/>
-      <c r="J113" s="35"/>
-      <c r="K113" s="35"/>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A114" s="30" t="s">
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A114" s="14" t="s">
         <v>280</v>
       </c>
-      <c r="B114" s="32" t="s">
+      <c r="B114" s="26" t="s">
         <v>283</v>
       </c>
-      <c r="C114" s="33" t="s">
+      <c r="C114" s="10" t="s">
         <v>282</v>
       </c>
       <c r="D114" s="8">
@@ -4331,26 +4397,22 @@
       <c r="E114" s="8">
         <v>146.18</v>
       </c>
-      <c r="F114" s="34">
+      <c r="F114" s="6">
         <f t="shared" si="3"/>
         <v>146.18</v>
       </c>
-      <c r="G114" s="35"/>
       <c r="H114" s="1" t="s">
         <v>281</v>
       </c>
-      <c r="I114" s="35"/>
-      <c r="J114" s="35"/>
-      <c r="K114" s="35"/>
-    </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="30" t="s">
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A115" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="B115" s="32" t="s">
+      <c r="B115" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="C115" s="33" t="s">
+      <c r="C115" s="10" t="s">
         <v>286</v>
       </c>
       <c r="D115" s="8">
@@ -4359,129 +4421,125 @@
       <c r="E115" s="8">
         <v>36.06</v>
       </c>
-      <c r="F115" s="34">
+      <c r="F115" s="6">
         <f t="shared" si="3"/>
         <v>36.06</v>
       </c>
-      <c r="G115" s="35"/>
-      <c r="H115" s="37" t="s">
+      <c r="H115" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="I115" s="35"/>
-      <c r="J115" s="35"/>
-      <c r="K115" s="35"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A116" s="30"/>
-      <c r="B116" s="32"/>
-      <c r="C116" s="33"/>
-      <c r="D116" s="8"/>
-      <c r="E116" s="8"/>
-      <c r="F116" s="34">
+    </row>
+    <row r="116" spans="1:11" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="31" t="s">
+        <v>288</v>
+      </c>
+      <c r="B116" s="32" t="s">
+        <v>289</v>
+      </c>
+      <c r="C116" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="D116" s="34">
+        <v>2</v>
+      </c>
+      <c r="E116" s="34">
+        <v>7.82</v>
+      </c>
+      <c r="F116" s="35">
         <f t="shared" ref="F116:F122" si="4">D116*E116</f>
-        <v>0</v>
-      </c>
-      <c r="G116" s="35"/>
-      <c r="H116" s="36"/>
-      <c r="I116" s="35"/>
-      <c r="J116" s="35"/>
-      <c r="K116" s="35"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="30"/>
-      <c r="B117" s="32"/>
-      <c r="C117" s="33"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="34">
+        <v>15.64</v>
+      </c>
+      <c r="H116" s="37" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="B117" s="43" t="s">
+        <v>292</v>
+      </c>
+      <c r="C117" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="D117" s="39">
+        <v>2</v>
+      </c>
+      <c r="E117" s="39">
+        <v>14.99</v>
+      </c>
+      <c r="F117" s="40">
+        <f t="shared" si="4"/>
+        <v>29.98</v>
+      </c>
+      <c r="G117" s="41"/>
+      <c r="H117" s="42" t="s">
+        <v>294</v>
+      </c>
+      <c r="I117" s="41"/>
+      <c r="J117" s="41"/>
+      <c r="K117" s="41"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A118" s="14"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="10"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G117" s="35"/>
-      <c r="H117" s="36"/>
-      <c r="I117" s="35"/>
-      <c r="J117" s="35"/>
-      <c r="K117" s="35"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="30"/>
-      <c r="B118" s="32"/>
-      <c r="C118" s="33"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="34">
+      <c r="H118" s="10"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A119" s="14"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="10"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G118" s="35"/>
-      <c r="H118" s="36"/>
-      <c r="I118" s="35"/>
-      <c r="J118" s="35"/>
-      <c r="K118" s="35"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="30"/>
-      <c r="B119" s="32"/>
-      <c r="C119" s="33"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="34">
+      <c r="H119" s="10"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A120" s="14"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="10"/>
+      <c r="D120" s="8"/>
+      <c r="E120" s="8"/>
+      <c r="F120" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G119" s="35"/>
-      <c r="H119" s="36"/>
-      <c r="I119" s="35"/>
-      <c r="J119" s="35"/>
-      <c r="K119" s="35"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="30"/>
-      <c r="B120" s="32"/>
-      <c r="C120" s="33"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="34">
+      <c r="H120" s="10"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A121" s="14"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="10"/>
+      <c r="D121" s="8"/>
+      <c r="E121" s="8"/>
+      <c r="F121" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G120" s="35"/>
-      <c r="H120" s="36"/>
-      <c r="I120" s="35"/>
-      <c r="J120" s="35"/>
-      <c r="K120" s="35"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="30"/>
-      <c r="B121" s="32"/>
-      <c r="C121" s="33"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="34">
+      <c r="H121" s="10"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A122" s="27"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="10"/>
+      <c r="D122" s="28"/>
+      <c r="E122" s="28"/>
+      <c r="F122" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="G121" s="35"/>
-      <c r="H121" s="36"/>
-      <c r="I121" s="35"/>
-      <c r="J121" s="35"/>
-      <c r="K121" s="35"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="31"/>
-      <c r="B122" s="32"/>
-      <c r="C122" s="33"/>
-      <c r="D122" s="28"/>
-      <c r="E122" s="28"/>
-      <c r="F122" s="34">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="G122" s="35"/>
-      <c r="H122" s="36"/>
-      <c r="I122" s="35"/>
-      <c r="J122" s="35"/>
-      <c r="K122" s="35"/>
+      <c r="H122" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4588,11 +4646,13 @@
     <hyperlink ref="H113" r:id="rId100" display="https://www.grainger.com/product/BANJO-Inline-Strainer-Polypropylene-3ELX2" xr:uid="{5DDCF04D-0B2B-4400-9BF3-CBBD33627CF9}"/>
     <hyperlink ref="H114" r:id="rId101" display="https://www.grainger.com/product/BELL-GOSSETT-Water-Pressure-Reducing-Valve-6LFA3" xr:uid="{704D45CE-3BF8-44FB-A2F9-FBD42F90D381}"/>
     <hyperlink ref="H115" r:id="rId102" xr:uid="{DA2A078E-95DA-4F11-A662-702B09E6F14A}"/>
+    <hyperlink ref="H116" r:id="rId103" display="https://www.grainger.com/product/803H45?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{05215C5A-3A93-40D1-9E83-5B1ABEB0BD2B}"/>
+    <hyperlink ref="H117" r:id="rId104" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{0F353E44-E7EA-4190-9112-90CB38990103}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId103"/>
+  <pageSetup orientation="portrait" r:id="rId105"/>
   <tableParts count="1">
-    <tablePart r:id="rId104"/>
+    <tablePart r:id="rId106"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ig2\Desktop\SMR Thermal\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0CC7EB-E376-4619-9A43-94EBDD984420}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8EFCAD-E538-49A4-B1BC-B069F4E5ED81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -1333,8 +1333,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K122" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K122" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K116" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K116" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1671,7 +1671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M122"/>
+  <dimension ref="A1:M116"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -3349,7 +3349,7 @@
         <v>45.81</v>
       </c>
       <c r="F67" s="6">
-        <f t="shared" ref="F67:F109" si="1">D67*E67</f>
+        <f t="shared" ref="F67:F103" si="1">D67*E67</f>
         <v>45.81</v>
       </c>
       <c r="H67" s="23" t="s">
@@ -3971,7 +3971,7 @@
         <v>110</v>
       </c>
       <c r="F93" s="6">
-        <f t="shared" ref="F93:F101" si="2">D93*E93</f>
+        <f t="shared" ref="F93:F95" si="2">D93*E93</f>
         <v>110</v>
       </c>
       <c r="H93" s="24" t="s">
@@ -4027,519 +4027,447 @@
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A96" s="13"/>
+      <c r="A96" s="14" t="s">
+        <v>68</v>
+      </c>
       <c r="B96" s="26"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
+      <c r="C96" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="D96" s="8">
+        <v>3</v>
+      </c>
+      <c r="E96" s="8">
+        <v>2.1800000000000002</v>
+      </c>
       <c r="F96" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H96" s="24"/>
-    </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A97" s="13"/>
+        <f t="shared" si="1"/>
+        <v>6.5400000000000009</v>
+      </c>
+      <c r="H96" s="25" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A97" s="13" t="s">
+        <v>69</v>
+      </c>
       <c r="B97" s="26"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="7"/>
-      <c r="E97" s="7"/>
+      <c r="C97" s="13">
+        <v>156665159304</v>
+      </c>
+      <c r="D97" s="7">
+        <v>3</v>
+      </c>
+      <c r="E97" s="7">
+        <v>35.97</v>
+      </c>
       <c r="F97" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H97" s="24"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A98" s="13"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="7"/>
-      <c r="E98" s="7"/>
+        <f t="shared" si="1"/>
+        <v>107.91</v>
+      </c>
+      <c r="H97" s="24" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A98" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>240</v>
+      </c>
+      <c r="C98" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D98" s="8">
+        <v>3</v>
+      </c>
+      <c r="E98" s="8">
+        <v>167.42</v>
+      </c>
       <c r="F98" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H98" s="24"/>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A99" s="13"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
+        <f t="shared" si="1"/>
+        <v>502.26</v>
+      </c>
+      <c r="H98" s="23" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A99" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C99" s="13">
+        <v>316529</v>
+      </c>
+      <c r="D99" s="7">
+        <v>1</v>
+      </c>
+      <c r="E99" s="7">
+        <v>405</v>
+      </c>
       <c r="F99" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H99" s="24"/>
-    </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A100" s="13"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="7"/>
-      <c r="E100" s="7"/>
+        <f t="shared" si="1"/>
+        <v>405</v>
+      </c>
+      <c r="H99" s="22" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A100" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="C100" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D100" s="8">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8">
+        <v>37.4</v>
+      </c>
       <c r="F100" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H100" s="24"/>
-    </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A101" s="13"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="13"/>
-      <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
+        <f t="shared" si="1"/>
+        <v>37.4</v>
+      </c>
+      <c r="H100" s="23" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A101" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>244</v>
+      </c>
+      <c r="C101" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D101" s="7">
+        <v>1</v>
+      </c>
+      <c r="E101" s="7">
+        <v>20.91</v>
+      </c>
       <c r="F101" s="6">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="H101" s="24"/>
-    </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" si="1"/>
+        <v>20.91</v>
+      </c>
+      <c r="H101" s="22" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A102" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="B102" s="26"/>
-      <c r="C102" s="14" t="s">
-        <v>150</v>
+        <v>61</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="C102" s="11" t="s">
+        <v>74</v>
       </c>
       <c r="D102" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E102" s="8">
-        <v>2.1800000000000002</v>
+        <v>79.099999999999994</v>
       </c>
       <c r="F102" s="6">
         <f t="shared" si="1"/>
-        <v>6.5400000000000009</v>
-      </c>
-      <c r="H102" s="25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+        <v>79.099999999999994</v>
+      </c>
+      <c r="H102" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A103" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B103" s="26"/>
-      <c r="C103" s="13">
-        <v>156665159304</v>
+        <v>71</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>246</v>
+      </c>
+      <c r="C103" s="17" t="s">
+        <v>153</v>
       </c>
       <c r="D103" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E103" s="7">
-        <v>35.97</v>
+        <v>16.260000000000002</v>
       </c>
       <c r="F103" s="6">
         <f t="shared" si="1"/>
-        <v>107.91</v>
-      </c>
-      <c r="H103" s="24" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A104" s="14" t="s">
-        <v>67</v>
+        <v>16.260000000000002</v>
+      </c>
+      <c r="H103" s="22" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A104" s="27" t="s">
+        <v>258</v>
       </c>
       <c r="B104" s="26" t="s">
-        <v>240</v>
-      </c>
-      <c r="C104" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D104" s="8">
-        <v>3</v>
-      </c>
-      <c r="E104" s="8">
-        <v>167.42</v>
+        <v>254</v>
+      </c>
+      <c r="C104" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="D104" s="28">
+        <v>1</v>
+      </c>
+      <c r="E104" s="28">
+        <v>5.35</v>
       </c>
       <c r="F104" s="6">
-        <f t="shared" si="1"/>
-        <v>502.26</v>
-      </c>
-      <c r="H104" s="23" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A105" s="13" t="s">
-        <v>70</v>
+        <f>D104*E104</f>
+        <v>5.35</v>
+      </c>
+      <c r="H104" s="1" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A105" s="27" t="s">
+        <v>259</v>
       </c>
       <c r="B105" s="26" t="s">
-        <v>249</v>
-      </c>
-      <c r="C105" s="13">
-        <v>316529</v>
-      </c>
-      <c r="D105" s="7">
-        <v>1</v>
-      </c>
-      <c r="E105" s="7">
-        <v>405</v>
+        <v>256</v>
+      </c>
+      <c r="C105" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="D105" s="28">
+        <v>1</v>
+      </c>
+      <c r="E105" s="28">
+        <v>10.75</v>
       </c>
       <c r="F105" s="6">
-        <f t="shared" si="1"/>
-        <v>405</v>
-      </c>
-      <c r="H105" s="22" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A106" s="14" t="s">
-        <v>66</v>
+        <f>D105*E105</f>
+        <v>10.75</v>
+      </c>
+      <c r="H105" s="1" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A106" s="27" t="s">
+        <v>260</v>
       </c>
       <c r="B106" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="C106" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D106" s="8">
-        <v>1</v>
-      </c>
-      <c r="E106" s="8">
-        <v>37.4</v>
+        <v>263</v>
+      </c>
+      <c r="C106" s="10" t="s">
+        <v>262</v>
+      </c>
+      <c r="D106" s="28">
+        <v>1</v>
+      </c>
+      <c r="E106" s="28">
+        <v>6.68</v>
       </c>
       <c r="F106" s="6">
-        <f t="shared" si="1"/>
-        <v>37.4</v>
-      </c>
-      <c r="H106" s="23" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A107" s="13" t="s">
-        <v>17</v>
+        <v>7.96</v>
+      </c>
+      <c r="H106" s="1" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A107" s="14" t="s">
+        <v>276</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>244</v>
-      </c>
-      <c r="C107" s="12" t="s">
-        <v>152</v>
-      </c>
-      <c r="D107" s="7">
-        <v>1</v>
-      </c>
-      <c r="E107" s="7">
-        <v>20.91</v>
+        <v>277</v>
+      </c>
+      <c r="C107" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D107" s="8">
+        <v>1</v>
+      </c>
+      <c r="E107" s="8">
+        <v>28.78</v>
       </c>
       <c r="F107" s="6">
-        <f t="shared" si="1"/>
-        <v>20.91</v>
-      </c>
-      <c r="H107" s="22" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+        <f t="shared" ref="F107:F109" si="3">D107*E107</f>
+        <v>28.78</v>
+      </c>
+      <c r="H107" s="1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A108" s="14" t="s">
-        <v>61</v>
+        <v>280</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>251</v>
-      </c>
-      <c r="C108" s="11" t="s">
-        <v>74</v>
+        <v>283</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>282</v>
       </c>
       <c r="D108" s="8">
         <v>1</v>
       </c>
       <c r="E108" s="8">
-        <v>79.099999999999994</v>
+        <v>146.18</v>
       </c>
       <c r="F108" s="6">
-        <f t="shared" si="1"/>
-        <v>79.099999999999994</v>
-      </c>
-      <c r="H108" s="23" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A109" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B109" s="26" t="s">
-        <v>246</v>
-      </c>
-      <c r="C109" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="D109" s="7">
-        <v>1</v>
-      </c>
-      <c r="E109" s="7">
-        <v>16.260000000000002</v>
-      </c>
-      <c r="F109" s="6">
-        <f t="shared" si="1"/>
-        <v>16.260000000000002</v>
-      </c>
-      <c r="H109" s="22" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A110" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="B110" s="26" t="s">
-        <v>254</v>
-      </c>
-      <c r="C110" s="10" t="s">
-        <v>253</v>
-      </c>
-      <c r="D110" s="28">
-        <v>1</v>
-      </c>
-      <c r="E110" s="28">
-        <v>5.35</v>
-      </c>
-      <c r="F110" s="6">
-        <f>D110*E110</f>
-        <v>5.35</v>
-      </c>
-      <c r="H110" s="1" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A111" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="B111" s="26" t="s">
-        <v>256</v>
-      </c>
-      <c r="C111" s="10" t="s">
-        <v>257</v>
-      </c>
-      <c r="D111" s="28">
-        <v>1</v>
-      </c>
-      <c r="E111" s="28">
-        <v>10.75</v>
-      </c>
-      <c r="F111" s="6">
-        <f>D111*E111</f>
-        <v>10.75</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A112" s="27" t="s">
-        <v>260</v>
-      </c>
-      <c r="B112" s="26" t="s">
-        <v>263</v>
-      </c>
-      <c r="C112" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="D112" s="28">
-        <v>1</v>
-      </c>
-      <c r="E112" s="28">
-        <v>6.68</v>
-      </c>
-      <c r="F112" s="6">
-        <v>7.96</v>
-      </c>
-      <c r="H112" s="1" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A113" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="B113" s="26" t="s">
-        <v>277</v>
-      </c>
-      <c r="C113" s="10" t="s">
-        <v>278</v>
-      </c>
-      <c r="D113" s="8">
-        <v>1</v>
-      </c>
-      <c r="E113" s="8">
-        <v>28.78</v>
-      </c>
-      <c r="F113" s="6">
-        <f t="shared" ref="F113:F115" si="3">D113*E113</f>
-        <v>28.78</v>
-      </c>
-      <c r="H113" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A114" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="B114" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="C114" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="D114" s="8">
-        <v>1</v>
-      </c>
-      <c r="E114" s="8">
-        <v>146.18</v>
-      </c>
-      <c r="F114" s="6">
         <f t="shared" si="3"/>
         <v>146.18</v>
       </c>
-      <c r="H114" s="1" t="s">
+      <c r="H108" s="1" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A115" s="14" t="s">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A109" s="14" t="s">
         <v>285</v>
       </c>
-      <c r="B115" s="26" t="s">
+      <c r="B109" s="26" t="s">
         <v>284</v>
       </c>
-      <c r="C115" s="10" t="s">
+      <c r="C109" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="D115" s="8">
-        <v>1</v>
-      </c>
-      <c r="E115" s="8">
+      <c r="D109" s="8">
+        <v>1</v>
+      </c>
+      <c r="E109" s="8">
         <v>36.06</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F109" s="6">
         <f t="shared" si="3"/>
         <v>36.06</v>
       </c>
-      <c r="H115" s="30" t="s">
+      <c r="H109" s="30" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="116" spans="1:11" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="31" t="s">
+    <row r="110" spans="1:11" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="31" t="s">
         <v>288</v>
       </c>
-      <c r="B116" s="32" t="s">
+      <c r="B110" s="32" t="s">
         <v>289</v>
       </c>
-      <c r="C116" s="33" t="s">
+      <c r="C110" s="33" t="s">
         <v>290</v>
       </c>
-      <c r="D116" s="34">
+      <c r="D110" s="34">
         <v>2</v>
       </c>
-      <c r="E116" s="34">
+      <c r="E110" s="34">
         <v>7.82</v>
       </c>
-      <c r="F116" s="35">
-        <f t="shared" ref="F116:F122" si="4">D116*E116</f>
+      <c r="F110" s="35">
+        <f t="shared" ref="F110:F116" si="4">D110*E110</f>
         <v>15.64</v>
       </c>
-      <c r="H116" s="37" t="s">
+      <c r="H110" s="37" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="38" t="s">
+    <row r="111" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B117" s="43" t="s">
+      <c r="B111" s="43" t="s">
         <v>292</v>
       </c>
-      <c r="C117" s="44" t="s">
+      <c r="C111" s="44" t="s">
         <v>293</v>
       </c>
-      <c r="D117" s="39">
+      <c r="D111" s="39">
         <v>2</v>
       </c>
-      <c r="E117" s="39">
+      <c r="E111" s="39">
         <v>14.99</v>
       </c>
-      <c r="F117" s="40">
+      <c r="F111" s="40">
         <f t="shared" si="4"/>
         <v>29.98</v>
       </c>
-      <c r="G117" s="41"/>
-      <c r="H117" s="42" t="s">
+      <c r="G111" s="41"/>
+      <c r="H111" s="42" t="s">
         <v>294</v>
       </c>
-      <c r="I117" s="41"/>
-      <c r="J117" s="41"/>
-      <c r="K117" s="41"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A118" s="14"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="10"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
-      <c r="F118" s="6">
+      <c r="I111" s="41"/>
+      <c r="J111" s="41"/>
+      <c r="K111" s="41"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A112" s="14"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="10"/>
+      <c r="D112" s="8"/>
+      <c r="E112" s="8"/>
+      <c r="F112" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H118" s="10"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A119" s="14"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="10"/>
-      <c r="D119" s="8"/>
-      <c r="E119" s="8"/>
-      <c r="F119" s="6">
+      <c r="H112" s="10"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A113" s="14"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="10"/>
+      <c r="D113" s="8"/>
+      <c r="E113" s="8"/>
+      <c r="F113" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H119" s="10"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A120" s="14"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="8"/>
-      <c r="E120" s="8"/>
-      <c r="F120" s="6">
+      <c r="H113" s="10"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A114" s="14"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="10"/>
+      <c r="D114" s="8"/>
+      <c r="E114" s="8"/>
+      <c r="F114" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H120" s="10"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A121" s="14"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="10"/>
-      <c r="D121" s="8"/>
-      <c r="E121" s="8"/>
-      <c r="F121" s="6">
+      <c r="H114" s="10"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A115" s="14"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="10"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H121" s="10"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A122" s="27"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="10"/>
-      <c r="D122" s="28"/>
-      <c r="E122" s="28"/>
-      <c r="F122" s="6">
+      <c r="H115" s="10"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A116" s="27"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="10"/>
+      <c r="D116" s="28"/>
+      <c r="E116" s="28"/>
+      <c r="F116" s="6">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="H122" s="10"/>
+      <c r="H116" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4632,22 +4560,22 @@
     <hyperlink ref="H89" r:id="rId86" display="https://www.grainger.com/product/1VFX8?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=6d4e1d7881c4014dc580a65ce33a0287e6d4e842f558a81fadd5dcde7a752909&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{460DB0C6-014B-408D-A50E-7C7CB6F31C51}"/>
     <hyperlink ref="H90" r:id="rId87" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{B046FF95-BF93-46C9-B8CE-FB723F36F53A}"/>
     <hyperlink ref="H91" r:id="rId88" display="https://www.grainger.com/product/Hex-Tap-Bolt-Stainless-Steel-41UH04?gucid=n:n:em:owned:wwg:deliveryConfirmation:apz_1&amp;emcid=body:pdpurl" xr:uid="{5ACA225F-14EA-4C12-8992-27C2A205D0A2}"/>
-    <hyperlink ref="H105" r:id="rId89" xr:uid="{66B68E33-6FB6-4B9E-8DEE-AD4543BA3948}"/>
-    <hyperlink ref="H104" r:id="rId90" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{E0383BBC-B224-42C5-8E0D-F57DE49C5FA3}"/>
-    <hyperlink ref="H106" r:id="rId91" xr:uid="{A3D63FAB-C850-40A1-A637-DF41091272C8}"/>
-    <hyperlink ref="H107" r:id="rId92" display="https://www.grainger.com/product/20XM58?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=5fbed57f928e0d20c3753de78a2b9a38ffd20234e126526a2f6d6b4fe4e772db&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C07356E-8DE4-40F2-A1AD-4E8492786388}"/>
-    <hyperlink ref="H108" r:id="rId93" xr:uid="{94CC04D7-EB9A-450B-BB5C-C756BC4DE898}"/>
-    <hyperlink ref="H109" r:id="rId94" display="https://www.grainger.com/product/IGUS-Flanged-Sleeve-Bearing-Polymer-2NCK6" xr:uid="{83384CCF-7FBA-4E7B-9A1D-1C877A885273}"/>
-    <hyperlink ref="H110" r:id="rId95" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
-    <hyperlink ref="H111" r:id="rId96" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
-    <hyperlink ref="H112" r:id="rId97" xr:uid="{FDEFAFD3-3687-4641-964A-8BC9B3E42512}"/>
+    <hyperlink ref="H99" r:id="rId89" xr:uid="{66B68E33-6FB6-4B9E-8DEE-AD4543BA3948}"/>
+    <hyperlink ref="H98" r:id="rId90" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{E0383BBC-B224-42C5-8E0D-F57DE49C5FA3}"/>
+    <hyperlink ref="H100" r:id="rId91" xr:uid="{A3D63FAB-C850-40A1-A637-DF41091272C8}"/>
+    <hyperlink ref="H101" r:id="rId92" display="https://www.grainger.com/product/20XM58?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=5fbed57f928e0d20c3753de78a2b9a38ffd20234e126526a2f6d6b4fe4e772db&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C07356E-8DE4-40F2-A1AD-4E8492786388}"/>
+    <hyperlink ref="H102" r:id="rId93" xr:uid="{94CC04D7-EB9A-450B-BB5C-C756BC4DE898}"/>
+    <hyperlink ref="H103" r:id="rId94" display="https://www.grainger.com/product/IGUS-Flanged-Sleeve-Bearing-Polymer-2NCK6" xr:uid="{83384CCF-7FBA-4E7B-9A1D-1C877A885273}"/>
+    <hyperlink ref="H104" r:id="rId95" display="https://www.grainger.com/product/Hex-Nut-Std-Hex-2FE69" xr:uid="{85183601-0793-4417-9C08-9D53A5FEB9B5}"/>
+    <hyperlink ref="H105" r:id="rId96" display="https://www.grainger.com/product/Mil-Spec-Flat-Washer-18-8-2DNV3" xr:uid="{FC3AB918-B994-4AB5-AFC0-90ECDBC2A4C8}"/>
+    <hyperlink ref="H106" r:id="rId97" xr:uid="{FDEFAFD3-3687-4641-964A-8BC9B3E42512}"/>
     <hyperlink ref="H95" r:id="rId98" xr:uid="{29622D1D-FB83-4317-A033-D7DD9D94A271}"/>
     <hyperlink ref="H94" r:id="rId99" xr:uid="{5FC8DB1C-6249-4551-B238-6394EA039EB9}"/>
-    <hyperlink ref="H113" r:id="rId100" display="https://www.grainger.com/product/BANJO-Inline-Strainer-Polypropylene-3ELX2" xr:uid="{5DDCF04D-0B2B-4400-9BF3-CBBD33627CF9}"/>
-    <hyperlink ref="H114" r:id="rId101" display="https://www.grainger.com/product/BELL-GOSSETT-Water-Pressure-Reducing-Valve-6LFA3" xr:uid="{704D45CE-3BF8-44FB-A2F9-FBD42F90D381}"/>
-    <hyperlink ref="H115" r:id="rId102" xr:uid="{DA2A078E-95DA-4F11-A662-702B09E6F14A}"/>
-    <hyperlink ref="H116" r:id="rId103" display="https://www.grainger.com/product/803H45?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{05215C5A-3A93-40D1-9E83-5B1ABEB0BD2B}"/>
-    <hyperlink ref="H117" r:id="rId104" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{0F353E44-E7EA-4190-9112-90CB38990103}"/>
+    <hyperlink ref="H107" r:id="rId100" display="https://www.grainger.com/product/BANJO-Inline-Strainer-Polypropylene-3ELX2" xr:uid="{5DDCF04D-0B2B-4400-9BF3-CBBD33627CF9}"/>
+    <hyperlink ref="H108" r:id="rId101" display="https://www.grainger.com/product/BELL-GOSSETT-Water-Pressure-Reducing-Valve-6LFA3" xr:uid="{704D45CE-3BF8-44FB-A2F9-FBD42F90D381}"/>
+    <hyperlink ref="H109" r:id="rId102" xr:uid="{DA2A078E-95DA-4F11-A662-702B09E6F14A}"/>
+    <hyperlink ref="H110" r:id="rId103" display="https://www.grainger.com/product/803H45?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{05215C5A-3A93-40D1-9E83-5B1ABEB0BD2B}"/>
+    <hyperlink ref="H111" r:id="rId104" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{0F353E44-E7EA-4190-9112-90CB38990103}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId105"/>

--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ig2\Desktop\SMR Thermal\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E8EFCAD-E538-49A4-B1BC-B069F4E5ED81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{4E8EFCAD-E538-49A4-B1BC-B069F4E5ED81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8E7CF4-B76E-48DF-B4ED-3359B809F3FC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="298">
   <si>
     <t>Total Cost</t>
   </si>
@@ -866,9 +866,6 @@
     <t>F3U133B16</t>
   </si>
   <si>
-    <t>Water Filter (TO ORDER)</t>
-  </si>
-  <si>
     <t>BANJO Inline Strainer: Polypropylene, 3/4 in, NPT, Mesh, 0.007 in Screen Size, 4 1/4 in Ht, 3 in Lg</t>
   </si>
   <si>
@@ -878,9 +875,6 @@
     <t>BANJO, Polypropylene, 3/4 in, Inline Strainer - 3ELX2|LSTM075-80C - Grainger</t>
   </si>
   <si>
-    <t>Pressure Reducer Valve (TO ORDER)</t>
-  </si>
-  <si>
     <t>BELL &amp; GOSSETT, NPT x NPT, 3/4 in Pipe Size, Water Pressure Reducing Valve - 6LFA3|110196LF - Grainger</t>
   </si>
   <si>
@@ -893,18 +887,12 @@
     <t>APOLLO Relief Valve: FNPT x FNPT, 3/4 in x 3/4 in, Bronze, 94 psi Max. Op Pressure</t>
   </si>
   <si>
-    <t>Pressure Relief Valve (TO ORDER)</t>
-  </si>
-  <si>
     <t>804Z55</t>
   </si>
   <si>
     <t>https://www.grainger.com/product/APOLLO-Relief-Valve-FNPT-x-FNPT-804Z55</t>
   </si>
   <si>
-    <t>Nichrome Rod (TO ORDER)</t>
-  </si>
-  <si>
     <t>360 Brass Rod: 3/8 in Outside Dia, 12 in Overall Lg, H02, Mill, 45,000 psi Yield Strength, Inch</t>
   </si>
   <si>
@@ -921,6 +909,27 @@
   </si>
   <si>
     <t>WEATHERHEAD, 3/8 in OD x 3/8 in OD Fitting Size, Compression x Compression, Compression Fitting Union - 20KF99|62X6 - Grainger</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nichrome Rod </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pressure Relief Valve </t>
+  </si>
+  <si>
+    <t>Pressure Reducer Valve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water Filter </t>
+  </si>
+  <si>
+    <t>3/8 in OD x 3/4 in Pipe Fitting Size, Brass, Compression Fitting Coupling - 20XM55|700068-0612 - Grainger</t>
+  </si>
+  <si>
+    <t>APPROVED VENDOR Compression Fitting Coupling: 3/8 in OD x 3/4 in Pipe Fitting Size, Brass</t>
+  </si>
+  <si>
+    <t>20XM55</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1198,19 +1207,16 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1672,24 +1678,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M116"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.08984375" customWidth="1"/>
-    <col min="3" max="3" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.453125" customWidth="1"/>
-    <col min="11" max="11" width="62.453125" customWidth="1"/>
-    <col min="12" max="12" width="55.6328125" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.6640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1724,7 +1730,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="13" t="s">
         <v>10</v>
       </c>
@@ -1750,7 +1756,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14" t="s">
         <v>11</v>
       </c>
@@ -1776,7 +1782,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
         <v>12</v>
       </c>
@@ -1801,7 +1807,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
         <v>10</v>
       </c>
@@ -1827,7 +1833,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="13" t="s">
         <v>10</v>
       </c>
@@ -1853,7 +1859,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="14" t="s">
         <v>13</v>
       </c>
@@ -1881,7 +1887,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="13" t="s">
         <v>14</v>
       </c>
@@ -1907,7 +1913,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
         <v>15</v>
       </c>
@@ -1934,7 +1940,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="13" t="s">
         <v>16</v>
       </c>
@@ -1959,7 +1965,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="14" t="s">
         <v>17</v>
       </c>
@@ -1985,7 +1991,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="13" t="s">
         <v>18</v>
       </c>
@@ -2009,7 +2015,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="14" t="s">
         <v>19</v>
       </c>
@@ -2035,7 +2041,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="13" t="s">
         <v>20</v>
       </c>
@@ -2061,7 +2067,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="14" t="s">
         <v>21</v>
       </c>
@@ -2087,7 +2093,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="13" t="s">
         <v>22</v>
       </c>
@@ -2113,7 +2119,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="14" t="s">
         <v>23</v>
       </c>
@@ -2139,7 +2145,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="13" t="s">
         <v>24</v>
       </c>
@@ -2163,7 +2169,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="14" t="s">
         <v>25</v>
       </c>
@@ -2189,7 +2195,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="13" t="s">
         <v>26</v>
       </c>
@@ -2215,7 +2221,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="14" t="s">
         <v>27</v>
       </c>
@@ -2241,7 +2247,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="13" t="s">
         <v>28</v>
       </c>
@@ -2267,7 +2273,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="14" t="s">
         <v>29</v>
       </c>
@@ -2293,7 +2299,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="13" t="s">
         <v>30</v>
       </c>
@@ -2319,7 +2325,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="14" t="s">
         <v>28</v>
       </c>
@@ -2345,7 +2351,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="13" t="s">
         <v>31</v>
       </c>
@@ -2371,7 +2377,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="14" t="s">
         <v>17</v>
       </c>
@@ -2396,7 +2402,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="13" t="s">
         <v>32</v>
       </c>
@@ -2420,7 +2426,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="14" t="s">
         <v>33</v>
       </c>
@@ -2444,7 +2450,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="13" t="s">
         <v>34</v>
       </c>
@@ -2468,7 +2474,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="14" t="s">
         <v>35</v>
       </c>
@@ -2492,7 +2498,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="13" t="s">
         <v>35</v>
       </c>
@@ -2516,7 +2522,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="14" t="s">
         <v>36</v>
       </c>
@@ -2540,7 +2546,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="13" t="s">
         <v>36</v>
       </c>
@@ -2564,7 +2570,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="14" t="s">
         <v>37</v>
       </c>
@@ -2588,7 +2594,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="13" t="s">
         <v>37</v>
       </c>
@@ -2612,7 +2618,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="14" t="s">
         <v>35</v>
       </c>
@@ -2636,7 +2642,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="13" t="s">
         <v>38</v>
       </c>
@@ -2660,7 +2666,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="14" t="s">
         <v>38</v>
       </c>
@@ -2684,7 +2690,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>12</v>
       </c>
@@ -2708,7 +2714,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>39</v>
       </c>
@@ -2732,7 +2738,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>40</v>
       </c>
@@ -2756,7 +2762,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>41</v>
       </c>
@@ -2780,7 +2786,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="13" t="s">
         <v>42</v>
       </c>
@@ -2804,7 +2810,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="14" t="s">
         <v>43</v>
       </c>
@@ -2828,7 +2834,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="13" t="s">
         <v>44</v>
       </c>
@@ -2852,7 +2858,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="14" t="s">
         <v>45</v>
       </c>
@@ -2876,7 +2882,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="13" t="s">
         <v>45</v>
       </c>
@@ -2900,7 +2906,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="14" t="s">
         <v>46</v>
       </c>
@@ -2924,7 +2930,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="13" t="s">
         <v>47</v>
       </c>
@@ -2948,7 +2954,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="14" t="s">
         <v>46</v>
       </c>
@@ -2972,7 +2978,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="13" t="s">
         <v>46</v>
       </c>
@@ -2996,7 +3002,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="14" t="s">
         <v>48</v>
       </c>
@@ -3020,7 +3026,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="13" t="s">
         <v>49</v>
       </c>
@@ -3044,7 +3050,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="14" t="s">
         <v>50</v>
       </c>
@@ -3068,7 +3074,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="13" t="s">
         <v>35</v>
       </c>
@@ -3092,7 +3098,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>48</v>
       </c>
@@ -3116,7 +3122,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="13" t="s">
         <v>39</v>
       </c>
@@ -3140,7 +3146,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="14" t="s">
         <v>12</v>
       </c>
@@ -3164,7 +3170,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="13" t="s">
         <v>51</v>
       </c>
@@ -3188,7 +3194,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="14" t="s">
         <v>46</v>
       </c>
@@ -3212,7 +3218,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="13" t="s">
         <v>52</v>
       </c>
@@ -3236,7 +3242,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="14" t="s">
         <v>52</v>
       </c>
@@ -3260,7 +3266,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="13" t="s">
         <v>48</v>
       </c>
@@ -3284,7 +3290,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="14" t="s">
         <v>45</v>
       </c>
@@ -3308,7 +3314,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="13" t="s">
         <v>37</v>
       </c>
@@ -3332,7 +3338,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="14" t="s">
         <v>53</v>
       </c>
@@ -3356,7 +3362,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="13" t="s">
         <v>45</v>
       </c>
@@ -3380,7 +3386,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="14" t="s">
         <v>54</v>
       </c>
@@ -3404,7 +3410,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="13" t="s">
         <v>54</v>
       </c>
@@ -3428,7 +3434,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="14" t="s">
         <v>55</v>
       </c>
@@ -3452,7 +3458,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="13" t="s">
         <v>46</v>
       </c>
@@ -3476,7 +3482,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="14" t="s">
         <v>56</v>
       </c>
@@ -3500,7 +3506,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="13" t="s">
         <v>57</v>
       </c>
@@ -3524,7 +3530,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="14" t="s">
         <v>11</v>
       </c>
@@ -3548,7 +3554,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="13" t="s">
         <v>58</v>
       </c>
@@ -3572,7 +3578,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="14" t="s">
         <v>46</v>
       </c>
@@ -3596,7 +3602,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="13" t="s">
         <v>39</v>
       </c>
@@ -3620,7 +3626,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="14" t="s">
         <v>59</v>
       </c>
@@ -3644,7 +3650,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="13" t="s">
         <v>60</v>
       </c>
@@ -3668,7 +3674,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="14" t="s">
         <v>61</v>
       </c>
@@ -3692,7 +3698,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="13" t="s">
         <v>62</v>
       </c>
@@ -3716,7 +3722,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="14" t="s">
         <v>63</v>
       </c>
@@ -3740,7 +3746,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="13" t="s">
         <v>64</v>
       </c>
@@ -3764,7 +3770,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="14" t="s">
         <v>35</v>
       </c>
@@ -3788,7 +3794,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="13" t="s">
         <v>63</v>
       </c>
@@ -3812,7 +3818,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="14" t="s">
         <v>65</v>
       </c>
@@ -3836,7 +3842,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="13" t="s">
         <v>63</v>
       </c>
@@ -3860,7 +3866,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="14" t="s">
         <v>66</v>
       </c>
@@ -3884,7 +3890,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3908,7 +3914,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="14" t="s">
         <v>46</v>
       </c>
@@ -3932,7 +3938,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -3954,7 +3960,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -3978,7 +3984,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4002,7 +4008,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4026,7 +4032,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="14" t="s">
         <v>68</v>
       </c>
@@ -4048,7 +4054,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4070,7 +4076,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="14" t="s">
         <v>67</v>
       </c>
@@ -4094,7 +4100,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4118,7 +4124,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="14" t="s">
         <v>66</v>
       </c>
@@ -4142,7 +4148,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4166,7 +4172,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="14" t="s">
         <v>61</v>
       </c>
@@ -4190,7 +4196,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4214,7 +4220,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="27" t="s">
         <v>258</v>
       </c>
@@ -4238,7 +4244,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="27" t="s">
         <v>259</v>
       </c>
@@ -4262,7 +4268,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="27" t="s">
         <v>260</v>
       </c>
@@ -4285,15 +4291,15 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="14" t="s">
+        <v>294</v>
+      </c>
+      <c r="B107" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="B107" s="26" t="s">
+      <c r="C107" s="10" t="s">
         <v>277</v>
-      </c>
-      <c r="C107" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="D107" s="8">
         <v>1</v>
@@ -4306,18 +4312,18 @@
         <v>28.78</v>
       </c>
       <c r="H107" s="1" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.35">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>281</v>
+      </c>
+      <c r="C108" s="10" t="s">
         <v>280</v>
-      </c>
-      <c r="B108" s="26" t="s">
-        <v>283</v>
-      </c>
-      <c r="C108" s="10" t="s">
-        <v>282</v>
       </c>
       <c r="D108" s="8">
         <v>1</v>
@@ -4330,18 +4336,18 @@
         <v>146.18</v>
       </c>
       <c r="H108" s="1" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.35">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="14" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C109" s="10" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D109" s="8">
         <v>1</v>
@@ -4354,18 +4360,18 @@
         <v>36.06</v>
       </c>
       <c r="H109" s="30" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="31" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B110" s="32" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="C110" s="33" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D110" s="34">
         <v>2</v>
@@ -4378,18 +4384,18 @@
         <v>15.64</v>
       </c>
       <c r="H110" s="37" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B111" s="43" t="s">
-        <v>292</v>
-      </c>
-      <c r="C111" s="44" t="s">
-        <v>293</v>
+      <c r="B111" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="C111" s="43" t="s">
+        <v>289</v>
       </c>
       <c r="D111" s="39">
         <v>2</v>
@@ -4401,15 +4407,15 @@
         <f t="shared" si="4"/>
         <v>29.98</v>
       </c>
-      <c r="G111" s="41"/>
-      <c r="H111" s="42" t="s">
-        <v>294</v>
-      </c>
-      <c r="I111" s="41"/>
-      <c r="J111" s="41"/>
-      <c r="K111" s="41"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="G111" s="26"/>
+      <c r="H111" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="I111" s="26"/>
+      <c r="J111" s="26"/>
+      <c r="K111" s="26"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="14"/>
       <c r="B112" s="26"/>
       <c r="C112" s="10"/>
@@ -4421,7 +4427,7 @@
       </c>
       <c r="H112" s="10"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="14"/>
       <c r="B113" s="26"/>
       <c r="C113" s="10"/>
@@ -4433,41 +4439,77 @@
       </c>
       <c r="H113" s="10"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A114" s="14"/>
-      <c r="B114" s="26"/>
-      <c r="C114" s="10"/>
-      <c r="D114" s="8"/>
-      <c r="E114" s="8"/>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A114" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>251</v>
+      </c>
+      <c r="C114" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D114" s="8">
+        <v>1</v>
+      </c>
+      <c r="E114" s="8">
+        <v>79.099999999999994</v>
+      </c>
       <c r="F114" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H114" s="10"/>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A115" s="14"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="10"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
+        <v>79.099999999999994</v>
+      </c>
+      <c r="H114" s="23" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A115" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>296</v>
+      </c>
+      <c r="C115" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D115" s="8">
+        <v>1</v>
+      </c>
+      <c r="E115" s="8">
+        <v>18.309999999999999</v>
+      </c>
       <c r="F115" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H115" s="10"/>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A116" s="27"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="10"/>
-      <c r="D116" s="28"/>
-      <c r="E116" s="28"/>
+        <v>18.309999999999999</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A116" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>250</v>
+      </c>
+      <c r="C116" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="D116" s="8">
+        <v>1</v>
+      </c>
+      <c r="E116" s="8">
+        <v>37.4</v>
+      </c>
       <c r="F116" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H116" s="10"/>
+        <v>37.4</v>
+      </c>
+      <c r="H116" s="23" t="s">
+        <v>243</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4576,11 +4618,14 @@
     <hyperlink ref="H109" r:id="rId102" xr:uid="{DA2A078E-95DA-4F11-A662-702B09E6F14A}"/>
     <hyperlink ref="H110" r:id="rId103" display="https://www.grainger.com/product/803H45?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{05215C5A-3A93-40D1-9E83-5B1ABEB0BD2B}"/>
     <hyperlink ref="H111" r:id="rId104" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{0F353E44-E7EA-4190-9112-90CB38990103}"/>
+    <hyperlink ref="H114" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
+    <hyperlink ref="H115" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
+    <hyperlink ref="H116" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId105"/>
+  <pageSetup orientation="portrait" r:id="rId108"/>
   <tableParts count="1">
-    <tablePart r:id="rId106"/>
+    <tablePart r:id="rId109"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="13_ncr:1_{4E8EFCAD-E538-49A4-B1BC-B069F4E5ED81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AC8E7CF4-B76E-48DF-B4ED-3359B809F3FC}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32175D1D-5F07-4B8C-9BA3-FC15C9F4C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -1098,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1131,9 +1131,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1158,9 +1155,6 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1170,59 +1164,94 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
   </cellXfs>
@@ -1339,8 +1368,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K116" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K116" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K114" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K114" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1677,25 +1706,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M116"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M114"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.44140625" customWidth="1"/>
-    <col min="11" max="11" width="62.44140625" customWidth="1"/>
-    <col min="12" max="12" width="55.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.42578125" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" customWidth="1"/>
+    <col min="12" max="12" width="55.7109375" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1730,14 +1759,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="13" t="s">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="23" t="s">
         <v>247</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>92012988</v>
       </c>
       <c r="D2" s="7">
@@ -1751,19 +1780,19 @@
         <v>25.58</v>
       </c>
       <c r="G2" s="5"/>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="20" t="s">
         <v>155</v>
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14" t="s">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="26" t="s">
+      <c r="B3" s="23" t="s">
         <v>156</v>
       </c>
-      <c r="C3" s="14">
+      <c r="C3" s="13">
         <v>67436964</v>
       </c>
       <c r="D3" s="8">
@@ -1777,19 +1806,19 @@
         <v>17.100000000000001</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="23" t="s">
+      <c r="H3" s="21" t="s">
         <v>156</v>
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="23" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="15">
+      <c r="C4" s="14">
         <v>67473967</v>
       </c>
       <c r="D4" s="7">
@@ -1803,18 +1832,18 @@
         <v>4.6999999999999993</v>
       </c>
       <c r="G4" s="5"/>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="20" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="14" t="s">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="23" t="s">
         <v>158</v>
       </c>
-      <c r="C5" s="16">
+      <c r="C5" s="15">
         <v>99176795</v>
       </c>
       <c r="D5" s="8">
@@ -1828,19 +1857,19 @@
         <v>32.700000000000003</v>
       </c>
       <c r="G5" s="5"/>
-      <c r="H5" s="23" t="s">
+      <c r="H5" s="21" t="s">
         <v>158</v>
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="13" t="s">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="26" t="s">
+      <c r="B6" s="23" t="s">
         <v>159</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="7">
@@ -1854,19 +1883,19 @@
         <v>77.820000000000007</v>
       </c>
       <c r="G6" s="5"/>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="20" t="s">
         <v>159</v>
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="14" t="s">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="26" t="s">
+      <c r="B7" s="23" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>73</v>
       </c>
       <c r="D7" s="8">
@@ -1880,21 +1909,21 @@
         <v>31.23</v>
       </c>
       <c r="G7" s="5"/>
-      <c r="H7" s="23" t="s">
+      <c r="H7" s="21" t="s">
         <v>160</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="23" t="s">
         <v>161</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C8" s="16" t="s">
         <v>74</v>
       </c>
       <c r="D8" s="7">
@@ -1908,19 +1937,19 @@
         <v>93.93</v>
       </c>
       <c r="G8" s="5"/>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="20" t="s">
         <v>161</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="14" t="s">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="B9" s="26" t="s">
+      <c r="B9" s="23" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>75</v>
       </c>
       <c r="D9" s="8">
@@ -1934,20 +1963,20 @@
         <v>5.99</v>
       </c>
       <c r="G9" s="5"/>
-      <c r="H9" s="23" t="s">
+      <c r="H9" s="21" t="s">
         <v>162</v>
       </c>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="13" t="s">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="16" t="s">
         <v>76</v>
       </c>
       <c r="D10" s="7">
@@ -1961,18 +1990,18 @@
         <v>41.22</v>
       </c>
       <c r="G10" s="5"/>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="20" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="14" t="s">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B11" s="26" t="s">
+      <c r="B11" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>77</v>
       </c>
       <c r="D11" s="8">
@@ -1986,17 +2015,17 @@
         <v>60.89</v>
       </c>
       <c r="G11" s="5"/>
-      <c r="H11" s="23" t="s">
+      <c r="H11" s="21" t="s">
         <v>164</v>
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="13" t="s">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="13" t="s">
+      <c r="B12" s="23"/>
+      <c r="C12" s="12" t="s">
         <v>78</v>
       </c>
       <c r="D12" s="7">
@@ -2010,19 +2039,19 @@
         <v>27.83</v>
       </c>
       <c r="G12" s="5"/>
-      <c r="H12" s="24" t="s">
+      <c r="H12" s="22" t="s">
         <v>78</v>
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="14" t="s">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="26" t="s">
+      <c r="B13" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <v>316533</v>
       </c>
       <c r="D13" s="8">
@@ -2036,19 +2065,19 @@
         <v>370</v>
       </c>
       <c r="G13" s="5"/>
-      <c r="H13" s="23" t="s">
+      <c r="H13" s="21" t="s">
         <v>165</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="26" t="s">
+      <c r="B14" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="16">
         <v>316530</v>
       </c>
       <c r="D14" s="7">
@@ -2062,19 +2091,19 @@
         <v>312</v>
       </c>
       <c r="G14" s="5"/>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="20" t="s">
         <v>166</v>
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="14" t="s">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <v>314802</v>
       </c>
       <c r="D15" s="8">
@@ -2088,19 +2117,19 @@
         <v>5.9</v>
       </c>
       <c r="G15" s="5"/>
-      <c r="H15" s="23" t="s">
+      <c r="H15" s="21" t="s">
         <v>167</v>
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="13" t="s">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="26" t="s">
+      <c r="B16" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C16" s="20">
+      <c r="C16" s="19">
         <v>164598</v>
       </c>
       <c r="D16" s="7">
@@ -2114,19 +2143,19 @@
         <v>1610</v>
       </c>
       <c r="G16" s="5"/>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="20" t="s">
         <v>168</v>
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="14" t="s">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="26" t="s">
+      <c r="B17" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="13" t="s">
         <v>79</v>
       </c>
       <c r="D17" s="8">
@@ -2140,17 +2169,17 @@
         <v>99.25</v>
       </c>
       <c r="G17" s="5"/>
-      <c r="H17" s="23" t="s">
+      <c r="H17" s="21" t="s">
         <v>169</v>
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="13" t="s">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="26"/>
-      <c r="C18" s="13" t="s">
+      <c r="B18" s="23"/>
+      <c r="C18" s="12" t="s">
         <v>80</v>
       </c>
       <c r="D18" s="7">
@@ -2164,19 +2193,19 @@
         <v>839.97</v>
       </c>
       <c r="G18" s="5"/>
-      <c r="H18" s="24" t="s">
+      <c r="H18" s="22" t="s">
         <v>78</v>
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="14" t="s">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="C19" s="14" t="s">
+      <c r="C19" s="13" t="s">
         <v>81</v>
       </c>
       <c r="D19" s="8">
@@ -2190,19 +2219,19 @@
         <v>28.04</v>
       </c>
       <c r="G19" s="5"/>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="21" t="s">
         <v>170</v>
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="13" t="s">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="26" t="s">
+      <c r="B20" s="23" t="s">
         <v>171</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" s="12" t="s">
         <v>82</v>
       </c>
       <c r="D20" s="7">
@@ -2216,19 +2245,19 @@
         <v>33.58</v>
       </c>
       <c r="G20" s="5"/>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="20" t="s">
         <v>171</v>
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="14" t="s">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="26" t="s">
+      <c r="B21" s="23" t="s">
         <v>172</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="13" t="s">
         <v>83</v>
       </c>
       <c r="D21" s="8">
@@ -2242,19 +2271,19 @@
         <v>31.66</v>
       </c>
       <c r="G21" s="5"/>
-      <c r="H21" s="23" t="s">
+      <c r="H21" s="21" t="s">
         <v>172</v>
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="13" t="s">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" s="12" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="7">
@@ -2268,19 +2297,19 @@
         <v>59</v>
       </c>
       <c r="G22" s="5"/>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="20" t="s">
         <v>173</v>
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="14" t="s">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B23" s="26" t="s">
+      <c r="B23" s="23" t="s">
         <v>174</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13">
         <v>7568365</v>
       </c>
       <c r="D23" s="8">
@@ -2294,19 +2323,19 @@
         <v>682.26</v>
       </c>
       <c r="G23" s="5"/>
-      <c r="H23" s="23" t="s">
+      <c r="H23" s="21" t="s">
         <v>174</v>
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="13" t="s">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="23" t="s">
         <v>175</v>
       </c>
-      <c r="C24" s="13">
+      <c r="C24" s="12">
         <v>8323512</v>
       </c>
       <c r="D24" s="7">
@@ -2320,19 +2349,19 @@
         <v>216.04</v>
       </c>
       <c r="G24" s="5"/>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="20" t="s">
         <v>175</v>
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="14" t="s">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B25" s="23" t="s">
         <v>173</v>
       </c>
-      <c r="C25" s="14" t="s">
+      <c r="C25" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="8">
@@ -2346,19 +2375,19 @@
         <v>295</v>
       </c>
       <c r="G25" s="2"/>
-      <c r="H25" s="23" t="s">
+      <c r="H25" s="21" t="s">
         <v>173</v>
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B26" s="23" t="s">
         <v>176</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" s="12" t="s">
         <v>85</v>
       </c>
       <c r="D26" s="7">
@@ -2372,19 +2401,19 @@
         <v>83.96</v>
       </c>
       <c r="G26" s="2"/>
-      <c r="H26" s="22" t="s">
+      <c r="H26" s="20" t="s">
         <v>176</v>
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="14" t="s">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B27" s="26" t="s">
+      <c r="B27" s="23" t="s">
         <v>177</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="17" t="s">
         <v>86</v>
       </c>
       <c r="D27" s="8">
@@ -2398,18 +2427,18 @@
         <v>29.84</v>
       </c>
       <c r="G27" s="2"/>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="26" t="s">
+      <c r="B28" s="23" t="s">
         <v>178</v>
       </c>
-      <c r="C28" s="17" t="s">
+      <c r="C28" s="16" t="s">
         <v>87</v>
       </c>
       <c r="D28" s="7">
@@ -2422,18 +2451,18 @@
         <f t="shared" si="0"/>
         <v>52.92</v>
       </c>
-      <c r="H28" s="22" t="s">
+      <c r="H28" s="20" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="14" t="s">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B29" s="26" t="s">
+      <c r="B29" s="23" t="s">
         <v>179</v>
       </c>
-      <c r="C29" s="14" t="s">
+      <c r="C29" s="13" t="s">
         <v>88</v>
       </c>
       <c r="D29" s="8">
@@ -2446,18 +2475,18 @@
         <f t="shared" si="0"/>
         <v>51.12</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="H29" s="21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="26" t="s">
+      <c r="B30" s="23" t="s">
         <v>180</v>
       </c>
-      <c r="C30" s="17" t="s">
+      <c r="C30" s="16" t="s">
         <v>89</v>
       </c>
       <c r="D30" s="7">
@@ -2470,18 +2499,18 @@
         <f t="shared" si="0"/>
         <v>39.96</v>
       </c>
-      <c r="H30" s="22" t="s">
+      <c r="H30" s="20" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="14" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="26" t="s">
+      <c r="B31" s="23" t="s">
         <v>181</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="17" t="s">
         <v>90</v>
       </c>
       <c r="D31" s="8">
@@ -2494,18 +2523,18 @@
         <f t="shared" si="0"/>
         <v>89.36</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="H31" s="21" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="23" t="s">
         <v>182</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="C32" s="16" t="s">
         <v>91</v>
       </c>
       <c r="D32" s="7">
@@ -2518,18 +2547,18 @@
         <f t="shared" si="0"/>
         <v>67.56</v>
       </c>
-      <c r="H32" s="22" t="s">
+      <c r="H32" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="14" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>92</v>
       </c>
       <c r="D33" s="8">
@@ -2542,18 +2571,18 @@
         <f t="shared" si="0"/>
         <v>43.58</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="H33" s="21" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="23" t="s">
         <v>184</v>
       </c>
-      <c r="C34" s="17" t="s">
+      <c r="C34" s="16" t="s">
         <v>93</v>
       </c>
       <c r="D34" s="7">
@@ -2566,18 +2595,18 @@
         <f t="shared" si="0"/>
         <v>39.72</v>
       </c>
-      <c r="H34" s="22" t="s">
+      <c r="H34" s="20" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="14" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="26" t="s">
+      <c r="B35" s="23" t="s">
         <v>185</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>94</v>
       </c>
       <c r="D35" s="8">
@@ -2590,18 +2619,18 @@
         <f t="shared" si="0"/>
         <v>36.979999999999997</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="H35" s="21" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="26" t="s">
+      <c r="B36" s="23" t="s">
         <v>186</v>
       </c>
-      <c r="C36" s="17" t="s">
+      <c r="C36" s="16" t="s">
         <v>95</v>
       </c>
       <c r="D36" s="7">
@@ -2614,18 +2643,18 @@
         <f t="shared" si="0"/>
         <v>26.2</v>
       </c>
-      <c r="H36" s="22" t="s">
+      <c r="H36" s="20" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="14" t="s">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B37" s="26" t="s">
+      <c r="B37" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>96</v>
       </c>
       <c r="D37" s="8">
@@ -2638,18 +2667,18 @@
         <f t="shared" si="0"/>
         <v>76.88</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="H37" s="21" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="23" t="s">
         <v>188</v>
       </c>
-      <c r="C38" s="17" t="s">
+      <c r="C38" s="16" t="s">
         <v>97</v>
       </c>
       <c r="D38" s="7">
@@ -2662,18 +2691,18 @@
         <f t="shared" si="0"/>
         <v>14.879999999999999</v>
       </c>
-      <c r="H38" s="22" t="s">
+      <c r="H38" s="20" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="14" t="s">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="23" t="s">
         <v>189</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>98</v>
       </c>
       <c r="D39" s="8">
@@ -2686,18 +2715,18 @@
         <f t="shared" si="0"/>
         <v>19.259999999999998</v>
       </c>
-      <c r="H39" s="23" t="s">
+      <c r="H39" s="21" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B40" s="26" t="s">
+      <c r="B40" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C40" s="16" t="s">
         <v>99</v>
       </c>
       <c r="D40" s="7">
@@ -2710,18 +2739,18 @@
         <f t="shared" si="0"/>
         <v>16.010000000000002</v>
       </c>
-      <c r="H40" s="22" t="s">
+      <c r="H40" s="20" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="14" t="s">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="26" t="s">
+      <c r="B41" s="23" t="s">
         <v>248</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="17" t="s">
         <v>100</v>
       </c>
       <c r="D41" s="8">
@@ -2734,18 +2763,18 @@
         <f t="shared" si="0"/>
         <v>22.65</v>
       </c>
-      <c r="H41" s="23" t="s">
+      <c r="H41" s="21" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="26" t="s">
+      <c r="B42" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="C42" s="17" t="s">
+      <c r="C42" s="16" t="s">
         <v>101</v>
       </c>
       <c r="D42" s="7">
@@ -2758,18 +2787,18 @@
         <f t="shared" si="0"/>
         <v>42.599999999999994</v>
       </c>
-      <c r="H42" s="22" t="s">
+      <c r="H42" s="20" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="14" t="s">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="26" t="s">
+      <c r="B43" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="17" t="s">
         <v>102</v>
       </c>
       <c r="D43" s="8">
@@ -2782,18 +2811,18 @@
         <f t="shared" si="0"/>
         <v>50.51</v>
       </c>
-      <c r="H43" s="23" t="s">
+      <c r="H43" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="B44" s="26" t="s">
+      <c r="B44" s="23" t="s">
         <v>194</v>
       </c>
-      <c r="C44" s="17" t="s">
+      <c r="C44" s="16" t="s">
         <v>103</v>
       </c>
       <c r="D44" s="7">
@@ -2806,18 +2835,18 @@
         <f t="shared" si="0"/>
         <v>24.17</v>
       </c>
-      <c r="H44" s="22" t="s">
+      <c r="H44" s="20" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="14" t="s">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B45" s="26" t="s">
+      <c r="B45" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="17" t="s">
         <v>104</v>
       </c>
       <c r="D45" s="8">
@@ -2830,18 +2859,18 @@
         <f t="shared" si="0"/>
         <v>26.01</v>
       </c>
-      <c r="H45" s="23" t="s">
+      <c r="H45" s="21" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="13" t="s">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="B46" s="26" t="s">
+      <c r="B46" s="23" t="s">
         <v>196</v>
       </c>
-      <c r="C46" s="17" t="s">
+      <c r="C46" s="16" t="s">
         <v>105</v>
       </c>
       <c r="D46" s="7">
@@ -2854,18 +2883,18 @@
         <f t="shared" si="0"/>
         <v>16.82</v>
       </c>
-      <c r="H46" s="22" t="s">
+      <c r="H46" s="20" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="14" t="s">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B47" s="26" t="s">
+      <c r="B47" s="23" t="s">
         <v>197</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="17" t="s">
         <v>106</v>
       </c>
       <c r="D47" s="8">
@@ -2878,18 +2907,18 @@
         <f t="shared" si="0"/>
         <v>50.34</v>
       </c>
-      <c r="H47" s="23" t="s">
+      <c r="H47" s="21" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="13" t="s">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B48" s="26" t="s">
+      <c r="B48" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="C48" s="17" t="s">
+      <c r="C48" s="16" t="s">
         <v>107</v>
       </c>
       <c r="D48" s="7">
@@ -2902,18 +2931,18 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="H48" s="22" t="s">
+      <c r="H48" s="20" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="14" t="s">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B49" s="26" t="s">
+      <c r="B49" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D49" s="8">
@@ -2926,18 +2955,18 @@
         <f t="shared" si="0"/>
         <v>28.56</v>
       </c>
-      <c r="H49" s="23" t="s">
+      <c r="H49" s="21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="13" t="s">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="B50" s="26" t="s">
+      <c r="B50" s="23" t="s">
         <v>200</v>
       </c>
-      <c r="C50" s="17" t="s">
+      <c r="C50" s="16" t="s">
         <v>109</v>
       </c>
       <c r="D50" s="7">
@@ -2950,18 +2979,18 @@
         <f t="shared" si="0"/>
         <v>16.75</v>
       </c>
-      <c r="H50" s="22" t="s">
+      <c r="H50" s="20" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="14" t="s">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B51" s="26" t="s">
+      <c r="B51" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="17" t="s">
         <v>110</v>
       </c>
       <c r="D51" s="8">
@@ -2974,18 +3003,18 @@
         <f t="shared" si="0"/>
         <v>14.81</v>
       </c>
-      <c r="H51" s="23" t="s">
+      <c r="H51" s="21" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="13" t="s">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B52" s="26" t="s">
+      <c r="B52" s="23" t="s">
         <v>202</v>
       </c>
-      <c r="C52" s="17" t="s">
+      <c r="C52" s="16" t="s">
         <v>111</v>
       </c>
       <c r="D52" s="7">
@@ -2998,18 +3027,18 @@
         <f t="shared" si="0"/>
         <v>19.989999999999998</v>
       </c>
-      <c r="H52" s="22" t="s">
+      <c r="H52" s="20" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="14" t="s">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B53" s="26" t="s">
+      <c r="B53" s="23" t="s">
         <v>203</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="17" t="s">
         <v>112</v>
       </c>
       <c r="D53" s="8">
@@ -3022,18 +3051,18 @@
         <f t="shared" si="0"/>
         <v>26.8</v>
       </c>
-      <c r="H53" s="23" t="s">
+      <c r="H53" s="21" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="13" t="s">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="B54" s="26" t="s">
+      <c r="B54" s="23" t="s">
         <v>204</v>
       </c>
-      <c r="C54" s="17" t="s">
+      <c r="C54" s="16" t="s">
         <v>113</v>
       </c>
       <c r="D54" s="7">
@@ -3046,18 +3075,18 @@
         <f t="shared" si="0"/>
         <v>40.14</v>
       </c>
-      <c r="H54" s="22" t="s">
+      <c r="H54" s="20" t="s">
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="14" t="s">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="26" t="s">
+      <c r="B55" s="23" t="s">
         <v>205</v>
       </c>
-      <c r="C55" s="14" t="s">
+      <c r="C55" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D55" s="8">
@@ -3070,18 +3099,18 @@
         <f t="shared" si="0"/>
         <v>300</v>
       </c>
-      <c r="H55" s="23" t="s">
+      <c r="H55" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="13" t="s">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B56" s="26" t="s">
+      <c r="B56" s="23" t="s">
         <v>206</v>
       </c>
-      <c r="C56" s="17" t="s">
+      <c r="C56" s="16" t="s">
         <v>114</v>
       </c>
       <c r="D56" s="7">
@@ -3094,18 +3123,18 @@
         <f t="shared" si="0"/>
         <v>69.179999999999993</v>
       </c>
-      <c r="H56" s="22" t="s">
+      <c r="H56" s="20" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="14" t="s">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B57" s="26" t="s">
+      <c r="B57" s="23" t="s">
         <v>207</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="17" t="s">
         <v>115</v>
       </c>
       <c r="D57" s="8">
@@ -3118,18 +3147,18 @@
         <f t="shared" si="0"/>
         <v>9.5</v>
       </c>
-      <c r="H57" s="23" t="s">
+      <c r="H57" s="21" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="13" t="s">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B58" s="26" t="s">
+      <c r="B58" s="23" t="s">
         <v>208</v>
       </c>
-      <c r="C58" s="17" t="s">
+      <c r="C58" s="16" t="s">
         <v>116</v>
       </c>
       <c r="D58" s="7">
@@ -3142,18 +3171,18 @@
         <f t="shared" si="0"/>
         <v>5.41</v>
       </c>
-      <c r="H58" s="22" t="s">
+      <c r="H58" s="20" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="14" t="s">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="B59" s="26" t="s">
+      <c r="B59" s="23" t="s">
         <v>209</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="17" t="s">
         <v>117</v>
       </c>
       <c r="D59" s="8">
@@ -3166,18 +3195,18 @@
         <f t="shared" si="0"/>
         <v>9.0299999999999994</v>
       </c>
-      <c r="H59" s="23" t="s">
+      <c r="H59" s="21" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="13" t="s">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B60" s="26" t="s">
+      <c r="B60" s="23" t="s">
         <v>210</v>
       </c>
-      <c r="C60" s="17" t="s">
+      <c r="C60" s="16" t="s">
         <v>118</v>
       </c>
       <c r="D60" s="7">
@@ -3190,18 +3219,18 @@
         <f t="shared" si="0"/>
         <v>16.87</v>
       </c>
-      <c r="H60" s="22" t="s">
+      <c r="H60" s="20" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="14" t="s">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B61" s="26" t="s">
+      <c r="B61" s="23" t="s">
         <v>211</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="17" t="s">
         <v>119</v>
       </c>
       <c r="D61" s="8">
@@ -3214,18 +3243,18 @@
         <f t="shared" si="0"/>
         <v>14.02</v>
       </c>
-      <c r="H61" s="23" t="s">
+      <c r="H61" s="21" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="13" t="s">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="B62" s="26" t="s">
+      <c r="B62" s="23" t="s">
         <v>212</v>
       </c>
-      <c r="C62" s="17" t="s">
+      <c r="C62" s="16" t="s">
         <v>120</v>
       </c>
       <c r="D62" s="7">
@@ -3238,18 +3267,18 @@
         <f t="shared" si="0"/>
         <v>8.83</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="20" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="14" t="s">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B63" s="26" t="s">
+      <c r="B63" s="23" t="s">
         <v>213</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="17" t="s">
         <v>121</v>
       </c>
       <c r="D63" s="8">
@@ -3262,18 +3291,18 @@
         <f t="shared" si="0"/>
         <v>7.19</v>
       </c>
-      <c r="H63" s="23" t="s">
+      <c r="H63" s="21" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="13" t="s">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="26" t="s">
+      <c r="B64" s="23" t="s">
         <v>214</v>
       </c>
-      <c r="C64" s="17" t="s">
+      <c r="C64" s="16" t="s">
         <v>122</v>
       </c>
       <c r="D64" s="7">
@@ -3286,18 +3315,18 @@
         <f t="shared" si="0"/>
         <v>11.04</v>
       </c>
-      <c r="H64" s="22" t="s">
+      <c r="H64" s="20" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="14" t="s">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B65" s="26" t="s">
+      <c r="B65" s="23" t="s">
         <v>215</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="17" t="s">
         <v>123</v>
       </c>
       <c r="D65" s="8">
@@ -3310,18 +3339,18 @@
         <f t="shared" si="0"/>
         <v>6.98</v>
       </c>
-      <c r="H65" s="23" t="s">
+      <c r="H65" s="21" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="13" t="s">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B66" s="26" t="s">
+      <c r="B66" s="23" t="s">
         <v>216</v>
       </c>
-      <c r="C66" s="17" t="s">
+      <c r="C66" s="16" t="s">
         <v>124</v>
       </c>
       <c r="D66" s="7">
@@ -3334,18 +3363,18 @@
         <f t="shared" si="0"/>
         <v>42.76</v>
       </c>
-      <c r="H66" s="22" t="s">
+      <c r="H66" s="20" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="14" t="s">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B67" s="26" t="s">
+      <c r="B67" s="23" t="s">
         <v>217</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="C67" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D67" s="8">
@@ -3358,18 +3387,18 @@
         <f t="shared" ref="F67:F103" si="1">D67*E67</f>
         <v>45.81</v>
       </c>
-      <c r="H67" s="23" t="s">
+      <c r="H67" s="21" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="13" t="s">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="B68" s="26" t="s">
+      <c r="B68" s="23" t="s">
         <v>218</v>
       </c>
-      <c r="C68" s="17" t="s">
+      <c r="C68" s="16" t="s">
         <v>126</v>
       </c>
       <c r="D68" s="7">
@@ -3382,18 +3411,18 @@
         <f t="shared" si="1"/>
         <v>18.73</v>
       </c>
-      <c r="H68" s="22" t="s">
+      <c r="H68" s="20" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="14" t="s">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B69" s="26" t="s">
+      <c r="B69" s="23" t="s">
         <v>219</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="C69" s="17" t="s">
         <v>127</v>
       </c>
       <c r="D69" s="8">
@@ -3406,18 +3435,18 @@
         <f t="shared" si="1"/>
         <v>4.99</v>
       </c>
-      <c r="H69" s="23" t="s">
+      <c r="H69" s="21" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="13" t="s">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="B70" s="26" t="s">
+      <c r="B70" s="23" t="s">
         <v>220</v>
       </c>
-      <c r="C70" s="17" t="s">
+      <c r="C70" s="16" t="s">
         <v>128</v>
       </c>
       <c r="D70" s="7">
@@ -3430,18 +3459,18 @@
         <f t="shared" si="1"/>
         <v>4.68</v>
       </c>
-      <c r="H70" s="22" t="s">
+      <c r="H70" s="20" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="14" t="s">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="B71" s="26" t="s">
+      <c r="B71" s="23" t="s">
         <v>221</v>
       </c>
-      <c r="C71" s="18" t="s">
+      <c r="C71" s="17" t="s">
         <v>129</v>
       </c>
       <c r="D71" s="8">
@@ -3454,18 +3483,18 @@
         <f t="shared" si="1"/>
         <v>39.72</v>
       </c>
-      <c r="H71" s="23" t="s">
+      <c r="H71" s="21" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="13" t="s">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="B72" s="26" t="s">
+      <c r="B72" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C72" s="16" t="s">
         <v>130</v>
       </c>
       <c r="D72" s="7">
@@ -3478,18 +3507,18 @@
         <f t="shared" si="1"/>
         <v>15.07</v>
       </c>
-      <c r="H72" s="22" t="s">
+      <c r="H72" s="20" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="14" t="s">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="B73" s="26" t="s">
+      <c r="B73" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="C73" s="18" t="s">
+      <c r="C73" s="17" t="s">
         <v>131</v>
       </c>
       <c r="D73" s="8">
@@ -3502,18 +3531,18 @@
         <f t="shared" si="1"/>
         <v>45.58</v>
       </c>
-      <c r="H73" s="23" t="s">
+      <c r="H73" s="21" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="13" t="s">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="B74" s="26" t="s">
+      <c r="B74" s="23" t="s">
         <v>224</v>
       </c>
-      <c r="C74" s="17" t="s">
+      <c r="C74" s="16" t="s">
         <v>132</v>
       </c>
       <c r="D74" s="7">
@@ -3526,18 +3555,18 @@
         <f t="shared" si="1"/>
         <v>6.43</v>
       </c>
-      <c r="H74" s="22" t="s">
+      <c r="H74" s="20" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="14" t="s">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="B75" s="26" t="s">
+      <c r="B75" s="23" t="s">
         <v>225</v>
       </c>
-      <c r="C75" s="18" t="s">
+      <c r="C75" s="17" t="s">
         <v>133</v>
       </c>
       <c r="D75" s="8">
@@ -3550,18 +3579,18 @@
         <f t="shared" si="1"/>
         <v>26.5</v>
       </c>
-      <c r="H75" s="23" t="s">
+      <c r="H75" s="21" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="13" t="s">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
-      <c r="B76" s="26" t="s">
+      <c r="B76" s="23" t="s">
         <v>226</v>
       </c>
-      <c r="C76" s="13" t="s">
+      <c r="C76" s="12" t="s">
         <v>134</v>
       </c>
       <c r="D76" s="7">
@@ -3574,18 +3603,18 @@
         <f t="shared" si="1"/>
         <v>25.6</v>
       </c>
-      <c r="H76" s="22" t="s">
+      <c r="H76" s="20" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="14" t="s">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B77" s="26" t="s">
+      <c r="B77" s="23" t="s">
         <v>227</v>
       </c>
-      <c r="C77" s="18" t="s">
+      <c r="C77" s="17" t="s">
         <v>135</v>
       </c>
       <c r="D77" s="8">
@@ -3598,18 +3627,18 @@
         <f t="shared" si="1"/>
         <v>14.16</v>
       </c>
-      <c r="H77" s="23" t="s">
+      <c r="H77" s="21" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="13" t="s">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B78" s="26" t="s">
+      <c r="B78" s="23" t="s">
         <v>228</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C78" s="16" t="s">
         <v>136</v>
       </c>
       <c r="D78" s="7">
@@ -3622,18 +3651,18 @@
         <f t="shared" si="1"/>
         <v>34.900000000000006</v>
       </c>
-      <c r="H78" s="22" t="s">
+      <c r="H78" s="20" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="14" t="s">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
-      <c r="B79" s="26" t="s">
+      <c r="B79" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="C79" s="18" t="s">
+      <c r="C79" s="17" t="s">
         <v>137</v>
       </c>
       <c r="D79" s="8">
@@ -3646,18 +3675,18 @@
         <f t="shared" si="1"/>
         <v>3.76</v>
       </c>
-      <c r="H79" s="23" t="s">
+      <c r="H79" s="21" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="13" t="s">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="B80" s="26" t="s">
+      <c r="B80" s="23" t="s">
         <v>230</v>
       </c>
-      <c r="C80" s="17" t="s">
+      <c r="C80" s="16" t="s">
         <v>138</v>
       </c>
       <c r="D80" s="7">
@@ -3670,18 +3699,18 @@
         <f t="shared" si="1"/>
         <v>4.72</v>
       </c>
-      <c r="H80" s="22" t="s">
+      <c r="H80" s="20" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="14" t="s">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B81" s="26" t="s">
+      <c r="B81" s="23" t="s">
         <v>231</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="C81" s="17" t="s">
         <v>139</v>
       </c>
       <c r="D81" s="8">
@@ -3694,18 +3723,18 @@
         <f t="shared" si="1"/>
         <v>122.08</v>
       </c>
-      <c r="H81" s="23" t="s">
+      <c r="H81" s="21" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="13" t="s">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="B82" s="26" t="s">
+      <c r="B82" s="23" t="s">
         <v>232</v>
       </c>
-      <c r="C82" s="17" t="s">
+      <c r="C82" s="16" t="s">
         <v>140</v>
       </c>
       <c r="D82" s="7">
@@ -3718,18 +3747,18 @@
         <f t="shared" si="1"/>
         <v>382.26</v>
       </c>
-      <c r="H82" s="22" t="s">
+      <c r="H82" s="20" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="14" t="s">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="B83" s="26" t="s">
+      <c r="B83" s="23" t="s">
         <v>233</v>
       </c>
-      <c r="C83" s="18" t="s">
+      <c r="C83" s="17" t="s">
         <v>141</v>
       </c>
       <c r="D83" s="8">
@@ -3742,18 +3771,18 @@
         <f t="shared" si="1"/>
         <v>95.56</v>
       </c>
-      <c r="H83" s="23" t="s">
+      <c r="H83" s="21" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="13" t="s">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="B84" s="26" t="s">
+      <c r="B84" s="23" t="s">
         <v>234</v>
       </c>
-      <c r="C84" s="17" t="s">
+      <c r="C84" s="16" t="s">
         <v>142</v>
       </c>
       <c r="D84" s="7">
@@ -3766,18 +3795,18 @@
         <f t="shared" si="1"/>
         <v>49.95</v>
       </c>
-      <c r="H84" s="22" t="s">
+      <c r="H84" s="20" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="14" t="s">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B85" s="26" t="s">
+      <c r="B85" s="23" t="s">
         <v>235</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="C85" s="17" t="s">
         <v>143</v>
       </c>
       <c r="D85" s="8">
@@ -3790,18 +3819,18 @@
         <f t="shared" si="1"/>
         <v>6.02</v>
       </c>
-      <c r="H85" s="23" t="s">
+      <c r="H85" s="21" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="13" t="s">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B86" s="26" t="s">
+      <c r="B86" s="23" t="s">
         <v>236</v>
       </c>
-      <c r="C86" s="17" t="s">
+      <c r="C86" s="16" t="s">
         <v>144</v>
       </c>
       <c r="D86" s="7">
@@ -3814,18 +3843,18 @@
         <f t="shared" si="1"/>
         <v>2.3199999999999998</v>
       </c>
-      <c r="H86" s="22" t="s">
+      <c r="H86" s="20" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="14" t="s">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="B87" s="26" t="s">
+      <c r="B87" s="23" t="s">
         <v>237</v>
       </c>
-      <c r="C87" s="14" t="s">
+      <c r="C87" s="13" t="s">
         <v>78</v>
       </c>
       <c r="D87" s="8">
@@ -3838,18 +3867,18 @@
         <f t="shared" si="1"/>
         <v>47.96</v>
       </c>
-      <c r="H87" s="23" t="s">
+      <c r="H87" s="21" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="13" t="s">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="B88" s="26" t="s">
+      <c r="B88" s="23" t="s">
         <v>238</v>
       </c>
-      <c r="C88" s="13" t="s">
+      <c r="C88" s="12" t="s">
         <v>145</v>
       </c>
       <c r="D88" s="7">
@@ -3862,652 +3891,672 @@
         <f t="shared" si="1"/>
         <v>9.99</v>
       </c>
-      <c r="H88" s="22" t="s">
+      <c r="H88" s="20" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="14" t="s">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A89" s="25" t="s">
         <v>66</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>239</v>
       </c>
-      <c r="C89" s="18" t="s">
+      <c r="C89" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="D89" s="8">
+      <c r="D89" s="28">
         <v>2</v>
       </c>
-      <c r="E89" s="8">
+      <c r="E89" s="28">
         <v>14.63</v>
       </c>
-      <c r="F89" s="6">
+      <c r="F89" s="29">
         <f t="shared" si="1"/>
         <v>29.26</v>
       </c>
-      <c r="H89" s="23" t="s">
+      <c r="G89" s="30"/>
+      <c r="H89" s="31" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="13" t="s">
+      <c r="I89" s="30"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A90" s="25" t="s">
         <v>67</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="21" t="s">
+      <c r="C90" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="D90" s="7">
+      <c r="D90" s="28">
         <v>4</v>
       </c>
-      <c r="E90" s="7">
+      <c r="E90" s="28">
         <v>167.42</v>
       </c>
-      <c r="F90" s="6">
+      <c r="F90" s="29">
         <f t="shared" si="1"/>
         <v>669.68</v>
       </c>
-      <c r="H90" s="22" t="s">
+      <c r="G90" s="30"/>
+      <c r="H90" s="31" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="14" t="s">
+      <c r="I90" s="30"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A91" s="25" t="s">
         <v>46</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="C91" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="D91" s="8">
-        <v>1</v>
-      </c>
-      <c r="E91" s="8">
+      <c r="D91" s="28">
+        <v>1</v>
+      </c>
+      <c r="E91" s="28">
         <v>12.61</v>
       </c>
-      <c r="F91" s="6">
+      <c r="F91" s="29">
         <f t="shared" si="1"/>
         <v>12.61</v>
       </c>
-      <c r="H91" s="23" t="s">
+      <c r="G91" s="30"/>
+      <c r="H91" s="31" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="13" t="s">
+      <c r="I91" s="30"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A92" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B92" s="26"/>
-      <c r="C92" s="13" t="s">
+      <c r="C92" s="25" t="s">
         <v>149</v>
       </c>
-      <c r="D92" s="7">
+      <c r="D92" s="28">
         <v>2</v>
       </c>
-      <c r="E92" s="7">
+      <c r="E92" s="28">
         <v>10.45</v>
       </c>
-      <c r="F92" s="6">
+      <c r="F92" s="29">
         <f t="shared" si="1"/>
         <v>20.9</v>
       </c>
-      <c r="H92" s="24" t="s">
+      <c r="G92" s="30"/>
+      <c r="H92" s="33" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="2" t="s">
+      <c r="I92" s="30"/>
+    </row>
+    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A93" s="34" t="s">
         <v>264</v>
       </c>
-      <c r="B93" s="2" t="s">
+      <c r="B93" s="34" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="29" t="s">
+      <c r="C93" s="35" t="s">
         <v>266</v>
       </c>
-      <c r="D93" s="2">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6">
+      <c r="D93" s="34">
+        <v>1</v>
+      </c>
+      <c r="E93" s="29">
         <v>110</v>
       </c>
-      <c r="F93" s="6">
+      <c r="F93" s="29">
         <f t="shared" ref="F93:F95" si="2">D93*E93</f>
         <v>110</v>
       </c>
-      <c r="H93" s="24" t="s">
+      <c r="G93" s="30"/>
+      <c r="H93" s="33" t="s">
         <v>267</v>
       </c>
-    </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="13" t="s">
+      <c r="I93" s="30"/>
+    </row>
+    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A94" s="25" t="s">
         <v>268</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>273</v>
       </c>
-      <c r="C94" s="13" t="s">
+      <c r="C94" s="25" t="s">
         <v>274</v>
       </c>
-      <c r="D94" s="7">
-        <v>1</v>
-      </c>
-      <c r="E94" s="7">
+      <c r="D94" s="28">
+        <v>1</v>
+      </c>
+      <c r="E94" s="28">
         <v>13.55</v>
       </c>
-      <c r="F94" s="6">
+      <c r="F94" s="29">
         <f t="shared" si="2"/>
         <v>13.55</v>
       </c>
-      <c r="H94" s="22" t="s">
+      <c r="G94" s="30"/>
+      <c r="H94" s="31" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="13" t="s">
+      <c r="I94" s="30"/>
+    </row>
+    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A95" s="25" t="s">
         <v>269</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>272</v>
       </c>
-      <c r="C95" s="13" t="s">
+      <c r="C95" s="25" t="s">
         <v>275</v>
       </c>
-      <c r="D95" s="7">
-        <v>1</v>
-      </c>
-      <c r="E95" s="7">
+      <c r="D95" s="28">
+        <v>1</v>
+      </c>
+      <c r="E95" s="28">
         <v>8.4700000000000006</v>
       </c>
-      <c r="F95" s="6">
+      <c r="F95" s="29">
         <f t="shared" si="2"/>
         <v>8.4700000000000006</v>
       </c>
-      <c r="H95" s="22" t="s">
+      <c r="G95" s="30"/>
+      <c r="H95" s="31" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="14" t="s">
+      <c r="I95" s="30"/>
+    </row>
+    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A96" s="25" t="s">
         <v>68</v>
       </c>
       <c r="B96" s="26"/>
-      <c r="C96" s="14" t="s">
+      <c r="C96" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="D96" s="8">
+      <c r="D96" s="28">
         <v>3</v>
       </c>
-      <c r="E96" s="8">
+      <c r="E96" s="28">
         <v>2.1800000000000002</v>
       </c>
-      <c r="F96" s="6">
+      <c r="F96" s="29">
         <f t="shared" si="1"/>
         <v>6.5400000000000009</v>
       </c>
-      <c r="H96" s="25" t="s">
+      <c r="G96" s="30"/>
+      <c r="H96" s="33" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A97" s="13" t="s">
+      <c r="I96" s="30"/>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" s="25" t="s">
         <v>69</v>
       </c>
       <c r="B97" s="26"/>
-      <c r="C97" s="13">
+      <c r="C97" s="25">
         <v>156665159304</v>
       </c>
-      <c r="D97" s="7">
+      <c r="D97" s="28">
         <v>3</v>
       </c>
-      <c r="E97" s="7">
+      <c r="E97" s="28">
         <v>35.97</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97" s="29">
         <f t="shared" si="1"/>
         <v>107.91</v>
       </c>
-      <c r="H97" s="24" t="s">
+      <c r="G97" s="30"/>
+      <c r="H97" s="33" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A98" s="14" t="s">
+      <c r="I97" s="30"/>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" s="25" t="s">
         <v>67</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>240</v>
       </c>
-      <c r="C98" s="14" t="s">
+      <c r="C98" s="25" t="s">
         <v>147</v>
       </c>
-      <c r="D98" s="8">
+      <c r="D98" s="28">
         <v>3</v>
       </c>
-      <c r="E98" s="8">
+      <c r="E98" s="28">
         <v>167.42</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98" s="29">
         <f t="shared" si="1"/>
         <v>502.26</v>
       </c>
-      <c r="H98" s="23" t="s">
+      <c r="G98" s="30"/>
+      <c r="H98" s="31" t="s">
         <v>240</v>
       </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A99" s="13" t="s">
+      <c r="I98" s="30"/>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" s="25" t="s">
         <v>70</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>249</v>
       </c>
-      <c r="C99" s="13">
+      <c r="C99" s="25">
         <v>316529</v>
       </c>
-      <c r="D99" s="7">
-        <v>1</v>
-      </c>
-      <c r="E99" s="7">
+      <c r="D99" s="28">
+        <v>1</v>
+      </c>
+      <c r="E99" s="28">
         <v>405</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99" s="29">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="H99" s="22" t="s">
+      <c r="G99" s="30"/>
+      <c r="H99" s="31" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A100" s="14" t="s">
+      <c r="I99" s="30"/>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" s="25" t="s">
         <v>66</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>250</v>
       </c>
-      <c r="C100" s="11" t="s">
+      <c r="C100" s="36" t="s">
         <v>151</v>
       </c>
-      <c r="D100" s="8">
-        <v>1</v>
-      </c>
-      <c r="E100" s="8">
+      <c r="D100" s="28">
+        <v>1</v>
+      </c>
+      <c r="E100" s="28">
         <v>37.4</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100" s="29">
         <f t="shared" si="1"/>
         <v>37.4</v>
       </c>
-      <c r="H100" s="23" t="s">
+      <c r="G100" s="30"/>
+      <c r="H100" s="31" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" s="13" t="s">
+      <c r="I100" s="30"/>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" s="25" t="s">
         <v>17</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>244</v>
       </c>
-      <c r="C101" s="12" t="s">
+      <c r="C101" s="36" t="s">
         <v>152</v>
       </c>
-      <c r="D101" s="7">
-        <v>1</v>
-      </c>
-      <c r="E101" s="7">
+      <c r="D101" s="28">
+        <v>1</v>
+      </c>
+      <c r="E101" s="28">
         <v>20.91</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101" s="29">
         <f t="shared" si="1"/>
         <v>20.91</v>
       </c>
-      <c r="H101" s="22" t="s">
+      <c r="G101" s="30"/>
+      <c r="H101" s="31" t="s">
         <v>244</v>
       </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A102" s="14" t="s">
+      <c r="I101" s="30"/>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" s="25" t="s">
         <v>61</v>
       </c>
       <c r="B102" s="26" t="s">
         <v>251</v>
       </c>
-      <c r="C102" s="11" t="s">
+      <c r="C102" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="D102" s="8">
-        <v>1</v>
-      </c>
-      <c r="E102" s="8">
+      <c r="D102" s="28">
+        <v>1</v>
+      </c>
+      <c r="E102" s="28">
         <v>79.099999999999994</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102" s="29">
         <f t="shared" si="1"/>
         <v>79.099999999999994</v>
       </c>
-      <c r="H102" s="23" t="s">
+      <c r="G102" s="30"/>
+      <c r="H102" s="31" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A103" s="13" t="s">
+      <c r="I102" s="30"/>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" s="25" t="s">
         <v>71</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>246</v>
       </c>
-      <c r="C103" s="17" t="s">
+      <c r="C103" s="27" t="s">
         <v>153</v>
       </c>
-      <c r="D103" s="7">
-        <v>1</v>
-      </c>
-      <c r="E103" s="7">
+      <c r="D103" s="28">
+        <v>1</v>
+      </c>
+      <c r="E103" s="28">
         <v>16.260000000000002</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103" s="29">
         <f t="shared" si="1"/>
         <v>16.260000000000002</v>
       </c>
-      <c r="H103" s="22" t="s">
+      <c r="G103" s="30"/>
+      <c r="H103" s="31" t="s">
         <v>246</v>
       </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A104" s="27" t="s">
+      <c r="I103" s="30"/>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" s="37" t="s">
         <v>258</v>
       </c>
       <c r="B104" s="26" t="s">
         <v>254</v>
       </c>
-      <c r="C104" s="10" t="s">
+      <c r="C104" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="D104" s="28">
-        <v>1</v>
-      </c>
-      <c r="E104" s="28">
+      <c r="D104" s="39">
+        <v>1</v>
+      </c>
+      <c r="E104" s="39">
         <v>5.35</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104" s="29">
         <f>D104*E104</f>
         <v>5.35</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="G104" s="30"/>
+      <c r="H104" s="40" t="s">
         <v>252</v>
       </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A105" s="27" t="s">
+      <c r="I104" s="30"/>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" s="37" t="s">
         <v>259</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>256</v>
       </c>
-      <c r="C105" s="10" t="s">
+      <c r="C105" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="D105" s="28">
-        <v>1</v>
-      </c>
-      <c r="E105" s="28">
+      <c r="D105" s="39">
+        <v>1</v>
+      </c>
+      <c r="E105" s="39">
         <v>10.75</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105" s="29">
         <f>D105*E105</f>
         <v>10.75</v>
       </c>
-      <c r="H105" s="1" t="s">
+      <c r="G105" s="30"/>
+      <c r="H105" s="40" t="s">
         <v>255</v>
       </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A106" s="27" t="s">
+      <c r="I105" s="30"/>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" s="37" t="s">
         <v>260</v>
       </c>
       <c r="B106" s="26" t="s">
         <v>263</v>
       </c>
-      <c r="C106" s="10" t="s">
+      <c r="C106" s="38" t="s">
         <v>262</v>
       </c>
-      <c r="D106" s="28">
-        <v>1</v>
-      </c>
-      <c r="E106" s="28">
+      <c r="D106" s="39">
+        <v>1</v>
+      </c>
+      <c r="E106" s="39">
         <v>6.68</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106" s="29">
         <v>7.96</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="G106" s="30"/>
+      <c r="H106" s="40" t="s">
         <v>261</v>
       </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A107" s="14" t="s">
+      <c r="I106" s="30"/>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" s="25" t="s">
         <v>294</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>276</v>
       </c>
-      <c r="C107" s="10" t="s">
+      <c r="C107" s="38" t="s">
         <v>277</v>
       </c>
-      <c r="D107" s="8">
-        <v>1</v>
-      </c>
-      <c r="E107" s="8">
+      <c r="D107" s="28">
+        <v>1</v>
+      </c>
+      <c r="E107" s="28">
         <v>28.78</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107" s="29">
         <f t="shared" ref="F107:F109" si="3">D107*E107</f>
         <v>28.78</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="G107" s="30"/>
+      <c r="H107" s="40" t="s">
         <v>278</v>
       </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A108" s="14" t="s">
+      <c r="I107" s="30"/>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" s="25" t="s">
         <v>293</v>
       </c>
       <c r="B108" s="26" t="s">
         <v>281</v>
       </c>
-      <c r="C108" s="10" t="s">
+      <c r="C108" s="38" t="s">
         <v>280</v>
       </c>
-      <c r="D108" s="8">
-        <v>1</v>
-      </c>
-      <c r="E108" s="8">
+      <c r="D108" s="28">
+        <v>1</v>
+      </c>
+      <c r="E108" s="28">
         <v>146.18</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108" s="29">
         <f t="shared" si="3"/>
         <v>146.18</v>
       </c>
-      <c r="H108" s="1" t="s">
+      <c r="G108" s="30"/>
+      <c r="H108" s="40" t="s">
         <v>279</v>
       </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A109" s="14" t="s">
+      <c r="I108" s="30"/>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" s="25" t="s">
         <v>292</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>282</v>
       </c>
-      <c r="C109" s="10" t="s">
+      <c r="C109" s="38" t="s">
         <v>283</v>
       </c>
-      <c r="D109" s="8">
-        <v>1</v>
-      </c>
-      <c r="E109" s="8">
+      <c r="D109" s="28">
+        <v>1</v>
+      </c>
+      <c r="E109" s="28">
         <v>36.06</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109" s="29">
         <f t="shared" si="3"/>
         <v>36.06</v>
       </c>
-      <c r="H109" s="30" t="s">
+      <c r="G109" s="30"/>
+      <c r="H109" s="41" t="s">
         <v>284</v>
       </c>
-    </row>
-    <row r="110" spans="1:11" s="36" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="31" t="s">
+      <c r="I109" s="30"/>
+    </row>
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="42" t="s">
         <v>291</v>
       </c>
-      <c r="B110" s="32" t="s">
+      <c r="B110" s="43" t="s">
         <v>285</v>
       </c>
-      <c r="C110" s="33" t="s">
+      <c r="C110" s="44" t="s">
         <v>286</v>
       </c>
-      <c r="D110" s="34">
+      <c r="D110" s="45">
         <v>2</v>
       </c>
-      <c r="E110" s="34">
+      <c r="E110" s="45">
         <v>7.82</v>
       </c>
-      <c r="F110" s="35">
-        <f t="shared" ref="F110:F116" si="4">D110*E110</f>
+      <c r="F110" s="46">
+        <f t="shared" ref="F110:F114" si="4">D110*E110</f>
         <v>15.64</v>
       </c>
-      <c r="H110" s="37" t="s">
+      <c r="G110" s="47"/>
+      <c r="H110" s="48" t="s">
         <v>287</v>
       </c>
-    </row>
-    <row r="111" spans="1:11" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="38" t="s">
+      <c r="I110" s="47"/>
+    </row>
+    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="49" t="s">
         <v>17</v>
       </c>
-      <c r="B111" s="42" t="s">
+      <c r="B111" s="50" t="s">
         <v>288</v>
       </c>
-      <c r="C111" s="43" t="s">
+      <c r="C111" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="D111" s="39">
+      <c r="D111" s="52">
         <v>2</v>
       </c>
-      <c r="E111" s="39">
+      <c r="E111" s="52">
         <v>14.99</v>
       </c>
-      <c r="F111" s="40">
+      <c r="F111" s="53">
         <f t="shared" si="4"/>
         <v>29.98</v>
       </c>
       <c r="G111" s="26"/>
-      <c r="H111" s="41" t="s">
+      <c r="H111" s="54" t="s">
         <v>290</v>
       </c>
       <c r="I111" s="26"/>
-      <c r="J111" s="26"/>
-      <c r="K111" s="26"/>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A112" s="14"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="10"/>
-      <c r="D112" s="8"/>
-      <c r="E112" s="8"/>
+      <c r="J111" s="23"/>
+      <c r="K111" s="23"/>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="B112" s="23" t="s">
+        <v>251</v>
+      </c>
+      <c r="C112" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="D112" s="8">
+        <v>1</v>
+      </c>
+      <c r="E112" s="8">
+        <v>79.099999999999994</v>
+      </c>
       <c r="F112" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H112" s="10"/>
-    </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="14"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="10"/>
-      <c r="D113" s="8"/>
-      <c r="E113" s="8"/>
+        <v>79.099999999999994</v>
+      </c>
+      <c r="H112" s="21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B113" s="23" t="s">
+        <v>296</v>
+      </c>
+      <c r="C113" s="10" t="s">
+        <v>297</v>
+      </c>
+      <c r="D113" s="8">
+        <v>1</v>
+      </c>
+      <c r="E113" s="8">
+        <v>18.309999999999999</v>
+      </c>
       <c r="F113" s="6">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="H113" s="10"/>
-    </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="B114" s="26" t="s">
-        <v>251</v>
+        <v>18.309999999999999</v>
+      </c>
+      <c r="H113" s="1" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B114" s="23" t="s">
+        <v>250</v>
       </c>
       <c r="C114" s="11" t="s">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="D114" s="8">
         <v>1</v>
       </c>
       <c r="E114" s="8">
-        <v>79.099999999999994</v>
+        <v>37.4</v>
       </c>
       <c r="F114" s="6">
         <f t="shared" si="4"/>
-        <v>79.099999999999994</v>
-      </c>
-      <c r="H114" s="23" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B115" s="26" t="s">
-        <v>296</v>
-      </c>
-      <c r="C115" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D115" s="8">
-        <v>1</v>
-      </c>
-      <c r="E115" s="8">
-        <v>18.309999999999999</v>
-      </c>
-      <c r="F115" s="6">
-        <f t="shared" si="4"/>
-        <v>18.309999999999999</v>
-      </c>
-      <c r="H115" s="1" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="B116" s="26" t="s">
-        <v>250</v>
-      </c>
-      <c r="C116" s="11" t="s">
-        <v>151</v>
-      </c>
-      <c r="D116" s="8">
-        <v>1</v>
-      </c>
-      <c r="E116" s="8">
         <v>37.4</v>
       </c>
-      <c r="F116" s="6">
-        <f t="shared" si="4"/>
-        <v>37.4</v>
-      </c>
-      <c r="H116" s="23" t="s">
+      <c r="H114" s="21" t="s">
         <v>243</v>
       </c>
     </row>
@@ -4618,9 +4667,9 @@
     <hyperlink ref="H109" r:id="rId102" xr:uid="{DA2A078E-95DA-4F11-A662-702B09E6F14A}"/>
     <hyperlink ref="H110" r:id="rId103" display="https://www.grainger.com/product/803H45?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{05215C5A-3A93-40D1-9E83-5B1ABEB0BD2B}"/>
     <hyperlink ref="H111" r:id="rId104" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{0F353E44-E7EA-4190-9112-90CB38990103}"/>
-    <hyperlink ref="H114" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
-    <hyperlink ref="H115" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
-    <hyperlink ref="H116" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
+    <hyperlink ref="H112" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
+    <hyperlink ref="H113" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
+    <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId108"/>

--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32175D1D-5F07-4B8C-9BA3-FC15C9F4C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{32175D1D-5F07-4B8C-9BA3-FC15C9F4C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19D10E8E-0365-404B-8293-397CD78FB61C}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="298">
   <si>
     <t>Total Cost</t>
   </si>
@@ -1098,7 +1098,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1170,89 +1170,80 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1368,8 +1359,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K114" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K114" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K120" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K120" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1706,25 +1697,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M114"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:M120"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.42578125" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" customWidth="1"/>
-    <col min="12" max="12" width="55.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.6640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1759,7 +1750,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1785,7 +1776,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1811,7 +1802,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1836,7 +1827,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1862,7 +1853,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1888,7 +1879,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1916,7 +1907,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1942,7 +1933,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1969,7 +1960,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -1994,7 +1985,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2020,7 +2011,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2044,7 +2035,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2070,7 +2061,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2096,7 +2087,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2122,7 +2113,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2148,7 +2139,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2174,7 +2165,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2198,7 +2189,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2224,7 +2215,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2250,7 +2241,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2276,7 +2267,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2302,7 +2293,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2328,7 +2319,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2354,7 +2345,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2380,7 +2371,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2406,7 +2397,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2431,7 +2422,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2455,7 +2446,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2479,7 +2470,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2503,7 +2494,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2527,7 +2518,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2551,7 +2542,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2575,7 +2566,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2599,7 +2590,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2623,7 +2614,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2647,7 +2638,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2671,7 +2662,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2695,7 +2686,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2719,7 +2710,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2743,7 +2734,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2767,7 +2758,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2791,7 +2782,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2815,7 +2806,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2839,7 +2830,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2863,7 +2854,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2887,7 +2878,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2911,7 +2902,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -2935,7 +2926,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -2959,7 +2950,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -2983,7 +2974,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -3007,7 +2998,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3031,7 +3022,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3055,7 +3046,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3079,7 +3070,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3103,7 +3094,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3127,7 +3118,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3151,7 +3142,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3175,7 +3166,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3199,7 +3190,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3223,7 +3214,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3247,7 +3238,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3271,7 +3262,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3295,7 +3286,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3319,7 +3310,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3343,7 +3334,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3367,7 +3358,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3391,7 +3382,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3415,7 +3406,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3439,7 +3430,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3463,7 +3454,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3487,7 +3478,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3511,7 +3502,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3535,7 +3526,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3559,7 +3550,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3583,7 +3574,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3607,7 +3598,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3631,7 +3622,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3655,7 +3646,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3679,7 +3670,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3703,7 +3694,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3727,7 +3718,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3751,7 +3742,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3775,7 +3766,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3799,7 +3790,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3823,7 +3814,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3847,7 +3838,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3871,7 +3862,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3895,600 +3886,556 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A89" s="25" t="s">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B89" s="26" t="s">
+      <c r="B89" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="C89" s="27" t="s">
+      <c r="C89" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="D89" s="28">
+      <c r="D89" s="8">
         <v>2</v>
       </c>
-      <c r="E89" s="28">
+      <c r="E89" s="8">
         <v>14.63</v>
       </c>
-      <c r="F89" s="29">
+      <c r="F89" s="6">
         <f t="shared" si="1"/>
         <v>29.26</v>
       </c>
-      <c r="G89" s="30"/>
-      <c r="H89" s="31" t="s">
+      <c r="H89" s="25" t="s">
         <v>239</v>
       </c>
-      <c r="I89" s="30"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A90" s="25" t="s">
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B90" s="26" t="s">
+      <c r="B90" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="C90" s="32" t="s">
+      <c r="C90" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="D90" s="28">
+      <c r="D90" s="8">
         <v>4</v>
       </c>
-      <c r="E90" s="28">
+      <c r="E90" s="8">
         <v>167.42</v>
       </c>
-      <c r="F90" s="29">
+      <c r="F90" s="6">
         <f t="shared" si="1"/>
         <v>669.68</v>
       </c>
-      <c r="G90" s="30"/>
-      <c r="H90" s="31" t="s">
+      <c r="H90" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="I90" s="30"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A91" s="25" t="s">
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B91" s="26" t="s">
+      <c r="B91" s="23" t="s">
         <v>241</v>
       </c>
-      <c r="C91" s="27" t="s">
+      <c r="C91" s="17" t="s">
         <v>148</v>
       </c>
-      <c r="D91" s="28">
-        <v>1</v>
-      </c>
-      <c r="E91" s="28">
+      <c r="D91" s="8">
+        <v>1</v>
+      </c>
+      <c r="E91" s="8">
         <v>12.61</v>
       </c>
-      <c r="F91" s="29">
+      <c r="F91" s="6">
         <f t="shared" si="1"/>
         <v>12.61</v>
       </c>
-      <c r="G91" s="30"/>
-      <c r="H91" s="31" t="s">
+      <c r="H91" s="25" t="s">
         <v>241</v>
       </c>
-      <c r="I91" s="30"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A92" s="25" t="s">
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B92" s="26"/>
-      <c r="C92" s="25" t="s">
+      <c r="B92" s="23"/>
+      <c r="C92" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="D92" s="28">
+      <c r="D92" s="8">
         <v>2</v>
       </c>
-      <c r="E92" s="28">
+      <c r="E92" s="8">
         <v>10.45</v>
       </c>
-      <c r="F92" s="29">
+      <c r="F92" s="6">
         <f t="shared" si="1"/>
         <v>20.9</v>
       </c>
-      <c r="G92" s="30"/>
-      <c r="H92" s="33" t="s">
+      <c r="H92" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="I92" s="30"/>
-    </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A93" s="34" t="s">
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B93" s="34" t="s">
+      <c r="B93" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="C93" s="35" t="s">
+      <c r="C93" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="D93" s="34">
-        <v>1</v>
-      </c>
-      <c r="E93" s="29">
+      <c r="D93" s="2">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6">
         <v>110</v>
       </c>
-      <c r="F93" s="29">
+      <c r="F93" s="6">
         <f t="shared" ref="F93:F95" si="2">D93*E93</f>
         <v>110</v>
       </c>
-      <c r="G93" s="30"/>
-      <c r="H93" s="33" t="s">
+      <c r="H93" s="27" t="s">
         <v>267</v>
       </c>
-      <c r="I93" s="30"/>
-    </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A94" s="25" t="s">
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
-      <c r="B94" s="26" t="s">
+      <c r="B94" s="23" t="s">
         <v>273</v>
       </c>
-      <c r="C94" s="25" t="s">
+      <c r="C94" s="13" t="s">
         <v>274</v>
       </c>
-      <c r="D94" s="28">
-        <v>1</v>
-      </c>
-      <c r="E94" s="28">
+      <c r="D94" s="8">
+        <v>1</v>
+      </c>
+      <c r="E94" s="8">
         <v>13.55</v>
       </c>
-      <c r="F94" s="29">
+      <c r="F94" s="6">
         <f t="shared" si="2"/>
         <v>13.55</v>
       </c>
-      <c r="G94" s="30"/>
-      <c r="H94" s="31" t="s">
+      <c r="H94" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="I94" s="30"/>
-    </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A95" s="25" t="s">
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
-      <c r="B95" s="26" t="s">
+      <c r="B95" s="23" t="s">
         <v>272</v>
       </c>
-      <c r="C95" s="25" t="s">
+      <c r="C95" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="D95" s="28">
-        <v>1</v>
-      </c>
-      <c r="E95" s="28">
+      <c r="D95" s="8">
+        <v>1</v>
+      </c>
+      <c r="E95" s="8">
         <v>8.4700000000000006</v>
       </c>
-      <c r="F95" s="29">
+      <c r="F95" s="6">
         <f t="shared" si="2"/>
         <v>8.4700000000000006</v>
       </c>
-      <c r="G95" s="30"/>
-      <c r="H95" s="31" t="s">
+      <c r="H95" s="25" t="s">
         <v>270</v>
       </c>
-      <c r="I95" s="30"/>
-    </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A96" s="25" t="s">
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="B96" s="26"/>
-      <c r="C96" s="25" t="s">
+      <c r="B96" s="23"/>
+      <c r="C96" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D96" s="28">
+      <c r="D96" s="8">
         <v>3</v>
       </c>
-      <c r="E96" s="28">
+      <c r="E96" s="8">
         <v>2.1800000000000002</v>
       </c>
-      <c r="F96" s="29">
+      <c r="F96" s="6">
         <f t="shared" si="1"/>
         <v>6.5400000000000009</v>
       </c>
-      <c r="G96" s="30"/>
-      <c r="H96" s="33" t="s">
+      <c r="H96" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="I96" s="30"/>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="25" t="s">
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="B97" s="26"/>
-      <c r="C97" s="25">
+      <c r="B97" s="23"/>
+      <c r="C97" s="13">
         <v>156665159304</v>
       </c>
-      <c r="D97" s="28">
+      <c r="D97" s="8">
         <v>3</v>
       </c>
-      <c r="E97" s="28">
+      <c r="E97" s="8">
         <v>35.97</v>
       </c>
-      <c r="F97" s="29">
+      <c r="F97" s="6">
         <f t="shared" si="1"/>
         <v>107.91</v>
       </c>
-      <c r="G97" s="30"/>
-      <c r="H97" s="33" t="s">
+      <c r="H97" s="27" t="s">
         <v>78</v>
       </c>
-      <c r="I97" s="30"/>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="25" t="s">
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="B98" s="26" t="s">
+      <c r="B98" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="C98" s="25" t="s">
+      <c r="C98" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="D98" s="28">
+      <c r="D98" s="8">
         <v>3</v>
       </c>
-      <c r="E98" s="28">
+      <c r="E98" s="8">
         <v>167.42</v>
       </c>
-      <c r="F98" s="29">
+      <c r="F98" s="6">
         <f t="shared" si="1"/>
         <v>502.26</v>
       </c>
-      <c r="G98" s="30"/>
-      <c r="H98" s="31" t="s">
+      <c r="H98" s="25" t="s">
         <v>240</v>
       </c>
-      <c r="I98" s="30"/>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="25" t="s">
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="B99" s="26" t="s">
+      <c r="B99" s="23" t="s">
         <v>249</v>
       </c>
-      <c r="C99" s="25">
+      <c r="C99" s="13">
         <v>316529</v>
       </c>
-      <c r="D99" s="28">
-        <v>1</v>
-      </c>
-      <c r="E99" s="28">
+      <c r="D99" s="8">
+        <v>1</v>
+      </c>
+      <c r="E99" s="8">
         <v>405</v>
       </c>
-      <c r="F99" s="29">
+      <c r="F99" s="6">
         <f t="shared" si="1"/>
         <v>405</v>
       </c>
-      <c r="G99" s="30"/>
-      <c r="H99" s="31" t="s">
+      <c r="H99" s="25" t="s">
         <v>242</v>
       </c>
-      <c r="I99" s="30"/>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A100" s="25" t="s">
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="B100" s="26" t="s">
+      <c r="B100" s="23" t="s">
         <v>250</v>
       </c>
-      <c r="C100" s="36" t="s">
+      <c r="C100" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="D100" s="28">
-        <v>1</v>
-      </c>
-      <c r="E100" s="28">
+      <c r="D100" s="8">
+        <v>1</v>
+      </c>
+      <c r="E100" s="8">
         <v>37.4</v>
       </c>
-      <c r="F100" s="29">
+      <c r="F100" s="6">
         <f t="shared" si="1"/>
         <v>37.4</v>
       </c>
-      <c r="G100" s="30"/>
-      <c r="H100" s="31" t="s">
+      <c r="H100" s="25" t="s">
         <v>243</v>
       </c>
-      <c r="I100" s="30"/>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A101" s="25" t="s">
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="B101" s="26" t="s">
+      <c r="B101" s="23" t="s">
         <v>244</v>
       </c>
-      <c r="C101" s="36" t="s">
+      <c r="C101" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="D101" s="28">
-        <v>1</v>
-      </c>
-      <c r="E101" s="28">
+      <c r="D101" s="8">
+        <v>1</v>
+      </c>
+      <c r="E101" s="8">
         <v>20.91</v>
       </c>
-      <c r="F101" s="29">
+      <c r="F101" s="6">
         <f t="shared" si="1"/>
         <v>20.91</v>
       </c>
-      <c r="G101" s="30"/>
-      <c r="H101" s="31" t="s">
+      <c r="H101" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="I101" s="30"/>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="25" t="s">
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="B102" s="26" t="s">
+      <c r="B102" s="23" t="s">
         <v>251</v>
       </c>
-      <c r="C102" s="36" t="s">
+      <c r="C102" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="D102" s="28">
-        <v>1</v>
-      </c>
-      <c r="E102" s="28">
+      <c r="D102" s="8">
+        <v>1</v>
+      </c>
+      <c r="E102" s="8">
         <v>79.099999999999994</v>
       </c>
-      <c r="F102" s="29">
+      <c r="F102" s="6">
         <f t="shared" si="1"/>
         <v>79.099999999999994</v>
       </c>
-      <c r="G102" s="30"/>
-      <c r="H102" s="31" t="s">
+      <c r="H102" s="25" t="s">
         <v>245</v>
       </c>
-      <c r="I102" s="30"/>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="25" t="s">
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="B103" s="26" t="s">
+      <c r="B103" s="23" t="s">
         <v>246</v>
       </c>
-      <c r="C103" s="27" t="s">
+      <c r="C103" s="17" t="s">
         <v>153</v>
       </c>
-      <c r="D103" s="28">
-        <v>1</v>
-      </c>
-      <c r="E103" s="28">
+      <c r="D103" s="8">
+        <v>1</v>
+      </c>
+      <c r="E103" s="8">
         <v>16.260000000000002</v>
       </c>
-      <c r="F103" s="29">
+      <c r="F103" s="6">
         <f t="shared" si="1"/>
         <v>16.260000000000002</v>
       </c>
-      <c r="G103" s="30"/>
-      <c r="H103" s="31" t="s">
+      <c r="H103" s="25" t="s">
         <v>246</v>
       </c>
-      <c r="I103" s="30"/>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="37" t="s">
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
-      <c r="B104" s="26" t="s">
+      <c r="B104" s="23" t="s">
         <v>254</v>
       </c>
-      <c r="C104" s="38" t="s">
+      <c r="C104" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="D104" s="39">
-        <v>1</v>
-      </c>
-      <c r="E104" s="39">
+      <c r="D104" s="30">
+        <v>1</v>
+      </c>
+      <c r="E104" s="30">
         <v>5.35</v>
       </c>
-      <c r="F104" s="29">
+      <c r="F104" s="6">
         <f>D104*E104</f>
         <v>5.35</v>
       </c>
-      <c r="G104" s="30"/>
-      <c r="H104" s="40" t="s">
+      <c r="H104" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="I104" s="30"/>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="37" t="s">
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
-      <c r="B105" s="26" t="s">
+      <c r="B105" s="23" t="s">
         <v>256</v>
       </c>
-      <c r="C105" s="38" t="s">
+      <c r="C105" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="D105" s="39">
-        <v>1</v>
-      </c>
-      <c r="E105" s="39">
+      <c r="D105" s="30">
+        <v>1</v>
+      </c>
+      <c r="E105" s="30">
         <v>10.75</v>
       </c>
-      <c r="F105" s="29">
+      <c r="F105" s="6">
         <f>D105*E105</f>
         <v>10.75</v>
       </c>
-      <c r="G105" s="30"/>
-      <c r="H105" s="40" t="s">
+      <c r="H105" s="31" t="s">
         <v>255</v>
       </c>
-      <c r="I105" s="30"/>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="37" t="s">
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="B106" s="26" t="s">
+      <c r="B106" s="23" t="s">
         <v>263</v>
       </c>
-      <c r="C106" s="38" t="s">
+      <c r="C106" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D106" s="39">
-        <v>1</v>
-      </c>
-      <c r="E106" s="39">
+      <c r="D106" s="30">
+        <v>1</v>
+      </c>
+      <c r="E106" s="30">
         <v>6.68</v>
       </c>
-      <c r="F106" s="29">
+      <c r="F106" s="6">
         <v>7.96</v>
       </c>
-      <c r="G106" s="30"/>
-      <c r="H106" s="40" t="s">
+      <c r="H106" s="31" t="s">
         <v>261</v>
       </c>
-      <c r="I106" s="30"/>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="25" t="s">
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
-      <c r="B107" s="26" t="s">
+      <c r="B107" s="23" t="s">
         <v>276</v>
       </c>
-      <c r="C107" s="38" t="s">
+      <c r="C107" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="D107" s="28">
-        <v>1</v>
-      </c>
-      <c r="E107" s="28">
+      <c r="D107" s="8">
+        <v>1</v>
+      </c>
+      <c r="E107" s="8">
         <v>28.78</v>
       </c>
-      <c r="F107" s="29">
+      <c r="F107" s="6">
         <f t="shared" ref="F107:F109" si="3">D107*E107</f>
         <v>28.78</v>
       </c>
-      <c r="G107" s="30"/>
-      <c r="H107" s="40" t="s">
+      <c r="H107" s="31" t="s">
         <v>278</v>
       </c>
-      <c r="I107" s="30"/>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="25" t="s">
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
-      <c r="B108" s="26" t="s">
+      <c r="B108" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="C108" s="38" t="s">
+      <c r="C108" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="D108" s="28">
-        <v>1</v>
-      </c>
-      <c r="E108" s="28">
+      <c r="D108" s="8">
+        <v>1</v>
+      </c>
+      <c r="E108" s="8">
         <v>146.18</v>
       </c>
-      <c r="F108" s="29">
+      <c r="F108" s="6">
         <f t="shared" si="3"/>
         <v>146.18</v>
       </c>
-      <c r="G108" s="30"/>
-      <c r="H108" s="40" t="s">
+      <c r="H108" s="31" t="s">
         <v>279</v>
       </c>
-      <c r="I108" s="30"/>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="25" t="s">
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
-      <c r="B109" s="26" t="s">
+      <c r="B109" s="23" t="s">
         <v>282</v>
       </c>
-      <c r="C109" s="38" t="s">
+      <c r="C109" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="D109" s="28">
-        <v>1</v>
-      </c>
-      <c r="E109" s="28">
+      <c r="D109" s="8">
+        <v>1</v>
+      </c>
+      <c r="E109" s="8">
         <v>36.06</v>
       </c>
-      <c r="F109" s="29">
+      <c r="F109" s="6">
         <f t="shared" si="3"/>
         <v>36.06</v>
       </c>
-      <c r="G109" s="30"/>
-      <c r="H109" s="41" t="s">
+      <c r="H109" s="32" t="s">
         <v>284</v>
       </c>
-      <c r="I109" s="30"/>
-    </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="42" t="s">
+    </row>
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
-      <c r="B110" s="43" t="s">
+      <c r="B110" s="34" t="s">
         <v>285</v>
       </c>
-      <c r="C110" s="44" t="s">
+      <c r="C110" s="35" t="s">
         <v>286</v>
       </c>
-      <c r="D110" s="45">
+      <c r="D110" s="36">
         <v>2</v>
       </c>
-      <c r="E110" s="45">
+      <c r="E110" s="36">
         <v>7.82</v>
       </c>
-      <c r="F110" s="46">
+      <c r="F110" s="37">
         <f t="shared" ref="F110:F114" si="4">D110*E110</f>
         <v>15.64</v>
       </c>
-      <c r="G110" s="47"/>
-      <c r="H110" s="48" t="s">
+      <c r="H110" s="38" t="s">
         <v>287</v>
       </c>
-      <c r="I110" s="47"/>
-    </row>
-    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="49" t="s">
+    </row>
+    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="B111" s="50" t="s">
+      <c r="B111" s="40" t="s">
         <v>288</v>
       </c>
-      <c r="C111" s="51" t="s">
+      <c r="C111" s="41" t="s">
         <v>289</v>
       </c>
-      <c r="D111" s="52">
+      <c r="D111" s="42">
         <v>2</v>
       </c>
-      <c r="E111" s="52">
+      <c r="E111" s="42">
         <v>14.99</v>
       </c>
-      <c r="F111" s="53">
+      <c r="F111" s="43">
         <f t="shared" si="4"/>
         <v>29.98</v>
       </c>
-      <c r="G111" s="26"/>
-      <c r="H111" s="54" t="s">
+      <c r="G111" s="23"/>
+      <c r="H111" s="44" t="s">
         <v>290</v>
       </c>
-      <c r="I111" s="26"/>
+      <c r="I111" s="23"/>
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4512,7 +4459,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4536,7 +4483,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4559,6 +4506,113 @@
       <c r="H114" s="21" t="s">
         <v>243</v>
       </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A115" s="45"/>
+      <c r="B115" s="47"/>
+      <c r="C115" s="48"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="49">
+        <f t="shared" ref="F115:F120" si="5">D115*E115</f>
+        <v>0</v>
+      </c>
+      <c r="G115" s="50"/>
+      <c r="H115" s="51"/>
+      <c r="I115" s="50"/>
+      <c r="J115" s="50"/>
+      <c r="K115" s="50"/>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A116" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>240</v>
+      </c>
+      <c r="C116" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D116" s="8">
+        <v>3</v>
+      </c>
+      <c r="E116" s="8">
+        <v>167.42</v>
+      </c>
+      <c r="F116" s="6">
+        <f t="shared" si="5"/>
+        <v>502.26</v>
+      </c>
+      <c r="H116" s="25" t="s">
+        <v>240</v>
+      </c>
+      <c r="I116" s="50"/>
+      <c r="J116" s="50"/>
+      <c r="K116" s="50"/>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A117" s="45"/>
+      <c r="B117" s="47"/>
+      <c r="C117" s="48"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G117" s="50"/>
+      <c r="H117" s="51"/>
+      <c r="I117" s="50"/>
+      <c r="J117" s="50"/>
+      <c r="K117" s="50"/>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A118" s="45"/>
+      <c r="B118" s="47"/>
+      <c r="C118" s="48"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G118" s="50"/>
+      <c r="H118" s="51"/>
+      <c r="I118" s="50"/>
+      <c r="J118" s="50"/>
+      <c r="K118" s="50"/>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A119" s="45"/>
+      <c r="B119" s="47"/>
+      <c r="C119" s="48"/>
+      <c r="D119" s="8"/>
+      <c r="E119" s="8"/>
+      <c r="F119" s="49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G119" s="50"/>
+      <c r="H119" s="51"/>
+      <c r="I119" s="50"/>
+      <c r="J119" s="50"/>
+      <c r="K119" s="50"/>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="46"/>
+      <c r="B120" s="47"/>
+      <c r="C120" s="48"/>
+      <c r="D120" s="30"/>
+      <c r="E120" s="30"/>
+      <c r="F120" s="49">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="G120" s="50"/>
+      <c r="H120" s="51"/>
+      <c r="I120" s="50"/>
+      <c r="J120" s="50"/>
+      <c r="K120" s="50"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4670,11 +4724,12 @@
     <hyperlink ref="H112" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
     <hyperlink ref="H113" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
     <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
+    <hyperlink ref="H116" r:id="rId108" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{8630E460-1674-409E-96EC-4238C68DEF5F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId108"/>
+  <pageSetup orientation="portrait" r:id="rId109"/>
   <tableParts count="1">
-    <tablePart r:id="rId109"/>
+    <tablePart r:id="rId110"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{32175D1D-5F07-4B8C-9BA3-FC15C9F4C689}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19D10E8E-0365-404B-8293-397CD78FB61C}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891D376-54C6-4945-BAD1-C808920EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="299">
   <si>
     <t>Total Cost</t>
   </si>
@@ -930,6 +930,9 @@
   </si>
   <si>
     <t>20XM55</t>
+  </si>
+  <si>
+    <t>https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V</t>
   </si>
 </sst>
 </file>
@@ -1098,7 +1101,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1225,25 +1228,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1698,24 +1682,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M120"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.44140625" customWidth="1"/>
-    <col min="11" max="11" width="62.44140625" customWidth="1"/>
-    <col min="12" max="12" width="55.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.42578125" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" customWidth="1"/>
+    <col min="12" max="12" width="55.7109375" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1750,7 +1734,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1776,7 +1760,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1802,7 +1786,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1827,7 +1811,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1853,7 +1837,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1879,7 +1863,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1907,7 +1891,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1933,7 +1917,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1960,7 +1944,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -1985,7 +1969,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2011,7 +1995,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2035,7 +2019,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2061,7 +2045,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2087,7 +2071,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2113,7 +2097,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2139,7 +2123,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2165,7 +2149,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2189,7 +2173,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2215,7 +2199,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2241,7 +2225,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2267,7 +2251,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2293,7 +2277,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2319,7 +2303,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2345,7 +2329,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2371,7 +2355,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2397,7 +2381,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2422,7 +2406,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2446,7 +2430,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2470,7 +2454,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2494,7 +2478,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2518,7 +2502,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2542,7 +2526,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2566,7 +2550,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2590,7 +2574,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2614,7 +2598,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2638,7 +2622,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2662,7 +2646,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2686,7 +2670,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2710,7 +2694,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2734,7 +2718,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2758,7 +2742,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2782,7 +2766,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2806,7 +2790,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2830,7 +2814,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2854,7 +2838,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2878,7 +2862,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2902,7 +2886,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -2926,7 +2910,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -2950,7 +2934,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -2974,7 +2958,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -2998,7 +2982,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3022,7 +3006,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3046,7 +3030,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3070,7 +3054,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3094,7 +3078,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3118,7 +3102,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3142,7 +3126,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3166,7 +3150,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3190,7 +3174,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3214,7 +3198,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3238,7 +3222,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3262,7 +3246,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3286,7 +3270,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3310,7 +3294,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3334,7 +3318,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3358,7 +3342,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3382,7 +3366,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3406,7 +3390,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3430,7 +3414,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3454,7 +3438,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3478,7 +3462,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3502,7 +3486,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3526,7 +3510,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3550,7 +3534,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3574,7 +3558,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3598,7 +3582,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3622,7 +3606,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3646,7 +3630,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3670,7 +3654,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3694,7 +3678,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3718,7 +3702,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3742,7 +3726,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3766,7 +3750,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3790,7 +3774,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3814,7 +3798,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3838,7 +3822,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3862,7 +3846,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3886,7 +3870,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
@@ -3910,7 +3894,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3934,7 +3918,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
@@ -3958,7 +3942,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -3980,7 +3964,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -4004,7 +3988,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4028,7 +4012,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4052,7 +4036,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
@@ -4074,7 +4058,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4096,7 +4080,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
@@ -4120,7 +4104,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4144,7 +4128,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
@@ -4168,7 +4152,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4192,7 +4176,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
@@ -4216,7 +4200,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4240,7 +4224,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
@@ -4264,7 +4248,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
@@ -4288,7 +4272,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
@@ -4311,7 +4295,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
@@ -4335,7 +4319,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
@@ -4359,7 +4343,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
@@ -4383,7 +4367,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
@@ -4407,7 +4391,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
@@ -4435,7 +4419,7 @@
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4459,7 +4443,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4483,7 +4467,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4507,23 +4491,19 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A115" s="45"/>
-      <c r="B115" s="47"/>
-      <c r="C115" s="48"/>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="13"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="10"/>
       <c r="D115" s="8"/>
       <c r="E115" s="8"/>
-      <c r="F115" s="49">
+      <c r="F115" s="6">
         <f t="shared" ref="F115:F120" si="5">D115*E115</f>
         <v>0</v>
       </c>
-      <c r="G115" s="50"/>
-      <c r="H115" s="51"/>
-      <c r="I115" s="50"/>
-      <c r="J115" s="50"/>
-      <c r="K115" s="50"/>
-    </row>
-    <row r="116" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H115" s="10"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="13" t="s">
         <v>67</v>
       </c>
@@ -4544,75 +4524,56 @@
         <v>502.26</v>
       </c>
       <c r="H116" s="25" t="s">
-        <v>240</v>
-      </c>
-      <c r="I116" s="50"/>
-      <c r="J116" s="50"/>
-      <c r="K116" s="50"/>
-    </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A117" s="45"/>
-      <c r="B117" s="47"/>
-      <c r="C117" s="48"/>
+        <v>298</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" s="13"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="10"/>
       <c r="D117" s="8"/>
       <c r="E117" s="8"/>
-      <c r="F117" s="49">
+      <c r="F117" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G117" s="50"/>
-      <c r="H117" s="51"/>
-      <c r="I117" s="50"/>
-      <c r="J117" s="50"/>
-      <c r="K117" s="50"/>
-    </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A118" s="45"/>
-      <c r="B118" s="47"/>
-      <c r="C118" s="48"/>
+      <c r="H117" s="10"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" s="13"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="10"/>
       <c r="D118" s="8"/>
       <c r="E118" s="8"/>
-      <c r="F118" s="49">
+      <c r="F118" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G118" s="50"/>
-      <c r="H118" s="51"/>
-      <c r="I118" s="50"/>
-      <c r="J118" s="50"/>
-      <c r="K118" s="50"/>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="45"/>
-      <c r="B119" s="47"/>
-      <c r="C119" s="48"/>
+      <c r="H118" s="10"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" s="13"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="10"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
-      <c r="F119" s="49">
+      <c r="F119" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G119" s="50"/>
-      <c r="H119" s="51"/>
-      <c r="I119" s="50"/>
-      <c r="J119" s="50"/>
-      <c r="K119" s="50"/>
-    </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="46"/>
-      <c r="B120" s="47"/>
-      <c r="C120" s="48"/>
+      <c r="H119" s="10"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" s="29"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="10"/>
       <c r="D120" s="30"/>
       <c r="E120" s="30"/>
-      <c r="F120" s="49">
+      <c r="F120" s="6">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="G120" s="50"/>
-      <c r="H120" s="51"/>
-      <c r="I120" s="50"/>
-      <c r="J120" s="50"/>
-      <c r="K120" s="50"/>
+      <c r="H120" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4724,7 +4685,7 @@
     <hyperlink ref="H112" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
     <hyperlink ref="H113" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
     <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
-    <hyperlink ref="H116" r:id="rId108" display="https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V" xr:uid="{8630E460-1674-409E-96EC-4238C68DEF5F}"/>
+    <hyperlink ref="H116" r:id="rId108" xr:uid="{4C7D87CB-190D-4B5C-AF33-DA969CBF5188}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId109"/>

--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C891D376-54C6-4945-BAD1-C808920EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{C891D376-54C6-4945-BAD1-C808920EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9201627-024D-497F-B630-842EB3C3FD84}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="298">
   <si>
     <t>Total Cost</t>
   </si>
@@ -930,9 +930,6 @@
   </si>
   <si>
     <t>20XM55</t>
-  </si>
-  <si>
-    <t>https://www.dwyeromega.com/en-us/oem-style-compact-pressure-transmitters/PX119/p/PX159A-060G5V</t>
   </si>
 </sst>
 </file>
@@ -1682,24 +1679,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M120"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.42578125" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" customWidth="1"/>
-    <col min="12" max="12" width="55.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.6640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1734,7 +1731,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1760,7 +1757,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1786,7 +1783,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1811,7 +1808,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1837,7 +1834,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1863,7 +1860,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1891,7 +1888,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1917,7 +1914,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1944,7 +1941,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -1969,7 +1966,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -1995,7 +1992,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2019,7 +2016,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2045,7 +2042,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2071,7 +2068,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2097,7 +2094,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2123,7 +2120,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2149,7 +2146,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2173,7 +2170,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2199,7 +2196,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2225,7 +2222,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2251,7 +2248,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2277,7 +2274,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2303,7 +2300,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2329,7 +2326,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2355,7 +2352,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2381,7 +2378,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2406,7 +2403,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2430,7 +2427,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2454,7 +2451,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2478,7 +2475,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2502,7 +2499,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2526,7 +2523,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2550,7 +2547,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2574,7 +2571,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2598,7 +2595,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2622,7 +2619,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2646,7 +2643,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2670,7 +2667,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2694,7 +2691,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2718,7 +2715,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2742,7 +2739,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2766,7 +2763,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2790,7 +2787,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2814,7 +2811,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2838,7 +2835,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2862,7 +2859,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2886,7 +2883,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -2910,7 +2907,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -2934,7 +2931,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -2958,7 +2955,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -2982,7 +2979,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3006,7 +3003,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3030,7 +3027,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3054,7 +3051,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3078,7 +3075,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3102,7 +3099,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3126,7 +3123,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3150,7 +3147,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3174,7 +3171,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3198,7 +3195,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3222,7 +3219,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3246,7 +3243,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3270,7 +3267,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3294,7 +3291,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3318,7 +3315,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3342,7 +3339,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3366,7 +3363,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3390,7 +3387,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3414,7 +3411,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3438,7 +3435,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3462,7 +3459,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3486,7 +3483,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3510,7 +3507,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3534,7 +3531,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3558,7 +3555,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3582,7 +3579,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3606,7 +3603,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3630,7 +3627,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3654,7 +3651,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3678,7 +3675,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3702,7 +3699,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3726,7 +3723,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3750,7 +3747,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3774,7 +3771,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3798,7 +3795,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3822,7 +3819,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3846,7 +3843,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3870,7 +3867,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
@@ -3894,7 +3891,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3918,7 +3915,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
@@ -3942,7 +3939,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -3964,7 +3961,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -3988,7 +3985,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4012,7 +4009,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4036,7 +4033,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
@@ -4058,7 +4055,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4080,7 +4077,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
@@ -4104,7 +4101,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4128,7 +4125,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
@@ -4152,7 +4149,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4176,7 +4173,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
@@ -4200,7 +4197,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4224,7 +4221,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
@@ -4248,7 +4245,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
@@ -4272,7 +4269,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
@@ -4295,7 +4292,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
@@ -4319,7 +4316,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
@@ -4343,7 +4340,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
@@ -4367,7 +4364,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
@@ -4391,7 +4388,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
@@ -4419,7 +4416,7 @@
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4443,7 +4440,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4467,7 +4464,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4491,7 +4488,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
       <c r="B115" s="23"/>
       <c r="C115" s="10"/>
@@ -4503,31 +4500,32 @@
       </c>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B116" s="23" t="s">
-        <v>240</v>
-      </c>
-      <c r="C116" s="26" t="s">
-        <v>147</v>
-      </c>
-      <c r="D116" s="8">
-        <v>3</v>
-      </c>
-      <c r="E116" s="8">
-        <v>167.42</v>
-      </c>
-      <c r="F116" s="6">
+    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="39" t="s">
+        <v>17</v>
+      </c>
+      <c r="B116" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C116" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="D116" s="42">
+        <v>1</v>
+      </c>
+      <c r="E116" s="42">
+        <v>14.99</v>
+      </c>
+      <c r="F116" s="43">
         <f t="shared" si="5"/>
-        <v>502.26</v>
-      </c>
-      <c r="H116" s="25" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14.99</v>
+      </c>
+      <c r="G116" s="23"/>
+      <c r="H116" s="44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="13"/>
       <c r="B117" s="23"/>
       <c r="C117" s="10"/>
@@ -4539,7 +4537,7 @@
       </c>
       <c r="H117" s="10"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
       <c r="B118" s="23"/>
       <c r="C118" s="10"/>
@@ -4551,7 +4549,7 @@
       </c>
       <c r="H118" s="10"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
@@ -4563,7 +4561,7 @@
       </c>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="29"/>
       <c r="B120" s="23"/>
       <c r="C120" s="10"/>
@@ -4685,7 +4683,7 @@
     <hyperlink ref="H112" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
     <hyperlink ref="H113" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
     <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
-    <hyperlink ref="H116" r:id="rId108" xr:uid="{4C7D87CB-190D-4B5C-AF33-DA969CBF5188}"/>
+    <hyperlink ref="H116" r:id="rId108" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C0D4D21-381D-4DE0-8627-C5CDD08AC966}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId109"/>

--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{C891D376-54C6-4945-BAD1-C808920EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D9201627-024D-497F-B630-842EB3C3FD84}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{C891D376-54C6-4945-BAD1-C808920EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFE4294F-78A9-46B5-B161-08D30B50E7C9}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="302">
   <si>
     <t>Total Cost</t>
   </si>
@@ -930,6 +930,18 @@
   </si>
   <si>
     <t>20XM55</t>
+  </si>
+  <si>
+    <t>Lug Terminal</t>
+  </si>
+  <si>
+    <t>Compression Lug: 3/8 in Stud Size, 4/0 AWG – 4/0 AWG For Wire Sizes, Stranded Wire Type, Std, Copper</t>
+  </si>
+  <si>
+    <t>24C366</t>
+  </si>
+  <si>
+    <t>3/8 in Stud Size, 4/0 AWG – 4/0 AWG For Wire Sizes, Compression Lug - 24C366|24C366 - Grainger</t>
   </si>
 </sst>
 </file>
@@ -4526,16 +4538,28 @@
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="13"/>
-      <c r="B117" s="23"/>
-      <c r="C117" s="10"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
+      <c r="A117" s="13" t="s">
+        <v>298</v>
+      </c>
+      <c r="B117" s="23" t="s">
+        <v>299</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="D117" s="8">
+        <v>3</v>
+      </c>
+      <c r="E117" s="8">
+        <v>6.37</v>
+      </c>
       <c r="F117" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H117" s="10"/>
+        <v>19.11</v>
+      </c>
+      <c r="H117" s="1" t="s">
+        <v>301</v>
+      </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="13"/>
@@ -4684,11 +4708,12 @@
     <hyperlink ref="H113" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
     <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
     <hyperlink ref="H116" r:id="rId108" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C0D4D21-381D-4DE0-8627-C5CDD08AC966}"/>
+    <hyperlink ref="H117" r:id="rId109" display="https://www.grainger.com/product/Compression-Lug-3-8-in-Stud-24C366" xr:uid="{969E4A0C-E52F-4A17-A6F5-A3D01F24676B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId109"/>
+  <pageSetup orientation="portrait" r:id="rId110"/>
   <tableParts count="1">
-    <tablePart r:id="rId110"/>
+    <tablePart r:id="rId111"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/thermal-loop/resources/v0.1.2/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{C891D376-54C6-4945-BAD1-C808920EC2F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EFE4294F-78A9-46B5-B161-08D30B50E7C9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="303">
   <si>
     <t>Total Cost</t>
   </si>
@@ -942,6 +942,9 @@
   </si>
   <si>
     <t>3/8 in Stud Size, 4/0 AWG – 4/0 AWG For Wire Sizes, Compression Lug - 24C366|24C366 - Grainger</t>
+  </si>
+  <si>
+    <t>NiChrome Rod joining Compression Fitting</t>
   </si>
 </sst>
 </file>
@@ -1691,24 +1694,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M120"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.44140625" customWidth="1"/>
-    <col min="11" max="11" width="62.44140625" customWidth="1"/>
-    <col min="12" max="12" width="55.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.42578125" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" customWidth="1"/>
+    <col min="12" max="12" width="55.7109375" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1769,7 +1772,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1795,7 +1798,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1820,7 +1823,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1846,7 +1849,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1872,7 +1875,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1900,7 +1903,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1926,7 +1929,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1953,7 +1956,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -1978,7 +1981,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2004,7 +2007,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2028,7 +2031,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2054,7 +2057,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2080,7 +2083,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2106,7 +2109,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2132,7 +2135,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2158,7 +2161,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2182,7 +2185,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2208,7 +2211,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2234,7 +2237,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2260,7 +2263,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2286,7 +2289,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2312,7 +2315,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2338,7 +2341,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2364,7 +2367,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2390,7 +2393,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2415,7 +2418,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2439,7 +2442,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2463,7 +2466,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2487,7 +2490,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2511,7 +2514,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2535,7 +2538,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2559,7 +2562,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2583,7 +2586,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2607,7 +2610,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2631,7 +2634,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2655,7 +2658,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2679,7 +2682,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2703,7 +2706,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2727,7 +2730,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2751,7 +2754,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2775,7 +2778,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2799,7 +2802,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2823,7 +2826,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2847,7 +2850,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2871,7 +2874,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2895,7 +2898,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -2919,7 +2922,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -2943,7 +2946,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -2967,7 +2970,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -2991,7 +2994,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3015,7 +3018,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3039,7 +3042,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3063,7 +3066,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3087,7 +3090,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3111,7 +3114,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3135,7 +3138,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3159,7 +3162,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3183,7 +3186,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3207,7 +3210,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3231,7 +3234,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3255,7 +3258,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3279,7 +3282,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3303,7 +3306,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3327,7 +3330,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3351,7 +3354,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3375,7 +3378,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3399,7 +3402,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3423,7 +3426,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3447,7 +3450,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3471,7 +3474,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3495,7 +3498,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3519,7 +3522,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3543,7 +3546,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3567,7 +3570,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3591,7 +3594,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3615,7 +3618,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3639,7 +3642,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3663,7 +3666,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3687,7 +3690,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3711,7 +3714,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3735,7 +3738,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3759,7 +3762,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3783,7 +3786,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3807,7 +3810,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3831,7 +3834,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3855,7 +3858,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3879,7 +3882,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
@@ -3903,7 +3906,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3927,7 +3930,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
@@ -3951,7 +3954,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -3973,7 +3976,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -3997,7 +4000,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4021,7 +4024,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4045,7 +4048,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
@@ -4067,7 +4070,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4089,7 +4092,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
@@ -4113,7 +4116,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4137,7 +4140,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
@@ -4161,7 +4164,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4185,7 +4188,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
@@ -4209,7 +4212,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4233,7 +4236,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
@@ -4257,7 +4260,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
@@ -4281,7 +4284,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
@@ -4304,7 +4307,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
@@ -4328,7 +4331,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
@@ -4352,7 +4355,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
@@ -4376,7 +4379,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
@@ -4400,7 +4403,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
@@ -4428,7 +4431,7 @@
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4452,7 +4455,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4476,7 +4479,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4500,7 +4503,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="13"/>
       <c r="B115" s="23"/>
       <c r="C115" s="10"/>
@@ -4512,9 +4515,9 @@
       </c>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="39" t="s">
-        <v>17</v>
+        <v>302</v>
       </c>
       <c r="B116" s="40" t="s">
         <v>288</v>
@@ -4537,7 +4540,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
         <v>298</v>
       </c>
@@ -4561,7 +4564,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
       <c r="B118" s="23"/>
       <c r="C118" s="10"/>
@@ -4573,7 +4576,7 @@
       </c>
       <c r="H118" s="10"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
@@ -4585,7 +4588,7 @@
       </c>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="29"/>
       <c r="B120" s="23"/>
       <c r="C120" s="10"/>

--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/core2s/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF25476-B12E-45D4-A545-B6A7F31C32AC}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-150" windowWidth="29040" windowHeight="15720" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="454" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="306">
   <si>
     <t>Total Cost</t>
   </si>
@@ -945,6 +945,15 @@
   </si>
   <si>
     <t>NiChrome Rod joining Compression Fitting</t>
+  </si>
+  <si>
+    <t>BB-MDR-40-48 Advantech Corporation | Industrial, DIN Rail Power Supplies | DigiKey</t>
+  </si>
+  <si>
+    <t>MeanWell 48V Power Supply</t>
+  </si>
+  <si>
+    <t>MDR-40-48 100-240VAC</t>
   </si>
 </sst>
 </file>
@@ -955,7 +964,7 @@
     <numFmt numFmtId="7" formatCode="&quot;$&quot;#,##0.00_);\(&quot;$&quot;#,##0.00\)"/>
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1052,6 +1061,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1113,7 +1128,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1241,6 +1256,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1694,24 +1710,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M120"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.42578125" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" customWidth="1"/>
-    <col min="12" max="12" width="55.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.6640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1746,7 +1762,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1772,7 +1788,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1798,7 +1814,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1823,7 +1839,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1849,7 +1865,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1875,7 +1891,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1903,7 +1919,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1929,7 +1945,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -1956,7 +1972,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -1981,7 +1997,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2007,7 +2023,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2031,7 +2047,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2057,7 +2073,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2083,7 +2099,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2109,7 +2125,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2135,7 +2151,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2161,7 +2177,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2185,7 +2201,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2211,7 +2227,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2237,7 +2253,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2263,7 +2279,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2289,7 +2305,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2315,7 +2331,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2341,7 +2357,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2367,7 +2383,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2393,7 +2409,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2418,7 +2434,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2442,7 +2458,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2466,7 +2482,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2490,7 +2506,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2514,7 +2530,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2538,7 +2554,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2562,7 +2578,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2586,7 +2602,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2610,7 +2626,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2634,7 +2650,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2658,7 +2674,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2682,7 +2698,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2706,7 +2722,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2730,7 +2746,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2754,7 +2770,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2778,7 +2794,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2802,7 +2818,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2826,7 +2842,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2850,7 +2866,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2874,7 +2890,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2898,7 +2914,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -2922,7 +2938,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -2946,7 +2962,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -2970,7 +2986,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -2994,7 +3010,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3018,7 +3034,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3042,7 +3058,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3066,7 +3082,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3090,7 +3106,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3114,7 +3130,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3138,7 +3154,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3162,7 +3178,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3186,7 +3202,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3210,7 +3226,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3234,7 +3250,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3258,7 +3274,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3282,7 +3298,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3306,7 +3322,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3330,7 +3346,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3354,7 +3370,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3378,7 +3394,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3402,7 +3418,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3426,7 +3442,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3450,7 +3466,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3474,7 +3490,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3498,7 +3514,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3522,7 +3538,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3546,7 +3562,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3570,7 +3586,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3594,7 +3610,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3618,7 +3634,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3642,7 +3658,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3666,7 +3682,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3690,7 +3706,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3714,7 +3730,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3738,7 +3754,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3762,7 +3778,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3786,7 +3802,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3810,7 +3826,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3834,7 +3850,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3858,7 +3874,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3882,7 +3898,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
@@ -3906,7 +3922,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3930,7 +3946,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
@@ -3954,7 +3970,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -3976,7 +3992,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -4000,7 +4016,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4024,7 +4040,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4048,7 +4064,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
@@ -4070,7 +4086,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4092,7 +4108,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
@@ -4116,7 +4132,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4140,7 +4156,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
@@ -4164,7 +4180,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4188,7 +4204,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
@@ -4212,7 +4228,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4236,7 +4252,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
@@ -4260,7 +4276,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
@@ -4284,7 +4300,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
@@ -4307,7 +4323,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
@@ -4331,7 +4347,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
@@ -4355,7 +4371,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
@@ -4379,7 +4395,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
@@ -4403,7 +4419,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
@@ -4431,7 +4447,7 @@
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4455,7 +4471,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4479,7 +4495,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4503,7 +4519,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
       <c r="B115" s="23"/>
       <c r="C115" s="10"/>
@@ -4515,7 +4531,7 @@
       </c>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="39" t="s">
         <v>302</v>
       </c>
@@ -4540,7 +4556,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>298</v>
       </c>
@@ -4564,19 +4580,29 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="13"/>
-      <c r="B118" s="23"/>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A118" s="13" t="s">
+        <v>304</v>
+      </c>
+      <c r="B118" s="45" t="s">
+        <v>305</v>
+      </c>
       <c r="C118" s="10"/>
-      <c r="D118" s="8"/>
-      <c r="E118" s="8"/>
+      <c r="D118" s="8">
+        <v>1</v>
+      </c>
+      <c r="E118" s="8">
+        <v>14.79</v>
+      </c>
       <c r="F118" s="6">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="H118" s="10"/>
-    </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+        <v>14.79</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
@@ -4588,7 +4614,7 @@
       </c>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="29"/>
       <c r="B120" s="23"/>
       <c r="C120" s="10"/>
@@ -4712,11 +4738,12 @@
     <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
     <hyperlink ref="H116" r:id="rId108" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C0D4D21-381D-4DE0-8627-C5CDD08AC966}"/>
     <hyperlink ref="H117" r:id="rId109" display="https://www.grainger.com/product/Compression-Lug-3-8-in-Stud-24C366" xr:uid="{969E4A0C-E52F-4A17-A6F5-A3D01F24676B}"/>
+    <hyperlink ref="H118" r:id="rId110" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId110"/>
+  <pageSetup orientation="portrait" r:id="rId111"/>
   <tableParts count="1">
-    <tablePart r:id="rId111"/>
+    <tablePart r:id="rId112"/>
   </tableParts>
 </worksheet>
 </file>